--- a/naver-place-crawler/results_nail/분당_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/분당_네일샵.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>트리나네일</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>treenanail@naver.com</t>
-        </is>
-      </c>
+          <t>보니타네일 더푸스프로</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1361-6532</t>
+          <t>0507-1327-4406</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/tree_na_nail</t>
+          <t>http://instagram.com/bonita_sohe_e</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +602,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4wl1y</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1157</v>
+        <v>634</v>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="R2" t="n">
-        <v>1252</v>
+        <v>686</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1331495059</t>
+          <t>1005133986</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331495059</t>
+          <t>https://m.place.naver.com/place/1005133986</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,34 +654,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일팜</t>
+          <t>르에 판교점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nailpalm@naver.com</t>
+          <t>leehhnail@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1371-5111</t>
+          <t>0507-1466-0874</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 돌마로 67 금산젬월드 4층 405호</t>
+          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailpalm</t>
+          <t>https://link.inpock.co.kr/le.ehh</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -719,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>857</v>
+        <v>106</v>
       </c>
       <c r="Q3" t="n">
-        <v>319</v>
+        <v>54</v>
       </c>
       <c r="R3" t="n">
-        <v>1176</v>
+        <v>160</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>37398310</t>
+          <t>1963747515</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37398310</t>
+          <t>https://m.place.naver.com/place/1963747515</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,29 +748,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일오브윤 분당점</t>
+          <t>더블트리</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>o___o373@naver.com</t>
+          <t>doubletree-lash@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1366-7390</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/o___o373</t>
+          <t>http://instagram.com/doubletree_nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +781,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -813,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1129</v>
+        <v>138</v>
       </c>
       <c r="Q4" t="n">
-        <v>894</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>2023</v>
+        <v>152</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1300308336</t>
+          <t>32699868</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300308336</t>
+          <t>https://m.place.naver.com/place/32699868</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -850,34 +838,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에러퍼펙트 분당서현점</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>jungwonnail@naver.com</t>
-        </is>
-      </c>
+          <t>나는 너의 네일</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1436-5758</t>
+          <t>0507-1391-8690</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 5층(다이소 바로 옆건물)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+          <t>https://pf.kakao.com/_Jxahxkxj/friend</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -887,22 +871,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs4bo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -911,13 +891,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1938</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>638</v>
+        <v>40</v>
       </c>
       <c r="R5" t="n">
-        <v>2576</v>
+        <v>49</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,17 +906,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1180875815</t>
+          <t>1174632490</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180875815</t>
+          <t>https://m.place.naver.com/place/1174632490</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -948,34 +928,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>조이네일</t>
+          <t>뮤네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>aa6364844@naver.com</t>
+          <t>mieux_by_nail@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1352-5816</t>
+          <t>0507-1474-1789</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 장미로 78 시그마3오피스텔 2층 207호</t>
+          <t>경기도 성남시 분당구 성남대로925번길 19 5층 501-2호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aa6364844</t>
+          <t>http://pf.kakao.com/_fxizxcxj</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -985,22 +965,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs0wd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +985,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2313</v>
+        <v>233</v>
       </c>
       <c r="Q6" t="n">
-        <v>602</v>
+        <v>26</v>
       </c>
       <c r="R6" t="n">
-        <v>2915</v>
+        <v>259</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1000,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37049599</t>
+          <t>1325100624</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37049599</t>
+          <t>https://m.place.naver.com/place/1325100624</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1046,29 +1022,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>827네일 분당미금점</t>
+          <t>네일보담</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>827nail@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1308-0827</t>
+          <t>0507-1344-9616</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 성남대로144번길 16 1층 827네일</t>
+          <t>경기도 성남시 분당구 성남대로926번길 12 금탑프라자 103호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/827nail</t>
+          <t>https://www.instagram.com/nail_bodam/?r=nametag</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1088,17 +1064,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcht5i</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1079,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2515</v>
+        <v>297</v>
       </c>
       <c r="Q7" t="n">
-        <v>383</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>2898</v>
+        <v>336</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1094,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1290037889</t>
+          <t>1229535513</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290037889</t>
+          <t>https://m.place.naver.com/place/1229535513</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1116,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>레푸스 판교점</t>
+          <t>네일스튜디오미니</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>yedamcp@naver.com</t>
+          <t>milk924@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-702-8870</t>
+          <t>031-789-3555</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yedamcp</t>
+          <t>http://www.instagram.com/nail_mini</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,19 +1153,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ui8r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1173,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1369</v>
+        <v>315</v>
       </c>
       <c r="Q8" t="n">
-        <v>567</v>
+        <v>33</v>
       </c>
       <c r="R8" t="n">
-        <v>1936</v>
+        <v>348</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1188,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1710320799</t>
+          <t>495440903</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710320799</t>
+          <t>https://m.place.naver.com/place/495440903</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1242,39 +1210,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>오로지푸스 앤 네일 스파</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>orosy2020@naver.com</t>
-        </is>
-      </c>
+          <t>메이드마이네일</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1382-0859</t>
+          <t>0507-1370-1842</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 느티로 16 304호</t>
+          <t>경기도 성남시 분당구 분당로53번길 14 2층 208호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/dnrtwwsxK</t>
+          <t>https://www.instagram.com/made_mynail</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1299,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>120</v>
+        <v>252</v>
       </c>
       <c r="Q9" t="n">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="R9" t="n">
-        <v>232</v>
+        <v>410</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1948399629</t>
+          <t>1528348158</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948399629</t>
+          <t>https://m.place.naver.com/place/1528348158</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1336,29 +1300,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일팰리스</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>nailpalace@naver.com</t>
-        </is>
-      </c>
+          <t>루나네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1325-7941</t>
+          <t>0507-1338-3307</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 백현로101번길 13 월드프라자 1층 올케어풋 \u002F 3층 네일팰리스</t>
+          <t>경기도 성남시 분당구 황새울로360번길 12 3층 317, 318호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailpalace_official/</t>
+          <t>https://open.kakao.com/o/sKOPRm0f</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1378,17 +1338,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc34mh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1397,13 +1353,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>243</v>
+        <v>164</v>
       </c>
       <c r="Q10" t="n">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="R10" t="n">
-        <v>344</v>
+        <v>204</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,17 +1368,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>33928799</t>
+          <t>1892992657</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33928799</t>
+          <t>https://m.place.naver.com/place/1892992657</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1434,29 +1390,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>쏘굿네일 분당미금점</t>
+          <t>모스네일 판교점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sohyun1304@naver.com</t>
+          <t>mossnail@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1427-2394</t>
+          <t>0507-1317-6311</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 돌마로 73 우방코아 2층 211호</t>
+          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/sso_good_nail</t>
+          <t>https://www.instagram.com/moss._.nail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1476,14 +1432,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc2e4j</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1495,13 +1447,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1398</v>
+        <v>395</v>
       </c>
       <c r="Q11" t="n">
-        <v>390</v>
+        <v>69</v>
       </c>
       <c r="R11" t="n">
-        <v>1788</v>
+        <v>464</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,17 +1462,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1235289874</t>
+          <t>1816221132</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1235289874</t>
+          <t>https://m.place.naver.com/place/1816221132</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1532,93 +1484,6001 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일, 연</t>
+          <t>레푸스 분당정자점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>leca814@naver.com</t>
+          <t>refuss_bundang@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1400-3992</t>
+          <t>031-709-8870</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 야탑로 95 세신빌딩 1층 107호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 3층 304호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>https://blog.naver.com/refuss_bundang</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1033</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>131</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1164</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1293054958</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293054958</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>비온빛 네일브라운 분당미금점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nailb1212@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1407-1279</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 52 2층 203호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailbrown_</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>879</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>784</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1663</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1647015847</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1647015847</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jjuahlee@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1403-3341</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1031</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>121</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1152</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>37870150</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37870150</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>네일팜</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>nailpalm@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1371-5111</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 67 금산젬월드 4층 405호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nailpalm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>862</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>322</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1184</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>37398310</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37398310</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>네일, 연</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wlsl9169@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1400-3992</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 1층 107호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/nailyeon_?igsh=MXAxdWN4M2I1ZHRldQ==</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yspj</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>227</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+      <c r="R16" t="n">
+        <v>256</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1232273978</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1232273978</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>라이티티아네일</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>laetitia5980@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/laetitia_nail_j</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>101</v>
+      </c>
+      <c r="R17" t="n">
+        <v>257</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1418162766</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1418162766</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>라모르뷰티 분당수내 본점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lamour11@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1465-5979</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>http://instagram.com/lamour.nail</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>81</v>
+      </c>
+      <c r="R18" t="n">
+        <v>343</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1397181784</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397181784</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>예쁘게살자</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sukjin1125@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>031-702-9340</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 2층 예쁘게살자</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sukjin1125</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>753</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>41</v>
+      </c>
+      <c r="R19" t="n">
+        <v>794</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1221851423</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1221851423</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>트리나네일</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>treenanail@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1361-6532</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/tree_na_nail</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1157</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>95</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1252</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1331495059</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1331495059</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>하낭네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1322-5647</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 73 현대 빌딩 2층 204호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ha.nang_nail_studio?igsh=MTR4anJrZW8yN3M4eA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>582</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>11</v>
+      </c>
+      <c r="R21" t="n">
+        <v>593</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1339933062</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1339933062</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>레푸스 판교점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>yedamcp@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>031-702-8870</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yedamcp</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1373</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>567</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1940</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1710320799</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1710320799</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>다다네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>tykd2048@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1466-3338</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dada.nail/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>70</v>
+      </c>
+      <c r="R23" t="n">
+        <v>511</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>240537974</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/240537974</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>조이네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>aa6364844@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1352-5816</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 2층 207호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aa6364844</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>2328</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>603</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2931</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>37049599</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37049599</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>포세타네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>achellnet@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailfossetta</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>86</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1702940792</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1702940792</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>반디인하우스 큐릭스 분당서현점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sdfw3t4@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1359-2111</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sdfw3t4</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1105</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>34</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1139</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1557758291</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1557758291</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>내일그리고네일</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>major13564@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1397-7847</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tomorrow7836</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>517</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>47</v>
+      </c>
+      <c r="R27" t="n">
+        <v>564</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1389203098</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1389203098</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>솜솜네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>mydbfla33@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1416-2241</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 51 포스빌 지하1층 50호 솜솜네일</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/somsomnail_</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>405</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>51</v>
+      </c>
+      <c r="R28" t="n">
+        <v>456</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1165691375</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1165691375</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>포쉬네일 AK분당점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1416-2324</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/forsynail_footcare</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>683</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>58</v>
+      </c>
+      <c r="R29" t="n">
+        <v>741</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1692272902</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1692272902</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>네일 조안</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>lds9525@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1369-6361</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>328</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>31</v>
+      </c>
+      <c r="R30" t="n">
+        <v>359</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1520161470</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1520161470</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>루미네일 수내점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1445-6255</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로165번길 38 청구아파트 상가 601동 125호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luminail_bd</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>522</v>
+      </c>
+      <c r="Q31" t="n">
         <v>29</v>
       </c>
-      <c r="R12" t="n">
-        <v>256</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1232273978</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1232273978</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="R31" t="n">
+        <v>551</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1065650334</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1065650334</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>버베인네일 분당수내점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>llltwjhlll@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1375-0335</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/llltwjhlll</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>31</v>
+      </c>
+      <c r="R32" t="n">
+        <v>84</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2016496556</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2016496556</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>바이뮤즈</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ynh3377@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 121 1층 C 10-1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_bymuse_</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>56</v>
+      </c>
+      <c r="R33" t="n">
+        <v>499</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1198012559</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1198012559</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>뷰티네일소리 야탑점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>smnewya@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1397-6467</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로926번길 12 8층 801-5호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>http://instagram.com/soriii_nail</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>43</v>
+      </c>
+      <c r="R34" t="n">
+        <v>343</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1650592747</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1650592747</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>다나네일</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>spring7503@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1464-0476</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 165 2층 218호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_FZMiG</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>11</v>
+      </c>
+      <c r="R35" t="n">
+        <v>241</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1679531126</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1679531126</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>네일드잇</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>suzing9@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로 172 2층 203호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://instagram.com/nailedit_mj</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>34</v>
+      </c>
+      <c r="R36" t="n">
+        <v>228</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>37918491</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37918491</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>러브엘네일</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>haniii_world@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 47 513-1호 5층 내려서 바로 왼쪽 입니다 :)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xhRYWn</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7</v>
+      </c>
+      <c r="R37" t="n">
+        <v>254</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2023334466</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2023334466</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>벨라뷰티</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>aqsw0111@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1391-1078</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 158 백궁프라자2 3층 301호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bellabeauty_nail</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>467</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>54</v>
+      </c>
+      <c r="R38" t="n">
+        <v>521</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1236154271</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236154271</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>백프로네일</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1416-7323</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_MgAwxl</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>118</v>
+      </c>
+      <c r="R39" t="n">
+        <v>184</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>512636239</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/512636239</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>후와네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1342-1792</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>446</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>18</v>
+      </c>
+      <c r="R40" t="n">
+        <v>464</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1782262137</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1782262137</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>네일바이라라</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>iam_jihye@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1356-4115</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailbylala.official</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>29</v>
+      </c>
+      <c r="R41" t="n">
+        <v>386</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1737395332</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1737395332</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>uijn_dd@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cherryshbeauty_official</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1078</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>524</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1602</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>36524000</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36524000</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>헤몬네일</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>barbie7085055@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/barbie7085055</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1297</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>718</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2015</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1117775011</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1117775011</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>손수지은</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>iksamo@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>031-711-7615</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 146 엠코헤리츠 1단지 101동 A128호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sonsu__</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>25</v>
+      </c>
+      <c r="R44" t="n">
+        <v>188</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1320525764</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320525764</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>하르네일</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1305-3099</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/harr__nail/</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>36</v>
+      </c>
+      <c r="R45" t="n">
+        <v>306</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2066713618</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2066713618</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>위치네일스 판교점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>witch_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>031-622-7290</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/witch_nail</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>554</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>67</v>
+      </c>
+      <c r="R46" t="n">
+        <v>621</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1458353971</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1458353971</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>네일인90</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>nailin90@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1331-0990</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로925번길 16 성남분당여객자동차터미널 2층 네일인90</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_in90</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1153</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>53</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1206</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1354180497</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1354180497</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>네일그자체</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wisp1205@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_itself</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>23</v>
+      </c>
+      <c r="R48" t="n">
+        <v>189</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2089755300</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2089755300</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>827네일 분당미금점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>827nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1308-0827</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로144번길 16 1층 827네일</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/827nail</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>2523</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>383</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2906</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1290037889</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1290037889</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>숨숨네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>rnys11@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1334-7410</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/soomsoom.nail</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>211</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>12</v>
+      </c>
+      <c r="R50" t="n">
+        <v>223</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1619651823</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1619651823</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>네일아르떼</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>tpfla1999@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__nail.arte/</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>37</v>
+      </c>
+      <c r="R51" t="n">
+        <v>510</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1010349043</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1010349043</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>네일포엠</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sahsar@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1381-1685</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 295 대림아크로텔 c동 129호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_poem</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>21</v>
+      </c>
+      <c r="R52" t="n">
+        <v>96</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1373998196</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1373998196</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>띠어리네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1314-1851</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 68 1층 107호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/theorynail</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>983</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>222</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1205</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1230407614</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1230407614</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>포쉬네일 판교아브뉴프랑점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>silentforest_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>031-603-3011</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>132</v>
+      </c>
+      <c r="R54" t="n">
+        <v>333</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>38258395</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38258395</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>쏘굿네일 분당미금점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sohyun1304@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1427-2394</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 73 우방코아 2층 211호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/sso_good_nail</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>1410</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>390</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1800</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1235289874</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1235289874</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>네일오브윤 분당점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>o___o373@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1366-7390</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/o___o373</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1158</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>916</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2074</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1300308336</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1300308336</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>에러퍼펙트 분당서현점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jungwonnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1436-5758</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>1950</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>639</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2589</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1180875815</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1180875815</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>온들네일 분당정자점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>lovmaria@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1443-7794</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 67 1층 104호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xkxaKin</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>26</v>
+      </c>
+      <c r="R58" t="n">
+        <v>80</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2085728870</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2085728870</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>안녕,예쁜손</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>bbolm@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1429-8836</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/hello_jininail</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>885</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>258</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1143</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>13399185</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13399185</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>서영언니네일 앤 뷰티크 판교점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>seo0unnienail@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1429-9122</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>2434</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2341</v>
+      </c>
+      <c r="R60" t="n">
+        <v>4775</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1335668367</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1335668367</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>네일발라봄</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>yuri831211@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1350-1712</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 51 B29호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nailballabom</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>14</v>
+      </c>
+      <c r="R61" t="n">
+        <v>41</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1585268852</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1585268852</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>비비네일</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1365-1483</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xnCjDG</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>38</v>
+      </c>
+      <c r="R62" t="n">
+        <v>145</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1505688975</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1505688975</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>네일다움 내성발톱 무좀 발각질 네일 문제성발 디톡스족욕</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>nail_dawoom@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1483-9994</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 85 동양프라자 4층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/foot_naildawoom</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>630</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>391</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1021</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1587982343</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587982343</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>뮤요네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>rabong1219@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1389-6160</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>306</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>18</v>
+      </c>
+      <c r="R64" t="n">
+        <v>324</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1549676698</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1549676698</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>오로지푸스 앤 네일 스파</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1382-0859</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 16 304호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://toss.place/_lb/dnrtwwsxK</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>116</v>
+      </c>
+      <c r="R65" t="n">
+        <v>241</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1948399629</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1948399629</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>베베네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>kub1207@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1309-9064</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 3층 308호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/bebe.nailstudio</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>341</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>26</v>
+      </c>
+      <c r="R66" t="n">
+        <v>367</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1290736362</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1290736362</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>무니네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>032-1000-1000</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로116번길 19-4 1층 무니네일스튜디오</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muninail_</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>14</v>
+      </c>
+      <c r="R67" t="n">
+        <v>120</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1764595990</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1764595990</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>네일604</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>esb2967@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1327-5862</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로916번길 20 노블리치오피스텔 A동208호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail604_ss</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>1547</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>39</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1586</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1789988736</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1789988736</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>프리미엘네일 분당미금역점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>premiel__nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1362-6250</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층 203-1호 프리미엘네일</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/premiel_nail</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>4188</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>323</v>
+      </c>
+      <c r="R69" t="n">
+        <v>4511</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1105478632</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1105478632</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>네일인어스</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailinus</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>636</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>162</v>
+      </c>
+      <c r="R70" t="n">
+        <v>798</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1591004723</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1591004723</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>뮤트샵</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>kimyi95@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>031-607-0069</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 1층 134호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_muteshop</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1016</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>71</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1087</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>37883447</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37883447</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>비벨리</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1371-1908</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>532</v>
+      </c>
+      <c r="R72" t="n">
+        <v>789</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1626230048</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1626230048</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>네일드와</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1445-1545</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_de_wa</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>721</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>16</v>
+      </c>
+      <c r="R73" t="n">
+        <v>737</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1349678048</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1349678048</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>뽐내 네일</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ppomnae369@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 926 분당메트로 3층 뽐내</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_qgWrG</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>239</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>121</v>
+      </c>
+      <c r="R74" t="n">
+        <v>360</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1228519183</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228519183</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>어도어네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>gywjd2303@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1391-6431</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 8 킨스타워 3층 311호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/adorenail__?igsh=MThpanMxYXA3a2M1aA==</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>158</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>39</v>
+      </c>
+      <c r="R75" t="n">
+        <v>197</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1011483246</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1011483246</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>마틸다네일M 분당점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 3-13 3층 301호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/matilda_nailshop</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1307</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1458</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1714191610</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1714191610</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/분당_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/분당_네일샵.xlsx
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>보니타네일 더푸스프로</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>벨라뷰티</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>aqsw0111@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1327-4406</t>
+          <t>0507-1391-1078</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 지하1층</t>
+          <t>경기도 성남시 분당구 정자일로 158 백궁프라자2 3층 301호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://instagram.com/bonita_sohe_e</t>
+          <t>https://www.instagram.com/bellabeauty_nail</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -608,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -617,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>634</v>
+        <v>467</v>
       </c>
       <c r="Q2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R2" t="n">
-        <v>686</v>
+        <v>521</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1005133986</t>
+          <t>1236154271</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005133986</t>
+          <t>https://m.place.naver.com/place/1236154271</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -654,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>르에 판교점</t>
+          <t>네일발라봄</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>leehhnail@naver.com</t>
+          <t>theboni@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1466-0874</t>
+          <t>0507-1350-1712</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
+          <t>경기도 성남시 분당구 성남대로 51 B29호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/le.ehh</t>
+          <t>http://instagram.com/nailballabom</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -691,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="Q3" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1963747515</t>
+          <t>1585268852</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963747515</t>
+          <t>https://m.place.naver.com/place/1585268852</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -748,25 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더블트리</t>
+          <t>트리나네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>doubletree-lash@naver.com</t>
+          <t>treenanail@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1361-6532</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://instagram.com/doubletree_nail</t>
+          <t>http://www.instagram.com/tree_na_nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>138</v>
+        <v>1159</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="R4" t="n">
-        <v>152</v>
+        <v>1254</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>32699868</t>
+          <t>1331495059</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32699868</t>
+          <t>https://m.place.naver.com/place/1331495059</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -838,30 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>나는 너의 네일</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>조이네일</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>aa6364844@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1391-8690</t>
+          <t>0507-1352-5816</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 미금프라자 5층(다이소 바로 옆건물)</t>
+          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 2층 207호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_Jxahxkxj/friend</t>
+          <t>https://blog.naver.com/aa6364844</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -871,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -882,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -891,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>2329</v>
       </c>
       <c r="Q5" t="n">
-        <v>40</v>
+        <v>603</v>
       </c>
       <c r="R5" t="n">
-        <v>49</v>
+        <v>2932</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -906,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1174632490</t>
+          <t>37049599</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174632490</t>
+          <t>https://m.place.naver.com/place/37049599</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -928,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>뮤네일</t>
+          <t>827네일 분당미금점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mieux_by_nail@naver.com</t>
+          <t>827nail@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1474-1789</t>
+          <t>0507-1308-0827</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로925번길 19 5층 501-2호</t>
+          <t>경기도 성남시 분당구 성남대로144번길 16 1층 827네일</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fxizxcxj</t>
+          <t>http://www.instagram.com/827nail</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -976,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -985,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>233</v>
+        <v>2523</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>384</v>
       </c>
       <c r="R6" t="n">
-        <v>259</v>
+        <v>2907</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1000,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1325100624</t>
+          <t>1290037889</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325100624</t>
+          <t>https://m.place.naver.com/place/1290037889</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1022,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일보담</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1344-9616</t>
+          <t>0507-1403-3341</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로926번길 12 금탑프라자 103호</t>
+          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_bodam/?r=nametag</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1054,7 +1066,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1070,22 +1082,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>297</v>
+        <v>1035</v>
       </c>
       <c r="Q7" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="R7" t="n">
-        <v>336</v>
+        <v>1156</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1229535513</t>
+          <t>37870150</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229535513</t>
+          <t>https://m.place.naver.com/place/37870150</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1116,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일스튜디오미니</t>
+          <t>네일, 연</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>milk924@naver.com</t>
+          <t>wlsl9169@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-789-3555</t>
+          <t>0507-1400-3992</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
+          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 1층 107호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mini</t>
+          <t>https://www.instagram.com/nailyeon_?igsh=MXAxdWN4M2I1ZHRldQ==</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1173,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>315</v>
+        <v>226</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1188,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>495440903</t>
+          <t>1232273978</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/495440903</t>
+          <t>https://m.place.naver.com/place/1232273978</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1210,25 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>메이드마이네일</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>하르네일</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cxd1000@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1370-1842</t>
+          <t>0507-1305-3099</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 14 2층 208호</t>
+          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/made_mynail</t>
+          <t>https://www.instagram.com/harr__nail/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="Q9" t="n">
-        <v>158</v>
+        <v>36</v>
       </c>
       <c r="R9" t="n">
-        <v>410</v>
+        <v>310</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1278,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1528348158</t>
+          <t>2066713618</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1528348158</t>
+          <t>https://m.place.naver.com/place/2066713618</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1300,30 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>루나네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>비비네일</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>milkycoco95@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1338-3307</t>
+          <t>0507-1365-1483</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 3층 317, 318호</t>
+          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sKOPRm0f</t>
+          <t>https://pf.kakao.com/_xnCjDG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1353,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="R10" t="n">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1368,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1892992657</t>
+          <t>1505688975</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892992657</t>
+          <t>https://m.place.naver.com/place/1505688975</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1390,29 +1410,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모스네일 판교점</t>
+          <t>네일그자체</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mossnail@naver.com</t>
+          <t>wisp1205@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1317-6311</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
+          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss._.nail</t>
+          <t>https://www.instagram.com/nail_itself</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>395</v>
+        <v>168</v>
       </c>
       <c r="Q11" t="n">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="R11" t="n">
-        <v>464</v>
+        <v>191</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1462,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1816221132</t>
+          <t>2089755300</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816221132</t>
+          <t>https://m.place.naver.com/place/2089755300</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1484,34 +1500,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>레푸스 분당정자점</t>
+          <t>다나네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>refuss_bundang@naver.com</t>
+          <t>spring7503@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>031-709-8870</t>
+          <t>0507-1464-0476</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 3층 304호</t>
+          <t>경기도 성남시 분당구 성남대로 165 2층 218호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refuss_bundang</t>
+          <t>http://pf.kakao.com/_FZMiG</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1521,7 +1537,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1541,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1033</v>
+        <v>231</v>
       </c>
       <c r="Q12" t="n">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="R12" t="n">
-        <v>1164</v>
+        <v>242</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1556,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1293054958</t>
+          <t>1679531126</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293054958</t>
+          <t>https://m.place.naver.com/place/1679531126</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1635,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="Q13" t="n">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="R13" t="n">
-        <v>1663</v>
+        <v>1667</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1660,7 +1676,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1672,39 +1688,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>백프로네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>dodream8069@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1403-3341</t>
+          <t>0507-1416-7323</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
+          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_MgAwxl</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1720,22 +1736,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1031</v>
+        <v>66</v>
       </c>
       <c r="Q14" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="R14" t="n">
-        <v>1152</v>
+        <v>184</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1744,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>37870150</t>
+          <t>512636239</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870150</t>
+          <t>https://m.place.naver.com/place/512636239</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1766,29 +1782,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일팜</t>
+          <t>알로이네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nailpalm@naver.com</t>
+          <t>aloinail@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1371-5111</t>
+          <t>0507-1448-7808</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 67 금산젬월드 4층 405호</t>
+          <t>경기도 성남시 분당구 정자일로 1 코오롱트리플리스1 상가 201호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailpalm</t>
+          <t>https://blog.naver.com/aloinail</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1814,7 +1830,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1823,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>862</v>
+        <v>360</v>
       </c>
       <c r="Q15" t="n">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="R15" t="n">
-        <v>1184</v>
+        <v>418</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1838,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>37398310</t>
+          <t>1956208028</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37398310</t>
+          <t>https://m.place.naver.com/place/1956208028</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1860,34 +1876,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일, 연</t>
+          <t>러브엘네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wlsl9169@naver.com</t>
+          <t>haniii_world@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1400-3992</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 1층 107호</t>
+          <t>경기도 성남시 분당구 돌마로 47 513-1호 5층 내려서 바로 왼쪽 입니다 :)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailyeon_?igsh=MXAxdWN4M2I1ZHRldQ==</t>
+          <t>http://pf.kakao.com/_xhRYWn</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1908,7 +1920,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1917,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="R16" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1932,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1232273978</t>
+          <t>2023334466</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1232273978</t>
+          <t>https://m.place.naver.com/place/2023334466</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1954,25 +1966,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>라이티티아네일</t>
+          <t>네일인90</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>laetitia5980@naver.com</t>
+          <t>nailin90@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1331-0990</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
+          <t>경기도 성남시 분당구 성남대로925번길 16 성남분당여객자동차터미널 2층 네일인90</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/laetitia_nail_j</t>
+          <t>https://www.instagram.com/nail_in90</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2007,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>156</v>
+        <v>1155</v>
       </c>
       <c r="Q17" t="n">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="R17" t="n">
-        <v>257</v>
+        <v>1208</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2022,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1418162766</t>
+          <t>1354180497</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418162766</t>
+          <t>https://m.place.naver.com/place/1354180497</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2044,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>라모르뷰티 분당수내 본점</t>
+          <t>버베인네일 분당수내점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>lamour11@naver.com</t>
+          <t>llltwjhlll@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1465-5979</t>
+          <t>0507-1375-0335</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://instagram.com/lamour.nail</t>
+          <t>https://blog.naver.com/llltwjhlll</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2081,7 +2097,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2101,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>262</v>
+        <v>54</v>
       </c>
       <c r="Q18" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="R18" t="n">
-        <v>343</v>
+        <v>85</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2116,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1397181784</t>
+          <t>2016496556</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397181784</t>
+          <t>https://m.place.naver.com/place/2016496556</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2138,29 +2154,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>예쁘게살자</t>
+          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sukjin1125@naver.com</t>
+          <t>uijn_dd@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>031-702-9340</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 2층 예쁘게살자</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sukjin1125</t>
+          <t>https://www.instagram.com/cherryshbeauty_official</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2175,7 +2187,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2195,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>753</v>
+        <v>1079</v>
       </c>
       <c r="Q19" t="n">
-        <v>41</v>
+        <v>524</v>
       </c>
       <c r="R19" t="n">
-        <v>794</v>
+        <v>1603</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2210,17 +2222,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1221851423</t>
+          <t>36524000</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1221851423</t>
+          <t>https://m.place.naver.com/place/36524000</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2232,34 +2244,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>트리나네일</t>
+          <t>르에 판교점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>treenanail@naver.com</t>
+          <t>leehhnail@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1361-6532</t>
+          <t>0507-1466-0874</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/tree_na_nail</t>
+          <t>https://link.inpock.co.kr/le.ehh</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2269,7 +2281,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2289,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1157</v>
+        <v>107</v>
       </c>
       <c r="Q20" t="n">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="R20" t="n">
-        <v>1252</v>
+        <v>161</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2304,17 +2316,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1331495059</t>
+          <t>1963747515</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331495059</t>
+          <t>https://m.place.naver.com/place/1963747515</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2326,25 +2338,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>하낭네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>후와네일</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>kimnk980409@naver.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1322-5647</t>
+          <t>0507-1342-1792</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 73 현대 빌딩 2층 204호</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ha.nang_nail_studio?igsh=MTR4anJrZW8yN3M4eA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,13 +2395,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>582</v>
+        <v>447</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R21" t="n">
-        <v>593</v>
+        <v>465</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2394,17 +2410,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1339933062</t>
+          <t>1782262137</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1339933062</t>
+          <t>https://m.place.naver.com/place/1782262137</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2416,29 +2432,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>레푸스 판교점</t>
+          <t>뮤트샵</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>yedamcp@naver.com</t>
+          <t>kimyi95@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>031-702-8870</t>
+          <t>031-607-0069</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 1층 134호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yedamcp</t>
+          <t>http://instagram.com/_muteshop</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2453,7 +2469,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2473,13 +2489,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1373</v>
+        <v>1018</v>
       </c>
       <c r="Q22" t="n">
-        <v>567</v>
+        <v>71</v>
       </c>
       <c r="R22" t="n">
-        <v>1940</v>
+        <v>1089</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2488,17 +2504,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1710320799</t>
+          <t>37883447</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710320799</t>
+          <t>https://m.place.naver.com/place/37883447</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2510,39 +2526,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>다다네일</t>
+          <t>오로지푸스 앤 네일 스파</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>tykd2048@naver.com</t>
+          <t>orosy2020@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1466-3338</t>
+          <t>0507-1382-0859</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
+          <t>경기도 성남시 분당구 느티로 16 304호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada.nail/</t>
+          <t>https://toss.place/_lb/dnrtwwsxK</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2567,13 +2583,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>441</v>
+        <v>125</v>
       </c>
       <c r="Q23" t="n">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="R23" t="n">
-        <v>511</v>
+        <v>241</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2582,17 +2598,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>240537974</t>
+          <t>1948399629</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/240537974</t>
+          <t>https://m.place.naver.com/place/1948399629</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2604,34 +2620,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>조이네일</t>
+          <t>뮤네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>aa6364844@naver.com</t>
+          <t>mieux_by_nail@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1352-5816</t>
+          <t>0507-1474-1789</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 2층 207호</t>
+          <t>경기도 성남시 분당구 성남대로925번길 19 5층 501-2호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aa6364844</t>
+          <t>http://pf.kakao.com/_fxizxcxj</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2641,7 +2657,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2652,7 +2668,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2661,13 +2677,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2328</v>
+        <v>233</v>
       </c>
       <c r="Q24" t="n">
-        <v>603</v>
+        <v>26</v>
       </c>
       <c r="R24" t="n">
-        <v>2931</v>
+        <v>259</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2676,17 +2692,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>37049599</t>
+          <t>1325100624</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37049599</t>
+          <t>https://m.place.naver.com/place/1325100624</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2714,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>포세타네일</t>
+          <t>바이뮤즈</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>achellnet@naver.com</t>
+          <t>ynh3377@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2711,12 +2727,12 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
+          <t>경기도 성남시 분당구 정자일로 121 1층 C 10-1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfossetta</t>
+          <t>http://instagram.com/_bymuse_</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2751,13 +2767,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>86</v>
+        <v>443</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="R25" t="n">
-        <v>86</v>
+        <v>499</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2766,17 +2782,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1702940792</t>
+          <t>1198012559</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1702940792</t>
+          <t>https://m.place.naver.com/place/1198012559</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2788,29 +2804,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>반디인하우스 큐릭스 분당서현점</t>
+          <t>네일팜</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sdfw3t4@naver.com</t>
+          <t>nailpalm@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1359-2111</t>
+          <t>0507-1371-5111</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
+          <t>경기도 성남시 분당구 돌마로 67 금산젬월드 4층 405호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sdfw3t4</t>
+          <t>https://blog.naver.com/nailpalm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2845,13 +2861,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1105</v>
+        <v>862</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="R26" t="n">
-        <v>1139</v>
+        <v>1185</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2860,17 +2876,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1557758291</t>
+          <t>37398310</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557758291</t>
+          <t>https://m.place.naver.com/place/37398310</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2882,39 +2898,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>내일그리고네일</t>
+          <t>네일 조안</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>major13564@naver.com</t>
+          <t>lds9525@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1397-7847</t>
+          <t>0507-1369-6361</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 3층308호 풍림아이원플러스</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://instagram.com/tomorrow7836</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2939,13 +2955,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>517</v>
+        <v>328</v>
       </c>
       <c r="Q27" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
-        <v>564</v>
+        <v>359</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2954,17 +2970,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1389203098</t>
+          <t>1520161470</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389203098</t>
+          <t>https://m.place.naver.com/place/1520161470</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2976,29 +2992,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>솜솜네일</t>
+          <t>네일스튜디오미니</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mydbfla33@naver.com</t>
+          <t>milk924@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1416-2241</t>
+          <t>031-789-3555</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 51 포스빌 지하1층 50호 솜솜네일</t>
+          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/somsomnail_</t>
+          <t>http://www.instagram.com/nail_mini</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3033,13 +3049,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>405</v>
+        <v>321</v>
       </c>
       <c r="Q28" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="R28" t="n">
-        <v>456</v>
+        <v>354</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3048,17 +3064,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1165691375</t>
+          <t>495440903</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165691375</t>
+          <t>https://m.place.naver.com/place/495440903</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3070,25 +3086,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>포쉬네일 AK분당점</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>메이드마이네일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>joololol_@naver.com</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1416-2324</t>
+          <t>0507-1370-1842</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
+          <t>경기도 성남시 분당구 분당로53번길 14 2층 208호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_footcare</t>
+          <t>https://www.instagram.com/made_mynail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3123,13 +3143,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>683</v>
+        <v>252</v>
       </c>
       <c r="Q29" t="n">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="R29" t="n">
-        <v>741</v>
+        <v>410</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3138,17 +3158,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1692272902</t>
+          <t>1528348158</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692272902</t>
+          <t>https://m.place.naver.com/place/1528348158</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3160,39 +3180,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일 조안</t>
+          <t>뷰티네일소리 야탑점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>lds9525@naver.com</t>
+          <t>jiiz_o@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1369-6361</t>
+          <t>0507-1397-6467</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
+          <t>경기도 성남시 분당구 성남대로926번길 12 8층 801-5호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>http://instagram.com/soriii_nail</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3217,13 +3237,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="R30" t="n">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3232,17 +3252,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1520161470</t>
+          <t>1650592747</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520161470</t>
+          <t>https://m.place.naver.com/place/1650592747</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3254,25 +3274,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>루미네일 수내점</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>포쉬네일 AK분당점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>woosy0225@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1445-6255</t>
+          <t>0507-1416-2324</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로165번길 38 청구아파트 상가 601동 125호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luminail_bd</t>
+          <t>https://www.instagram.com/forsynail_footcare</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3307,13 +3331,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>522</v>
+        <v>682</v>
       </c>
       <c r="Q31" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="R31" t="n">
-        <v>551</v>
+        <v>740</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3322,17 +3346,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1065650334</t>
+          <t>1692272902</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065650334</t>
+          <t>https://m.place.naver.com/place/1692272902</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3344,29 +3368,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>버베인네일 분당수내점</t>
+          <t>네일아르떼</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>llltwjhlll@naver.com</t>
+          <t>tpfla1999@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1375-0335</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/llltwjhlll</t>
+          <t>https://www.instagram.com/__nail.arte/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3381,7 +3401,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3401,13 +3421,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>53</v>
+        <v>473</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="R32" t="n">
-        <v>84</v>
+        <v>510</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3416,17 +3436,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2016496556</t>
+          <t>1010349043</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016496556</t>
+          <t>https://m.place.naver.com/place/1010349043</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3438,25 +3458,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>바이뮤즈</t>
+          <t>띠어리네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ynh3377@naver.com</t>
+          <t>rnys11@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1314-1851</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 1층 C 10-1</t>
+          <t>경기도 성남시 분당구 돌마로 68 1층 107호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://instagram.com/_bymuse_</t>
+          <t>https://www.instagram.com/theorynail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3491,13 +3515,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>443</v>
+        <v>984</v>
       </c>
       <c r="Q33" t="n">
-        <v>56</v>
+        <v>222</v>
       </c>
       <c r="R33" t="n">
-        <v>499</v>
+        <v>1206</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3506,17 +3530,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1198012559</t>
+          <t>1230407614</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198012559</t>
+          <t>https://m.place.naver.com/place/1230407614</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3528,29 +3552,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>뷰티네일소리 야탑점</t>
+          <t>서영언니네일 앤 뷰티크 판교점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>smnewya@naver.com</t>
+          <t>seo0unnienail@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1397-6467</t>
+          <t>0507-1429-9122</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로926번길 12 8층 801-5호</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://instagram.com/soriii_nail</t>
+          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3585,13 +3609,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>300</v>
+        <v>2434</v>
       </c>
       <c r="Q34" t="n">
-        <v>43</v>
+        <v>2342</v>
       </c>
       <c r="R34" t="n">
-        <v>343</v>
+        <v>4776</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3600,17 +3624,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1650592747</t>
+          <t>1335668367</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650592747</t>
+          <t>https://m.place.naver.com/place/1335668367</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3622,34 +3646,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>다나네일</t>
+          <t>위치네일스 판교점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>spring7503@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1464-0476</t>
+          <t>031-622-7290</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 165 2층 218호</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FZMiG</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3659,7 +3683,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3670,7 +3694,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3679,13 +3703,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>230</v>
+        <v>555</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="R35" t="n">
-        <v>241</v>
+        <v>622</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3694,17 +3718,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1679531126</t>
+          <t>1458353971</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679531126</t>
+          <t>https://m.place.naver.com/place/1458353971</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3716,25 +3740,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일드잇</t>
+          <t>프리미엘네일 분당미금역점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>suzing9@naver.com</t>
+          <t>premiel__nail@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1362-6250</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로 172 2층 203호</t>
+          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층 203-1호 프리미엘네일</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://instagram.com/nailedit_mj</t>
+          <t>https://www.instagram.com/premiel_nail</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3769,13 +3797,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>194</v>
+        <v>4208</v>
       </c>
       <c r="Q36" t="n">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="R36" t="n">
-        <v>228</v>
+        <v>4531</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3784,17 +3812,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>37918491</t>
+          <t>1105478632</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37918491</t>
+          <t>https://m.place.naver.com/place/1105478632</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3834,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>러브엘네일</t>
+          <t>더블트리</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>haniii_world@naver.com</t>
+          <t>doubletree-lash@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3819,17 +3847,17 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 513-1호 5층 내려서 바로 왼쪽 입니다 :)</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhRYWn</t>
+          <t>http://instagram.com/doubletree_nail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3850,7 +3878,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3859,13 +3887,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>247</v>
+        <v>138</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R37" t="n">
-        <v>254</v>
+        <v>152</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3874,17 +3902,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2023334466</t>
+          <t>32699868</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023334466</t>
+          <t>https://m.place.naver.com/place/32699868</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3896,29 +3924,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>벨라뷰티</t>
+          <t>네일드잇</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>aqsw0111@naver.com</t>
+          <t>suzing9@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0507-1391-1078</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 158 백궁프라자2 3층 301호</t>
+          <t>경기도 성남시 분당구 내정로 172 2층 203호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bellabeauty_nail</t>
+          <t>https://instagram.com/nailedit_mj</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3944,7 +3968,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3953,13 +3977,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>467</v>
+        <v>194</v>
       </c>
       <c r="Q38" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="R38" t="n">
-        <v>521</v>
+        <v>228</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3968,17 +3992,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1236154271</t>
+          <t>37918491</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236154271</t>
+          <t>https://m.place.naver.com/place/37918491</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3990,25 +4014,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>백프로네일</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>나는 너의 네일</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>boboboc098@naver.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1416-7323</t>
+          <t>0507-1391-8690</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 5층(다이소 바로 옆건물)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_MgAwxl</t>
+          <t>https://pf.kakao.com/_Jxahxkxj/friend</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4043,13 +4071,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="Q39" t="n">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="R39" t="n">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4058,17 +4086,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>512636239</t>
+          <t>1174632490</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/512636239</t>
+          <t>https://m.place.naver.com/place/1174632490</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4080,30 +4108,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>후와네일</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>뽐내 네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ppomnae369@naver.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1342-1792</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
+          <t>경기도 성남시 분당구 성남대로 926 분당메트로 3층 뽐내</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_qgWrG</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4124,7 +4152,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4133,13 +4161,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>446</v>
+        <v>243</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="R40" t="n">
-        <v>464</v>
+        <v>364</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4148,17 +4176,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1782262137</t>
+          <t>1228519183</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782262137</t>
+          <t>https://m.place.naver.com/place/1228519183</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4170,29 +4198,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일바이라라</t>
+          <t>루나네일스튜디오</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>iam_jihye@naver.com</t>
+          <t>seoyan11@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1356-4115</t>
+          <t>0507-1338-3307</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 12 3층 317, 318호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbylala.official</t>
+          <t>https://open.kakao.com/o/sKOPRm0f</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4218,7 +4246,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4227,13 +4255,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="Q41" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="R41" t="n">
-        <v>386</v>
+        <v>204</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4242,17 +4270,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1737395332</t>
+          <t>1892992657</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737395332</t>
+          <t>https://m.place.naver.com/place/1892992657</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4264,25 +4292,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
+          <t>베베네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>uijn_dd@naver.com</t>
+          <t>kub1207@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1309-9064</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
+          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 3층 308호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cherryshbeauty_official</t>
+          <t>http://www.instagram.com/bebe.nailstudio</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4317,13 +4349,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1078</v>
+        <v>341</v>
       </c>
       <c r="Q42" t="n">
-        <v>524</v>
+        <v>26</v>
       </c>
       <c r="R42" t="n">
-        <v>1602</v>
+        <v>367</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4332,17 +4364,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>36524000</t>
+          <t>1290736362</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36524000</t>
+          <t>https://m.place.naver.com/place/1290736362</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4354,25 +4386,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>헤몬네일</t>
+          <t>비벨리</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>barbie7085055@naver.com</t>
+          <t>traveltrip11@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1371-1908</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
+          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbie7085055</t>
+          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4387,7 +4423,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4398,7 +4434,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4407,13 +4443,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1297</v>
+        <v>257</v>
       </c>
       <c r="Q43" t="n">
-        <v>718</v>
+        <v>532</v>
       </c>
       <c r="R43" t="n">
-        <v>2015</v>
+        <v>789</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4422,17 +4458,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1117775011</t>
+          <t>1626230048</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117775011</t>
+          <t>https://m.place.naver.com/place/1626230048</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4444,29 +4480,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>손수지은</t>
+          <t>에러퍼펙트 분당서현점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>iksamo@naver.com</t>
+          <t>jungwonnail@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>031-711-7615</t>
+          <t>0507-1436-5758</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 146 엠코헤리츠 1단지 101동 A128호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sonsu__</t>
+          <t>https://blog.naver.com/jungwonnail?tab=1</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4481,7 +4517,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4501,13 +4537,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>163</v>
+        <v>1952</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>639</v>
       </c>
       <c r="R44" t="n">
-        <v>188</v>
+        <v>2591</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4516,17 +4552,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1320525764</t>
+          <t>1180875815</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320525764</t>
+          <t>https://m.place.naver.com/place/1180875815</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4538,25 +4574,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>하르네일</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>네일바이라라</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>iam_jihye@naver.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1305-3099</t>
+          <t>0507-1356-4115</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/harr__nail/</t>
+          <t>https://www.instagram.com/nailbylala.official</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4591,13 +4631,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="Q45" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="R45" t="n">
-        <v>306</v>
+        <v>389</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4606,17 +4646,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2066713618</t>
+          <t>1737395332</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066713618</t>
+          <t>https://m.place.naver.com/place/1737395332</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4628,29 +4668,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>위치네일스 판교점</t>
+          <t>언니네네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>fuddl3318@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>031-622-7290</t>
+          <t>0507-1378-0725</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+          <t>경기도 성남시 분당구 성남대로 170 한국프라자 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4660,12 +4700,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4681,17 +4721,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>554</v>
+        <v>406</v>
       </c>
       <c r="Q46" t="n">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="R46" t="n">
-        <v>621</v>
+        <v>593</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4700,17 +4740,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1458353971</t>
+          <t>37554011</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458353971</t>
+          <t>https://m.place.naver.com/place/37554011</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4722,29 +4762,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일인90</t>
+          <t>유리네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>nailin90@naver.com</t>
+          <t>sfsf0525@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1331-0990</t>
+          <t>0507-1310-6342</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로925번길 16 성남분당여객자동차터미널 2층 네일인90</t>
+          <t>경기도 성남시 분당구 성남대로 51 분당포스빌 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_in90</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4754,7 +4794,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4775,17 +4815,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1153</v>
+        <v>198</v>
       </c>
       <c r="Q47" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="R47" t="n">
-        <v>1206</v>
+        <v>314</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4794,17 +4834,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1354180497</t>
+          <t>37638489</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354180497</t>
+          <t>https://m.place.naver.com/place/37638489</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4816,25 +4856,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일그자체</t>
+          <t>뮤요네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>wisp1205@naver.com</t>
+          <t>rabong1219@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1389-6160</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
+          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_itself</t>
+          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4869,13 +4913,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>166</v>
+        <v>316</v>
       </c>
       <c r="Q48" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="R48" t="n">
-        <v>189</v>
+        <v>334</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4884,17 +4928,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2089755300</t>
+          <t>1549676698</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089755300</t>
+          <t>https://m.place.naver.com/place/1549676698</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4906,29 +4950,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>827네일 분당미금점</t>
+          <t>보니타네일 더푸스프로</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>827nail@naver.com</t>
+          <t>soobromom_mijjang@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1308-0827</t>
+          <t>0507-1327-4406</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로144번길 16 1층 827네일</t>
+          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 지하1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/827nail</t>
+          <t>http://instagram.com/bonita_sohe_e</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4963,13 +5007,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2523</v>
+        <v>635</v>
       </c>
       <c r="Q49" t="n">
-        <v>383</v>
+        <v>52</v>
       </c>
       <c r="R49" t="n">
-        <v>2906</v>
+        <v>687</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4978,17 +5022,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1290037889</t>
+          <t>1005133986</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290037889</t>
+          <t>https://m.place.naver.com/place/1005133986</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5000,29 +5044,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>숨숨네일</t>
+          <t>네일다움 내성발톱 무좀 발각질 네일 문제성발 디톡스족욕</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>rnys11@naver.com</t>
+          <t>nail_dawoom@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1334-7410</t>
+          <t>0507-1483-9994</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로146번길 31-6 1층</t>
+          <t>경기도 성남시 분당구 돌마로 85 동양프라자 4층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soomsoom.nail</t>
+          <t>https://www.instagram.com/foot_naildawoom</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5057,13 +5101,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>211</v>
+        <v>632</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>391</v>
       </c>
       <c r="R50" t="n">
-        <v>223</v>
+        <v>1023</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5072,17 +5116,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1619651823</t>
+          <t>1587982343</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619651823</t>
+          <t>https://m.place.naver.com/place/1587982343</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5094,12 +5138,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일아르떼</t>
+          <t>포세타네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>tpfla1999@naver.com</t>
+          <t>achellnet@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -5107,12 +5151,12 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nail.arte/</t>
+          <t>https://www.instagram.com/nailfossetta</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5147,13 +5191,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>473</v>
+        <v>86</v>
       </c>
       <c r="Q51" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>510</v>
+        <v>86</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5162,17 +5206,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1010349043</t>
+          <t>1702940792</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010349043</t>
+          <t>https://m.place.naver.com/place/1702940792</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5184,29 +5228,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일포엠</t>
+          <t>반디인하우스 큐릭스 분당서현점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>sahsar@naver.com</t>
+          <t>sdfw3t4@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1381-1685</t>
+          <t>0507-1359-2111</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 295 대림아크로텔 c동 129호</t>
+          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_poem</t>
+          <t>https://blog.naver.com/sdfw3t4</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5221,7 +5265,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5241,13 +5285,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>75</v>
+        <v>1105</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="R52" t="n">
-        <v>96</v>
+        <v>1139</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5256,17 +5300,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1373998196</t>
+          <t>1557758291</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373998196</t>
+          <t>https://m.place.naver.com/place/1557758291</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5278,25 +5322,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>띠어리네일</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>네일보담</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1314-1851</t>
+          <t>0507-1344-9616</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 68 1층 107호</t>
+          <t>경기도 성남시 분당구 성남대로926번길 12 금탑프라자 103호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/theorynail</t>
+          <t>https://www.instagram.com/nail_bodam/?r=nametag</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5322,7 +5370,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5331,13 +5379,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>983</v>
+        <v>297</v>
       </c>
       <c r="Q53" t="n">
-        <v>222</v>
+        <v>39</v>
       </c>
       <c r="R53" t="n">
-        <v>1205</v>
+        <v>336</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5346,17 +5394,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1230407614</t>
+          <t>1229535513</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230407614</t>
+          <t>https://m.place.naver.com/place/1229535513</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5368,29 +5416,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>포쉬네일 판교아브뉴프랑점</t>
+          <t>레푸스 분당정자점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>silentforest_studio@naver.com</t>
+          <t>refuss_bundang@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>031-603-3011</t>
+          <t>031-709-8870</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 3층 304호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/refuss_bundang</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5400,12 +5448,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5416,22 +5464,22 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>201</v>
+        <v>1038</v>
       </c>
       <c r="Q54" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R54" t="n">
-        <v>333</v>
+        <v>1169</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5440,17 +5488,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>38258395</t>
+          <t>1293054958</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38258395</t>
+          <t>https://m.place.naver.com/place/1293054958</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5462,29 +5510,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>쏘굿네일 분당미금점</t>
+          <t>헤몬네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sohyun1304@naver.com</t>
+          <t>barbie7085055@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0507-1427-2394</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 73 우방코아 2층 211호</t>
+          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/sso_good_nail</t>
+          <t>https://blog.naver.com/barbie7085055</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5499,7 +5543,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5510,7 +5554,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5519,13 +5563,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1410</v>
+        <v>1299</v>
       </c>
       <c r="Q55" t="n">
-        <v>390</v>
+        <v>718</v>
       </c>
       <c r="R55" t="n">
-        <v>1800</v>
+        <v>2017</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5534,17 +5578,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1235289874</t>
+          <t>1117775011</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1235289874</t>
+          <t>https://m.place.naver.com/place/1117775011</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5556,29 +5600,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일오브윤 분당점</t>
+          <t>솜솜네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>o___o373@naver.com</t>
+          <t>mydbfla33@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1366-7390</t>
+          <t>0507-1416-2241</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
+          <t>경기도 성남시 분당구 성남대로 51 포스빌 지하1층 50호 솜솜네일</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/o___o373</t>
+          <t>https://www.instagram.com/somsomnail_</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5593,7 +5637,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5613,13 +5657,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1158</v>
+        <v>405</v>
       </c>
       <c r="Q56" t="n">
-        <v>916</v>
+        <v>51</v>
       </c>
       <c r="R56" t="n">
-        <v>2074</v>
+        <v>456</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5628,17 +5672,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1300308336</t>
+          <t>1165691375</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300308336</t>
+          <t>https://m.place.naver.com/place/1165691375</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5650,29 +5694,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>에러퍼펙트 분당서현점</t>
+          <t>다다네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jungwonnail@naver.com</t>
+          <t>tykd2048@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1436-5758</t>
+          <t>0507-1466-3338</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+          <t>https://www.instagram.com/dada.nail/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5687,7 +5731,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5707,13 +5751,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1950</v>
+        <v>441</v>
       </c>
       <c r="Q57" t="n">
-        <v>639</v>
+        <v>70</v>
       </c>
       <c r="R57" t="n">
-        <v>2589</v>
+        <v>511</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5722,17 +5766,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1180875815</t>
+          <t>240537974</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180875815</t>
+          <t>https://m.place.naver.com/place/240537974</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5744,39 +5788,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>온들네일 분당정자점</t>
+          <t>포쉬네일 판교아브뉴프랑점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>lovmaria@naver.com</t>
+          <t>silentforest_studio@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1443-7794</t>
+          <t>031-603-3011</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 67 1층 104호</t>
+          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkxaKin</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5792,22 +5836,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="R58" t="n">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5816,17 +5860,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2085728870</t>
+          <t>38258395</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2085728870</t>
+          <t>https://m.place.naver.com/place/38258395</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5838,29 +5882,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>안녕,예쁜손</t>
+          <t>언투네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>bbolm@naver.com</t>
+          <t>loveili@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1429-8836</t>
+          <t>0507-1346-4298</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
+          <t>경기도 성남시 분당구 방아로 25 지하1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hello_jininail</t>
+          <t>https://www.instagram.com/untonail_?igsh=MXI0ejlrc3FkOGNvcA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5895,13 +5939,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>885</v>
+        <v>90</v>
       </c>
       <c r="Q59" t="n">
-        <v>258</v>
+        <v>8</v>
       </c>
       <c r="R59" t="n">
-        <v>1143</v>
+        <v>98</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5910,17 +5954,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>13399185</t>
+          <t>1449565892</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13399185</t>
+          <t>https://m.place.naver.com/place/1449565892</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5932,29 +5976,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>서영언니네일 앤 뷰티크 판교점</t>
+          <t>네일604</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>seo0unnienail@naver.com</t>
+          <t>esb2967@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1429-9122</t>
+          <t>0507-1327-5862</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+          <t>경기도 성남시 분당구 성남대로916번길 20 노블리치오피스텔 A동208호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+          <t>https://www.instagram.com/nail604_ss</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5989,13 +6033,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2434</v>
+        <v>1552</v>
       </c>
       <c r="Q60" t="n">
-        <v>2341</v>
+        <v>39</v>
       </c>
       <c r="R60" t="n">
-        <v>4775</v>
+        <v>1591</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6004,17 +6048,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1335668367</t>
+          <t>1789988736</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335668367</t>
+          <t>https://m.place.naver.com/place/1789988736</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6026,29 +6070,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일발라봄</t>
+          <t>라이티티아네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>yuri831211@naver.com</t>
+          <t>laetitia5980@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0507-1350-1712</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 51 B29호</t>
+          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailballabom</t>
+          <t>https://www.instagram.com/laetitia_nail_j</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6083,13 +6123,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="R61" t="n">
-        <v>41</v>
+        <v>257</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6098,17 +6138,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1585268852</t>
+          <t>1418162766</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1585268852</t>
+          <t>https://m.place.naver.com/place/1418162766</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6120,30 +6160,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>비비네일</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>네일드와</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>hellomj18@naver.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1365-1483</t>
+          <t>0507-1445-1545</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnCjDG</t>
+          <t>https://www.instagram.com/nail_de_wa</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6164,7 +6208,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6173,13 +6217,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>107</v>
+        <v>721</v>
       </c>
       <c r="Q62" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="R62" t="n">
-        <v>145</v>
+        <v>737</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6188,17 +6232,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1505688975</t>
+          <t>1349678048</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505688975</t>
+          <t>https://m.place.naver.com/place/1349678048</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6210,34 +6254,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일다움 내성발톱 무좀 발각질 네일 문제성발 디톡스족욕</t>
+          <t>온들네일 분당정자점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>nail_dawoom@naver.com</t>
+          <t>lovmaria@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1483-9994</t>
+          <t>0507-1443-7794</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 85 동양프라자 4층</t>
+          <t>경기도 성남시 분당구 느티로 67 1층 104호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/foot_naildawoom</t>
+          <t>http://pf.kakao.com/_xkxaKin</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6258,7 +6302,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6267,13 +6311,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>630</v>
+        <v>54</v>
       </c>
       <c r="Q63" t="n">
-        <v>391</v>
+        <v>26</v>
       </c>
       <c r="R63" t="n">
-        <v>1021</v>
+        <v>80</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6282,17 +6326,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1587982343</t>
+          <t>2085728870</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1587982343</t>
+          <t>https://m.place.naver.com/place/2085728870</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6304,29 +6348,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>뮤요네일</t>
+          <t>마틸다네일M 분당점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>rabong1219@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0507-1389-6160</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-13 3층 301호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/matilda_nailshop</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6361,13 +6401,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>306</v>
+        <v>149</v>
       </c>
       <c r="Q64" t="n">
-        <v>18</v>
+        <v>1307</v>
       </c>
       <c r="R64" t="n">
-        <v>324</v>
+        <v>1456</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6376,17 +6416,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1549676698</t>
+          <t>1714191610</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549676698</t>
+          <t>https://m.place.naver.com/place/1714191610</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6398,35 +6438,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>오로지푸스 앤 네일 스파</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>네일인어스</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>gywjd2303@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0507-1382-0859</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 304호</t>
+          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/dnrtwwsxK</t>
+          <t>https://www.instagram.com/nailinus</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6451,13 +6491,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>125</v>
+        <v>636</v>
       </c>
       <c r="Q65" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="R65" t="n">
-        <v>241</v>
+        <v>798</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6466,17 +6506,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1948399629</t>
+          <t>1591004723</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948399629</t>
+          <t>https://m.place.naver.com/place/1591004723</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6488,29 +6528,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>베베네일</t>
+          <t>레푸스 판교점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>kub1207@naver.com</t>
+          <t>yedamcp@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1309-9064</t>
+          <t>031-702-8870</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 3층 308호</t>
+          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/bebe.nailstudio</t>
+          <t>https://blog.naver.com/yedamcp</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6525,7 +6565,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6545,13 +6585,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>341</v>
+        <v>1378</v>
       </c>
       <c r="Q66" t="n">
-        <v>26</v>
+        <v>567</v>
       </c>
       <c r="R66" t="n">
-        <v>367</v>
+        <v>1945</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6560,17 +6600,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1290736362</t>
+          <t>1710320799</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290736362</t>
+          <t>https://m.place.naver.com/place/1710320799</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6582,25 +6622,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>무니네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>라온네일클리닉 판교 본점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sungunara226@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>032-1000-1000</t>
+          <t>0507-1418-3314</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로116번길 19-4 1층 무니네일스튜디오</t>
+          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muninail_</t>
+          <t>https://blog.naver.com/sungunara226</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6615,7 +6659,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6635,13 +6679,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>283</v>
       </c>
       <c r="R67" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6650,17 +6694,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1764595990</t>
+          <t>1137420501</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764595990</t>
+          <t>https://m.place.naver.com/place/1137420501</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6672,29 +6716,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일604</t>
+          <t>예쁘게살자</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>esb2967@naver.com</t>
+          <t>sukjin1125@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1327-5862</t>
+          <t>031-702-9340</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 20 노블리치오피스텔 A동208호</t>
+          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 2층 예쁘게살자</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail604_ss</t>
+          <t>https://blog.naver.com/sukjin1125</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6709,7 +6753,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6729,13 +6773,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1547</v>
+        <v>753</v>
       </c>
       <c r="Q68" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R68" t="n">
-        <v>1586</v>
+        <v>794</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6744,17 +6788,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1789988736</t>
+          <t>1221851423</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1789988736</t>
+          <t>https://m.place.naver.com/place/1221851423</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6766,29 +6810,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>프리미엘네일 분당미금역점</t>
+          <t>네일오브윤 분당점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>premiel__nail@naver.com</t>
+          <t>o___o373@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1362-6250</t>
+          <t>0507-1366-7390</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층 203-1호 프리미엘네일</t>
+          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/premiel_nail</t>
+          <t>https://blog.naver.com/o___o373</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6803,7 +6847,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6823,13 +6867,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>4188</v>
+        <v>1171</v>
       </c>
       <c r="Q69" t="n">
-        <v>323</v>
+        <v>920</v>
       </c>
       <c r="R69" t="n">
-        <v>4511</v>
+        <v>2091</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6838,17 +6882,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1105478632</t>
+          <t>1300308336</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105478632</t>
+          <t>https://m.place.naver.com/place/1300308336</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6860,21 +6904,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일인어스</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>어도어네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>gywjd2303@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1391-6431</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 8 킨스타워 3층 311호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailinus</t>
+          <t>https://www.instagram.com/adorenail__?igsh=MThpanMxYXA3a2M1aA==</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6909,13 +6961,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>636</v>
+        <v>158</v>
       </c>
       <c r="Q70" t="n">
-        <v>162</v>
+        <v>39</v>
       </c>
       <c r="R70" t="n">
-        <v>798</v>
+        <v>197</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6924,17 +6976,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1591004723</t>
+          <t>1011483246</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591004723</t>
+          <t>https://m.place.naver.com/place/1011483246</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6946,29 +6998,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>뮤트샵</t>
+          <t>네일포엠</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>kimyi95@naver.com</t>
+          <t>sahsar@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>031-607-0069</t>
+          <t>0507-1381-1685</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 1층 134호</t>
+          <t>경기도 성남시 분당구 성남대로 295 대림아크로텔 c동 129호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://instagram.com/_muteshop</t>
+          <t>http://instagram.com/nail_poem</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7003,13 +7055,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1016</v>
+        <v>77</v>
       </c>
       <c r="Q71" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="R71" t="n">
-        <v>1087</v>
+        <v>98</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7018,17 +7070,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>37883447</t>
+          <t>1373998196</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37883447</t>
+          <t>https://m.place.naver.com/place/1373998196</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7040,25 +7092,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>비벨리</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>쏘굿네일 분당미금점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sohyun1304@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1371-1908</t>
+          <t>0507-1427-2394</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+          <t>경기도 성남시 분당구 돌마로 73 우방코아 2층 211호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+          <t>http://www.instagram.com/sso_good_nail</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7093,13 +7149,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>257</v>
+        <v>1410</v>
       </c>
       <c r="Q72" t="n">
-        <v>532</v>
+        <v>390</v>
       </c>
       <c r="R72" t="n">
-        <v>789</v>
+        <v>1800</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7108,17 +7164,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1626230048</t>
+          <t>1235289874</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626230048</t>
+          <t>https://m.place.naver.com/place/1235289874</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7130,25 +7186,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일드와</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>무니네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>efjekkk0888@naver.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1445-1545</t>
+          <t>032-1000-1000</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
+          <t>경기도 성남시 분당구 황새울로116번길 19-4 1층 무니네일스튜디오</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_wa</t>
+          <t>https://www.instagram.com/muninail_</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7183,13 +7243,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>721</v>
+        <v>106</v>
       </c>
       <c r="Q73" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R73" t="n">
-        <v>737</v>
+        <v>120</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7198,17 +7258,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1349678048</t>
+          <t>1764595990</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349678048</t>
+          <t>https://m.place.naver.com/place/1764595990</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7220,30 +7280,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>뽐내 네일</t>
+          <t>안녕,예쁜손</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ppomnae369@naver.com</t>
+          <t>bbolm@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1429-8836</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 926 분당메트로 3층 뽐내</t>
+          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qgWrG</t>
+          <t>http://www.instagram.com/hello_jininail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7264,7 +7328,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7273,13 +7337,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>239</v>
+        <v>885</v>
       </c>
       <c r="Q74" t="n">
-        <v>121</v>
+        <v>258</v>
       </c>
       <c r="R74" t="n">
-        <v>360</v>
+        <v>1143</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7288,17 +7352,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1228519183</t>
+          <t>13399185</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228519183</t>
+          <t>https://m.place.naver.com/place/13399185</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7310,29 +7374,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>어도어네일스튜디오</t>
+          <t>라모르뷰티 분당수내 본점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>gywjd2303@naver.com</t>
+          <t>lamour11@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1391-6431</t>
+          <t>0507-1465-5979</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 8 킨스타워 3층 311호</t>
+          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/adorenail__?igsh=MThpanMxYXA3a2M1aA==</t>
+          <t>http://instagram.com/lamour.nail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7367,13 +7431,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="Q75" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="R75" t="n">
-        <v>197</v>
+        <v>345</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7382,17 +7446,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1011483246</t>
+          <t>1397181784</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1011483246</t>
+          <t>https://m.place.naver.com/place/1397181784</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7404,21 +7468,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>마틸다네일M 분당점</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>모스네일 판교점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>mossnail@naver.com</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1317-6311</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-13 3층 301호</t>
+          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/matilda_nailshop</t>
+          <t>https://www.instagram.com/moss._.nail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7453,13 +7525,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>151</v>
+        <v>395</v>
       </c>
       <c r="Q76" t="n">
-        <v>1307</v>
+        <v>69</v>
       </c>
       <c r="R76" t="n">
-        <v>1458</v>
+        <v>464</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7468,17 +7540,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1714191610</t>
+          <t>1816221132</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1714191610</t>
+          <t>https://m.place.naver.com/place/1816221132</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/분당_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/분당_네일샵.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V76"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>벨라뷰티</t>
+          <t>후와네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>aqsw0111@naver.com</t>
+          <t>kimnk980409@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1391-1078</t>
+          <t>0507-1342-1792</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 158 백궁프라자2 3층 301호</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bellabeauty_nail</t>
+          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="Q2" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>521</v>
+        <v>465</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1236154271</t>
+          <t>1782262137</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236154271</t>
+          <t>https://m.place.naver.com/place/1782262137</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일발라봄</t>
+          <t>포쉬네일 AK분당점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>theboni@naver.com</t>
+          <t>woosy0225@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1350-1712</t>
+          <t>0507-1416-2324</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 51 B29호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailballabom</t>
+          <t>https://www.instagram.com/forsynail_footcare</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>27</v>
+        <v>682</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="R3" t="n">
-        <v>41</v>
+        <v>741</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1585268852</t>
+          <t>1692272902</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1585268852</t>
+          <t>https://m.place.naver.com/place/1692272902</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>트리나네일</t>
+          <t>레푸스 분당정자점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>treenanail@naver.com</t>
+          <t>refuss_bundang@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1361-6532</t>
+          <t>031-709-8870</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 3층 304호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/tree_na_nail</t>
+          <t>https://blog.naver.com/refuss_bundang</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1159</v>
+        <v>1038</v>
       </c>
       <c r="Q4" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="R4" t="n">
-        <v>1254</v>
+        <v>1169</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1331495059</t>
+          <t>1293054958</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331495059</t>
+          <t>https://m.place.naver.com/place/1293054958</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>조이네일</t>
+          <t>베베네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>aa6364844@naver.com</t>
+          <t>kub1207@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1352-5816</t>
+          <t>0507-1309-9064</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 2층 207호</t>
+          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 3층 308호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aa6364844</t>
+          <t>http://www.instagram.com/bebe.nailstudio</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2329</v>
+        <v>342</v>
       </c>
       <c r="Q5" t="n">
-        <v>603</v>
+        <v>26</v>
       </c>
       <c r="R5" t="n">
-        <v>2932</v>
+        <v>368</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37049599</t>
+          <t>1290736362</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37049599</t>
+          <t>https://m.place.naver.com/place/1290736362</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>827네일 분당미금점</t>
+          <t>서영언니네일 앤 뷰티크 판교점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>827nail@naver.com</t>
+          <t>seo0unnienail@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1308-0827</t>
+          <t>0507-1429-9122</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로144번길 16 1층 827네일</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/827nail</t>
+          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2523</v>
+        <v>2434</v>
       </c>
       <c r="Q6" t="n">
-        <v>384</v>
+        <v>2342</v>
       </c>
       <c r="R6" t="n">
-        <v>2907</v>
+        <v>4776</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1290037889</t>
+          <t>1335668367</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290037889</t>
+          <t>https://m.place.naver.com/place/1335668367</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>어도어네일스튜디오</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>gywjd2303@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1403-3341</t>
+          <t>0507-1391-6431</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 8 킨스타워 3층 311호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/adorenail__?igsh=MThpanMxYXA3a2M1aA==</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1035</v>
+        <v>158</v>
       </c>
       <c r="Q7" t="n">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>1156</v>
+        <v>197</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37870150</t>
+          <t>1011483246</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870150</t>
+          <t>https://m.place.naver.com/place/1011483246</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일, 연</t>
+          <t>예쁘게살자</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wlsl9169@naver.com</t>
+          <t>sukjin1125@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1400-3992</t>
+          <t>031-702-9340</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 1층 107호</t>
+          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 2층 예쁘게살자</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailyeon_?igsh=MXAxdWN4M2I1ZHRldQ==</t>
+          <t>https://blog.naver.com/sukjin1125</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>226</v>
+        <v>753</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="R8" t="n">
-        <v>256</v>
+        <v>794</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1232273978</t>
+          <t>1221851423</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1232273978</t>
+          <t>https://m.place.naver.com/place/1221851423</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>하르네일</t>
+          <t>네일드와</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cxd1000@naver.com</t>
+          <t>hellomj18@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1305-3099</t>
+          <t>0507-1445-1545</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/harr__nail/</t>
+          <t>https://www.instagram.com/nail_de_wa</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>274</v>
+        <v>721</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="R9" t="n">
-        <v>310</v>
+        <v>737</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2066713618</t>
+          <t>1349678048</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066713618</t>
+          <t>https://m.place.naver.com/place/1349678048</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,39 +1316,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>언니네네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>fuddl3318@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1365-1483</t>
+          <t>0507-1378-0725</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
+          <t>경기도 성남시 분당구 성남대로 170 한국프라자 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnCjDG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1364,22 +1364,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>107</v>
+        <v>406</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>187</v>
       </c>
       <c r="R10" t="n">
-        <v>145</v>
+        <v>593</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1505688975</t>
+          <t>37554011</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505688975</t>
+          <t>https://m.place.naver.com/place/37554011</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,25 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일그자체</t>
+          <t>네일팜</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wisp1205@naver.com</t>
+          <t>nailpalm@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1371-5111</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
+          <t>경기도 성남시 분당구 돌마로 67 금산젬월드 4층 405호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_itself</t>
+          <t>https://blog.naver.com/nailpalm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1443,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>168</v>
+        <v>862</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>323</v>
       </c>
       <c r="R11" t="n">
-        <v>191</v>
+        <v>1185</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2089755300</t>
+          <t>37398310</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089755300</t>
+          <t>https://m.place.naver.com/place/37398310</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1500,34 +1504,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>다나네일</t>
+          <t>네일보담</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>spring7503@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1464-0476</t>
+          <t>0507-1344-9616</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 165 2층 218호</t>
+          <t>경기도 성남시 분당구 성남대로926번길 12 금탑프라자 103호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FZMiG</t>
+          <t>https://www.instagram.com/nail_bodam/?r=nametag</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1557,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>231</v>
+        <v>297</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="R12" t="n">
-        <v>242</v>
+        <v>336</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1679531126</t>
+          <t>1229535513</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679531126</t>
+          <t>https://m.place.naver.com/place/1229535513</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1594,34 +1598,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>비온빛 네일브라운 분당미금점</t>
+          <t>르에 판교점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nailb1212@naver.com</t>
+          <t>leehhnail@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1407-1279</t>
+          <t>0507-1466-0874</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 52 2층 203호</t>
+          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbrown_</t>
+          <t>https://link.inpock.co.kr/le.ehh</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1631,7 +1635,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1651,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>882</v>
+        <v>107</v>
       </c>
       <c r="Q13" t="n">
-        <v>785</v>
+        <v>55</v>
       </c>
       <c r="R13" t="n">
-        <v>1667</v>
+        <v>162</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,12 +1670,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1647015847</t>
+          <t>1963747515</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1647015847</t>
+          <t>https://m.place.naver.com/place/1963747515</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1688,34 +1692,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>백프로네일</t>
+          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dodream8069@naver.com</t>
+          <t>uijn_dd@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1416-7323</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_MgAwxl</t>
+          <t>https://www.instagram.com/cherryshbeauty_official</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1736,7 +1736,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>66</v>
+        <v>1079</v>
       </c>
       <c r="Q14" t="n">
-        <v>118</v>
+        <v>524</v>
       </c>
       <c r="R14" t="n">
-        <v>184</v>
+        <v>1603</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>512636239</t>
+          <t>36524000</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/512636239</t>
+          <t>https://m.place.naver.com/place/36524000</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1782,34 +1782,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>알로이네일</t>
+          <t>러브엘네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>aloinail@naver.com</t>
+          <t>haniii_world@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1448-7808</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 1 코오롱트리플리스1 상가 201호</t>
+          <t>경기도 성남시 분당구 돌마로 47 513-1호 5층 내려서 바로 왼쪽 입니다 :)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aloinail</t>
+          <t>http://pf.kakao.com/_xhRYWn</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1819,7 +1815,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1839,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>360</v>
+        <v>246</v>
       </c>
       <c r="Q15" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>418</v>
+        <v>253</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,12 +1850,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1956208028</t>
+          <t>2023334466</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956208028</t>
+          <t>https://m.place.naver.com/place/2023334466</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1876,30 +1872,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>러브엘네일</t>
+          <t>프리미엘네일 분당미금역점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>haniii_world@naver.com</t>
+          <t>premiel__nail@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1362-6250</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 513-1호 5층 내려서 바로 왼쪽 입니다 :)</t>
+          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층 203-1호 프리미엘네일</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhRYWn</t>
+          <t>https://www.instagram.com/premiel_nail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1920,7 +1920,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>246</v>
+        <v>4213</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="R16" t="n">
-        <v>253</v>
+        <v>4537</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2023334466</t>
+          <t>1105478632</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023334466</t>
+          <t>https://m.place.naver.com/place/1105478632</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1966,29 +1966,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일인90</t>
+          <t>네일, 연</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nailin90@naver.com</t>
+          <t>wlsl9169@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1331-0990</t>
+          <t>0507-1400-3992</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로925번길 16 성남분당여객자동차터미널 2층 네일인90</t>
+          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 1층 107호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_in90</t>
+          <t>https://www.instagram.com/nailyeon_?igsh=MXAxdWN4M2I1ZHRldQ==</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1155</v>
+        <v>226</v>
       </c>
       <c r="Q17" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="R17" t="n">
-        <v>1208</v>
+        <v>256</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1354180497</t>
+          <t>1232273978</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354180497</t>
+          <t>https://m.place.naver.com/place/1232273978</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2060,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>버베인네일 분당수내점</t>
+          <t>827네일 분당미금점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>llltwjhlll@naver.com</t>
+          <t>827nail@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1375-0335</t>
+          <t>0507-1308-0827</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
+          <t>경기도 성남시 분당구 성남대로144번길 16 1층 827네일</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/llltwjhlll</t>
+          <t>http://www.instagram.com/827nail</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>54</v>
+        <v>2524</v>
       </c>
       <c r="Q18" t="n">
-        <v>31</v>
+        <v>384</v>
       </c>
       <c r="R18" t="n">
-        <v>85</v>
+        <v>2908</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2016496556</t>
+          <t>1290037889</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016496556</t>
+          <t>https://m.place.naver.com/place/1290037889</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2154,25 +2154,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
+          <t>유리네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>uijn_dd@naver.com</t>
+          <t>sfsf0525@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1310-6342</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
+          <t>경기도 성남시 분당구 성남대로 51 분당포스빌 1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cherryshbeauty_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2182,7 +2186,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2203,17 +2207,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1079</v>
+        <v>198</v>
       </c>
       <c r="Q19" t="n">
-        <v>524</v>
+        <v>116</v>
       </c>
       <c r="R19" t="n">
-        <v>1603</v>
+        <v>314</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,12 +2226,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36524000</t>
+          <t>37638489</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36524000</t>
+          <t>https://m.place.naver.com/place/37638489</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2244,34 +2248,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>르에 판교점</t>
+          <t>벨라뷰티</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>leehhnail@naver.com</t>
+          <t>aqsw0111@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1466-0874</t>
+          <t>0507-1391-1078</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
+          <t>경기도 성남시 분당구 정자일로 158 백궁프라자2 3층 301호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/le.ehh</t>
+          <t>https://www.instagram.com/bellabeauty_nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2281,7 +2285,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2292,7 +2296,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2301,13 +2305,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>107</v>
+        <v>467</v>
       </c>
       <c r="Q20" t="n">
         <v>54</v>
       </c>
       <c r="R20" t="n">
-        <v>161</v>
+        <v>521</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,12 +2320,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1963747515</t>
+          <t>1236154271</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963747515</t>
+          <t>https://m.place.naver.com/place/1236154271</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2338,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>후와네일</t>
+          <t>레푸스 판교점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kimnk980409@naver.com</t>
+          <t>yedamcp@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1342-1792</t>
+          <t>031-702-8870</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
+          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/yedamcp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2375,7 +2379,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2395,13 +2399,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>447</v>
+        <v>1378</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>567</v>
       </c>
       <c r="R21" t="n">
-        <v>465</v>
+        <v>1945</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,12 +2414,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1782262137</t>
+          <t>1710320799</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782262137</t>
+          <t>https://m.place.naver.com/place/1710320799</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2432,29 +2436,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>뮤트샵</t>
+          <t>더블트리</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kimyi95@naver.com</t>
+          <t>doubletree-lash@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>031-607-0069</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 1층 134호</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://instagram.com/_muteshop</t>
+          <t>http://instagram.com/doubletree_nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1018</v>
+        <v>138</v>
       </c>
       <c r="Q22" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="R22" t="n">
-        <v>1089</v>
+        <v>152</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>37883447</t>
+          <t>32699868</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37883447</t>
+          <t>https://m.place.naver.com/place/32699868</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2526,44 +2526,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>오로지푸스 앤 네일 스파</t>
+          <t>알로이네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>orosy2020@naver.com</t>
+          <t>aloinail@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1382-0859</t>
+          <t>0507-1448-7808</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 304호</t>
+          <t>경기도 성남시 분당구 정자일로 1 코오롱트리플리스1 상가 201호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/dnrtwwsxK</t>
+          <t>https://blog.naver.com/aloinail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2574,7 +2574,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>125</v>
+        <v>360</v>
       </c>
       <c r="Q23" t="n">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="R23" t="n">
-        <v>241</v>
+        <v>418</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1948399629</t>
+          <t>1956208028</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948399629</t>
+          <t>https://m.place.naver.com/place/1956208028</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2620,34 +2620,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>뮤네일</t>
+          <t>솜솜네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mieux_by_nail@naver.com</t>
+          <t>mydbfla33@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1474-1789</t>
+          <t>0507-1416-2241</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로925번길 19 5층 501-2호</t>
+          <t>경기도 성남시 분당구 성남대로 51 포스빌 지하1층 50호 솜솜네일</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fxizxcxj</t>
+          <t>https://www.instagram.com/somsomnail_</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2668,7 +2668,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>233</v>
+        <v>405</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="R24" t="n">
-        <v>259</v>
+        <v>456</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1325100624</t>
+          <t>1165691375</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325100624</t>
+          <t>https://m.place.naver.com/place/1165691375</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>바이뮤즈</t>
+          <t>네일인어스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ynh3377@naver.com</t>
+          <t>gywjd2303@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2727,12 +2727,12 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 1층 C 10-1</t>
+          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://instagram.com/_bymuse_</t>
+          <t>https://www.instagram.com/nailinus</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>443</v>
+        <v>635</v>
       </c>
       <c r="Q25" t="n">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="R25" t="n">
-        <v>499</v>
+        <v>797</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1198012559</t>
+          <t>1591004723</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198012559</t>
+          <t>https://m.place.naver.com/place/1591004723</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2804,29 +2804,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일팜</t>
+          <t>하낭네일스튜디오</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nailpalm@naver.com</t>
+          <t>senniverse@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1371-5111</t>
+          <t>0507-1322-5647</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 67 금산젬월드 4층 405호</t>
+          <t>경기도 성남시 분당구 느티로 73 현대 빌딩 2층 204호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailpalm</t>
+          <t>https://www.instagram.com/ha.nang_nail_studio?igsh=MTR4anJrZW8yN3M4eA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>862</v>
+        <v>584</v>
       </c>
       <c r="Q26" t="n">
-        <v>323</v>
+        <v>11</v>
       </c>
       <c r="R26" t="n">
-        <v>1185</v>
+        <v>595</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,12 +2876,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>37398310</t>
+          <t>1339933062</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37398310</t>
+          <t>https://m.place.naver.com/place/1339933062</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2898,39 +2898,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일 조안</t>
+          <t>네일드잇</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>lds9525@naver.com</t>
+          <t>tudougunniang@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0507-1369-6361</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
+          <t>경기도 성남시 분당구 내정로 172 2층 203호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>https://instagram.com/nailedit_mj</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2955,13 +2951,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>328</v>
+        <v>194</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R27" t="n">
-        <v>359</v>
+        <v>228</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,12 +2966,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1520161470</t>
+          <t>37918491</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520161470</t>
+          <t>https://m.place.naver.com/place/37918491</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2992,29 +2988,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일스튜디오미니</t>
+          <t>모스네일 판교점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>milk924@naver.com</t>
+          <t>mossnail@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>031-789-3555</t>
+          <t>0507-1317-6311</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
+          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mini</t>
+          <t>https://www.instagram.com/moss._.nail</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3049,13 +3045,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>321</v>
+        <v>396</v>
       </c>
       <c r="Q28" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="R28" t="n">
-        <v>354</v>
+        <v>465</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,12 +3060,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>495440903</t>
+          <t>1816221132</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/495440903</t>
+          <t>https://m.place.naver.com/place/1816221132</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3086,34 +3082,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>메이드마이네일</t>
+          <t>뽐내 네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>joololol_@naver.com</t>
+          <t>ppomnae369@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1370-1842</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 14 2층 208호</t>
+          <t>경기도 성남시 분당구 성남대로 926 분당메트로 3층 뽐내</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/made_mynail</t>
+          <t>http://pf.kakao.com/_qgWrG</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3134,7 +3126,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3143,13 +3135,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="Q29" t="n">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="R29" t="n">
-        <v>410</v>
+        <v>364</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3158,12 +3150,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1528348158</t>
+          <t>1228519183</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1528348158</t>
+          <t>https://m.place.naver.com/place/1228519183</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3180,29 +3172,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>뷰티네일소리 야탑점</t>
+          <t>반디인하우스 큐릭스 분당서현점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jiiz_o@naver.com</t>
+          <t>sdfw3t4@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1397-6467</t>
+          <t>0507-1359-2111</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로926번길 12 8층 801-5호</t>
+          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://instagram.com/soriii_nail</t>
+          <t>https://blog.naver.com/sdfw3t4</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3217,7 +3209,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3237,13 +3229,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>302</v>
+        <v>1105</v>
       </c>
       <c r="Q30" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="R30" t="n">
-        <v>345</v>
+        <v>1139</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3252,12 +3244,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1650592747</t>
+          <t>1557758291</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650592747</t>
+          <t>https://m.place.naver.com/place/1557758291</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3274,29 +3266,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>포쉬네일 AK분당점</t>
+          <t>네일다움 내성발톱 무좀 발각질 네일 문제성발 디톡스족욕</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>woosy0225@naver.com</t>
+          <t>nail_dawoom@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1416-2324</t>
+          <t>0507-1483-9994</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
+          <t>경기도 성남시 분당구 돌마로 85 동양프라자 4층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_footcare</t>
+          <t>https://www.instagram.com/foot_naildawoom</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3331,13 +3323,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>682</v>
+        <v>632</v>
       </c>
       <c r="Q31" t="n">
-        <v>58</v>
+        <v>391</v>
       </c>
       <c r="R31" t="n">
-        <v>740</v>
+        <v>1023</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3346,12 +3338,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1692272902</t>
+          <t>1587982343</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692272902</t>
+          <t>https://m.place.naver.com/place/1587982343</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3368,25 +3360,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일아르떼</t>
+          <t>버베인네일 분당수내점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>tpfla1999@naver.com</t>
+          <t>llltwjhlll@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1375-0335</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nail.arte/</t>
+          <t>https://blog.naver.com/llltwjhlll</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3401,7 +3397,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3421,13 +3417,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>473</v>
+        <v>54</v>
       </c>
       <c r="Q32" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="R32" t="n">
-        <v>510</v>
+        <v>85</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3436,12 +3432,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1010349043</t>
+          <t>2016496556</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010349043</t>
+          <t>https://m.place.naver.com/place/2016496556</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3458,34 +3454,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>띠어리네일</t>
+          <t>다나네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rnys11@naver.com</t>
+          <t>spring7503@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1314-1851</t>
+          <t>0507-1464-0476</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 68 1층 107호</t>
+          <t>경기도 성남시 분당구 성남대로 165 2층 218호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/theorynail</t>
+          <t>http://pf.kakao.com/_FZMiG</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3506,7 +3502,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3515,13 +3511,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>984</v>
+        <v>231</v>
       </c>
       <c r="Q33" t="n">
-        <v>222</v>
+        <v>11</v>
       </c>
       <c r="R33" t="n">
-        <v>1206</v>
+        <v>242</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3530,12 +3526,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1230407614</t>
+          <t>1679531126</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230407614</t>
+          <t>https://m.place.naver.com/place/1679531126</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3552,34 +3548,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>서영언니네일 앤 뷰티크 판교점</t>
+          <t>요푸네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>seo0unnienail@naver.com</t>
+          <t>may_12kr@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1429-9122</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+          <t>경기도 성남시 분당구 정자일로 158 5층 505호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+          <t>https://pf.kakao.com/_YxnRpxj?fbclid=PAAabkExMKD1XfiHVnimpBpaxeFWr-IdBTPk4ssczHjPJqMvRDPWrhZlMlVNY</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3600,7 +3592,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3609,13 +3601,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2434</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>2342</v>
+        <v>11</v>
       </c>
       <c r="R34" t="n">
-        <v>4776</v>
+        <v>13</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3624,12 +3616,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1335668367</t>
+          <t>1301522129</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335668367</t>
+          <t>https://m.place.naver.com/place/1301522129</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3646,34 +3638,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>위치네일스 판교점</t>
+          <t>백프로네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>dodream8069@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>031-622-7290</t>
+          <t>0507-1416-7323</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>https://pf.kakao.com/_MgAwxl</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3683,7 +3675,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3694,7 +3686,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3703,13 +3695,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>555</v>
+        <v>66</v>
       </c>
       <c r="Q35" t="n">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="R35" t="n">
-        <v>622</v>
+        <v>184</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3718,12 +3710,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1458353971</t>
+          <t>512636239</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458353971</t>
+          <t>https://m.place.naver.com/place/512636239</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3740,39 +3732,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>프리미엘네일 분당미금역점</t>
+          <t>네일 조안</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>premiel__nail@naver.com</t>
+          <t>yoj1116kr@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1362-6250</t>
+          <t>0507-1369-6361</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층 203-1호 프리미엘네일</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/premiel_nail</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3797,13 +3789,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4208</v>
+        <v>328</v>
       </c>
       <c r="Q36" t="n">
-        <v>323</v>
+        <v>31</v>
       </c>
       <c r="R36" t="n">
-        <v>4531</v>
+        <v>359</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3812,12 +3804,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1105478632</t>
+          <t>1520161470</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105478632</t>
+          <t>https://m.place.naver.com/place/1520161470</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3834,25 +3826,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>더블트리</t>
+          <t>네일스튜디오미니</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>doubletree-lash@naver.com</t>
+          <t>milk924@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>031-789-3555</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
+          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://instagram.com/doubletree_nail</t>
+          <t>http://www.instagram.com/nail_mini</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3887,13 +3883,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>138</v>
+        <v>321</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="R37" t="n">
-        <v>152</v>
+        <v>354</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,12 +3898,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>32699868</t>
+          <t>495440903</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32699868</t>
+          <t>https://m.place.naver.com/place/495440903</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3924,25 +3920,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>네일드잇</t>
+          <t>네일오브윤 분당점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>suzing9@naver.com</t>
+          <t>o___o373@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1366-7390</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로 172 2층 203호</t>
+          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://instagram.com/nailedit_mj</t>
+          <t>https://blog.naver.com/o___o373</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3977,13 +3977,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>194</v>
+        <v>1172</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>921</v>
       </c>
       <c r="R38" t="n">
-        <v>228</v>
+        <v>2093</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>37918491</t>
+          <t>1300308336</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37918491</t>
+          <t>https://m.place.naver.com/place/1300308336</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4014,34 +4014,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>나는 너의 네일</t>
+          <t>네일그자체</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>boboboc098@naver.com</t>
+          <t>wisp1205@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1391-8690</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 미금프라자 5층(다이소 바로 옆건물)</t>
+          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_Jxahxkxj/friend</t>
+          <t>https://www.instagram.com/nail_itself</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4062,7 +4058,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4071,13 +4067,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>9</v>
+        <v>169</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R39" t="n">
-        <v>49</v>
+        <v>192</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,12 +4082,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1174632490</t>
+          <t>2089755300</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174632490</t>
+          <t>https://m.place.naver.com/place/2089755300</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4108,12 +4104,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>뽐내 네일</t>
+          <t>바이뮤즈</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ppomnae369@naver.com</t>
+          <t>ynh3377@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -4121,17 +4117,17 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 926 분당메트로 3층 뽐내</t>
+          <t>경기도 성남시 분당구 정자일로 121 1층 C 10-1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qgWrG</t>
+          <t>http://instagram.com/_bymuse_</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4152,7 +4148,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4161,13 +4157,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>243</v>
+        <v>443</v>
       </c>
       <c r="Q40" t="n">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="R40" t="n">
-        <v>364</v>
+        <v>499</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4176,12 +4172,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1228519183</t>
+          <t>1198012559</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228519183</t>
+          <t>https://m.place.naver.com/place/1198012559</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4198,29 +4194,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>루나네일스튜디오</t>
+          <t>네일포엠</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>seoyan11@naver.com</t>
+          <t>sahsar@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1338-3307</t>
+          <t>0507-1381-1685</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 3층 317, 318호</t>
+          <t>경기도 성남시 분당구 성남대로 295 대림아크로텔 c동 129호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sKOPRm0f</t>
+          <t>http://instagram.com/nail_poem</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4246,7 +4242,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4255,13 +4251,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="Q41" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="R41" t="n">
-        <v>204</v>
+        <v>98</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4270,12 +4266,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1892992657</t>
+          <t>1373998196</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892992657</t>
+          <t>https://m.place.naver.com/place/1373998196</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4292,34 +4288,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>베베네일</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kub1207@naver.com</t>
+          <t>milkycoco95@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1309-9064</t>
+          <t>0507-1365-1483</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 3층 308호</t>
+          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/bebe.nailstudio</t>
+          <t>https://pf.kakao.com/_xnCjDG</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4340,7 +4336,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4349,13 +4345,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>341</v>
+        <v>107</v>
       </c>
       <c r="Q42" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="R42" t="n">
-        <v>367</v>
+        <v>145</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4364,12 +4360,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1290736362</t>
+          <t>1505688975</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290736362</t>
+          <t>https://m.place.naver.com/place/1505688975</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4386,39 +4382,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>비벨리</t>
+          <t>오로지푸스 앤 네일 스파</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>traveltrip11@naver.com</t>
+          <t>orosy2020@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1371-1908</t>
+          <t>0507-1382-0859</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+          <t>경기도 성남시 분당구 느티로 16 304호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+          <t>https://toss.place/_lb/dnrtwwsxK</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4443,13 +4439,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>257</v>
+        <v>125</v>
       </c>
       <c r="Q43" t="n">
-        <v>532</v>
+        <v>116</v>
       </c>
       <c r="R43" t="n">
-        <v>789</v>
+        <v>241</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4458,12 +4454,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1626230048</t>
+          <t>1948399629</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626230048</t>
+          <t>https://m.place.naver.com/place/1948399629</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4480,29 +4476,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>에러퍼펙트 분당서현점</t>
+          <t>메이드마이네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jungwonnail@naver.com</t>
+          <t>joololol_@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1436-5758</t>
+          <t>0507-1370-1842</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+          <t>경기도 성남시 분당구 분당로53번길 14 2층 208호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+          <t>https://www.instagram.com/made_mynail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4517,7 +4513,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4537,13 +4533,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1952</v>
+        <v>252</v>
       </c>
       <c r="Q44" t="n">
-        <v>639</v>
+        <v>158</v>
       </c>
       <c r="R44" t="n">
-        <v>2591</v>
+        <v>410</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4552,12 +4548,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1180875815</t>
+          <t>1528348158</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180875815</t>
+          <t>https://m.place.naver.com/place/1528348158</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4574,29 +4570,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일바이라라</t>
+          <t>에러퍼펙트 분당서현점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>iam_jihye@naver.com</t>
+          <t>jungwonnail@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1356-4115</t>
+          <t>0507-1436-5758</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbylala.official</t>
+          <t>https://blog.naver.com/jungwonnail?tab=1</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4611,7 +4607,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4631,13 +4627,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>360</v>
+        <v>1952</v>
       </c>
       <c r="Q45" t="n">
-        <v>29</v>
+        <v>640</v>
       </c>
       <c r="R45" t="n">
-        <v>389</v>
+        <v>2592</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4646,2909 +4642,15 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1737395332</t>
+          <t>1180875815</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737395332</t>
+          <t>https://m.place.naver.com/place/1180875815</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>언니네네일</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>fuddl3318@naver.com</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1378-0725</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로 170 한국프라자 1층</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>406</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>187</v>
-      </c>
-      <c r="R46" t="n">
-        <v>593</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>37554011</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37554011</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>유리네일</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>sfsf0525@naver.com</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0507-1310-6342</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로 51 분당포스빌 1층</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>198</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>116</v>
-      </c>
-      <c r="R47" t="n">
-        <v>314</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>37638489</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37638489</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>뮤요네일</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>rabong1219@naver.com</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0507-1389-6160</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>316</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>18</v>
-      </c>
-      <c r="R48" t="n">
-        <v>334</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1549676698</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1549676698</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>보니타네일 더푸스프로</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>soobromom_mijjang@naver.com</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1327-4406</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 지하1층</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>http://instagram.com/bonita_sohe_e</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>635</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>52</v>
-      </c>
-      <c r="R49" t="n">
-        <v>687</v>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>1005133986</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1005133986</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>네일다움 내성발톱 무좀 발각질 네일 문제성발 디톡스족욕</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>nail_dawoom@naver.com</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1483-9994</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 돌마로 85 동양프라자 4층</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/foot_naildawoom</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P50" t="n">
-        <v>632</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>391</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1023</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>1587982343</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1587982343</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>포세타네일</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>achellnet@naver.com</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nailfossetta</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P51" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>86</v>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>1702940792</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1702940792</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>반디인하우스 큐릭스 분당서현점</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>sdfw3t4@naver.com</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0507-1359-2111</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/sdfw3t4</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P52" t="n">
-        <v>1105</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>34</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1139</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>1557758291</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1557758291</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>네일보담</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>bongbong323@naver.com</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1344-9616</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로926번길 12 금탑프라자 103호</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nail_bodam/?r=nametag</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P53" t="n">
-        <v>297</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>39</v>
-      </c>
-      <c r="R53" t="n">
-        <v>336</v>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>1229535513</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1229535513</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>레푸스 분당정자점</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>refuss_bundang@naver.com</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>031-709-8870</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 3층 304호</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/refuss_bundang</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P54" t="n">
-        <v>1038</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>131</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1169</v>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>1293054958</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1293054958</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>헤몬네일</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>barbie7085055@naver.com</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/barbie7085055</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P55" t="n">
-        <v>1299</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>718</v>
-      </c>
-      <c r="R55" t="n">
-        <v>2017</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>1117775011</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1117775011</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>솜솜네일</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>mydbfla33@naver.com</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1416-2241</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로 51 포스빌 지하1층 50호 솜솜네일</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/somsomnail_</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>405</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>51</v>
-      </c>
-      <c r="R56" t="n">
-        <v>456</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>1165691375</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1165691375</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>다다네일</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>tykd2048@naver.com</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0507-1466-3338</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dada.nail/</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P57" t="n">
-        <v>441</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>70</v>
-      </c>
-      <c r="R57" t="n">
-        <v>511</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>240537974</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/240537974</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>포쉬네일 판교아브뉴프랑점</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>silentforest_studio@naver.com</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>031-603-3011</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P58" t="n">
-        <v>201</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>132</v>
-      </c>
-      <c r="R58" t="n">
-        <v>333</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>38258395</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/38258395</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>언투네일</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>loveili@naver.com</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0507-1346-4298</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 방아로 25 지하1층</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/untonail_?igsh=MXI0ejlrc3FkOGNvcA%3D%3D&amp;utm_source=qr</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P59" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>8</v>
-      </c>
-      <c r="R59" t="n">
-        <v>98</v>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>1449565892</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1449565892</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>네일604</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>esb2967@naver.com</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1327-5862</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로916번길 20 노블리치오피스텔 A동208호</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nail604_ss</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P60" t="n">
-        <v>1552</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>39</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1591</v>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>1789988736</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1789988736</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>라이티티아네일</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>laetitia5980@naver.com</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/laetitia_nail_j</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P61" t="n">
-        <v>156</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>101</v>
-      </c>
-      <c r="R61" t="n">
-        <v>257</v>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>1418162766</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1418162766</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>네일드와</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>hellomj18@naver.com</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0507-1445-1545</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nail_de_wa</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P62" t="n">
-        <v>721</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>16</v>
-      </c>
-      <c r="R62" t="n">
-        <v>737</v>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>1349678048</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1349678048</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>온들네일 분당정자점</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>lovmaria@naver.com</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0507-1443-7794</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 느티로 67 1층 104호</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>http://pf.kakao.com/_xkxaKin</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P63" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>26</v>
-      </c>
-      <c r="R63" t="n">
-        <v>80</v>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>2085728870</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2085728870</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>마틸다네일M 분당점</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>vin2roo@naver.com</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-13 3층 301호</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/matilda_nailshop</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P64" t="n">
-        <v>149</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>1307</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1456</v>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>1714191610</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1714191610</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>네일인어스</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>gywjd2303@naver.com</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nailinus</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P65" t="n">
-        <v>636</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>162</v>
-      </c>
-      <c r="R65" t="n">
-        <v>798</v>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>1591004723</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1591004723</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>레푸스 판교점</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>yedamcp@naver.com</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>031-702-8870</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/yedamcp</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P66" t="n">
-        <v>1378</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>567</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1945</v>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>1710320799</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1710320799</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>라온네일클리닉 판교 본점</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>sungunara226@naver.com</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0507-1418-3314</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 판교역로 230 삼환하이펙스 B동 1층 122-1호</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/sungunara226</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P67" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>283</v>
-      </c>
-      <c r="R67" t="n">
-        <v>350</v>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>1137420501</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1137420501</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>예쁘게살자</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>sukjin1125@naver.com</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>031-702-9340</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 2층 예쁘게살자</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/sukjin1125</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P68" t="n">
-        <v>753</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>41</v>
-      </c>
-      <c r="R68" t="n">
-        <v>794</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>1221851423</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1221851423</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>네일오브윤 분당점</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>o___o373@naver.com</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0507-1366-7390</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/o___o373</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P69" t="n">
-        <v>1171</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>920</v>
-      </c>
-      <c r="R69" t="n">
-        <v>2091</v>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>1300308336</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1300308336</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>어도어네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>gywjd2303@naver.com</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0507-1391-6431</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로331번길 8 킨스타워 3층 311호</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/adorenail__?igsh=MThpanMxYXA3a2M1aA==</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P70" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>39</v>
-      </c>
-      <c r="R70" t="n">
-        <v>197</v>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>1011483246</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1011483246</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>네일포엠</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>sahsar@naver.com</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1381-1685</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 성남대로 295 대림아크로텔 c동 129호</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>http://instagram.com/nail_poem</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P71" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>21</v>
-      </c>
-      <c r="R71" t="n">
-        <v>98</v>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>1373998196</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1373998196</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>쏘굿네일 분당미금점</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>sohyun1304@naver.com</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1427-2394</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 돌마로 73 우방코아 2층 211호</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>http://www.instagram.com/sso_good_nail</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P72" t="n">
-        <v>1410</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>390</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1800</v>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>1235289874</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1235289874</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>무니네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>efjekkk0888@naver.com</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>032-1000-1000</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 황새울로116번길 19-4 1층 무니네일스튜디오</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/muninail_</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P73" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>14</v>
-      </c>
-      <c r="R73" t="n">
-        <v>120</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>1764595990</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1764595990</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>안녕,예쁜손</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>bbolm@naver.com</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0507-1429-8836</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>http://www.instagram.com/hello_jininail</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P74" t="n">
-        <v>885</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>258</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1143</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>13399185</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/13399185</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>라모르뷰티 분당수내 본점</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>lamour11@naver.com</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1465-5979</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>http://instagram.com/lamour.nail</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P75" t="n">
-        <v>264</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>81</v>
-      </c>
-      <c r="R75" t="n">
-        <v>345</v>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>1397181784</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1397181784</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>모스네일 판교점</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>mossnail@naver.com</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0507-1317-6311</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/moss._.nail</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P76" t="n">
-        <v>395</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>69</v>
-      </c>
-      <c r="R76" t="n">
-        <v>464</v>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>1816221132</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1816221132</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_nail/분당_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/분당_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -4656,6 +4656,2860 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>뮤트샵</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>kimyi95@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>031-607-0069</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 1층 134호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_muteshop</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>1018</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>71</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1089</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>37883447</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37883447</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jjuahlee@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1403-3341</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1036</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>121</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1157</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>37870150</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37870150</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>라이티티아네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>laetitia5980@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/laetitia_nail_j</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>101</v>
+      </c>
+      <c r="R48" t="n">
+        <v>257</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1418162766</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1418162766</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>위치네일스 판교점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>witch_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>031-622-7290</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/witch_nail</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>556</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>67</v>
+      </c>
+      <c r="R49" t="n">
+        <v>623</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1458353971</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1458353971</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>루미네일 수내점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>halobebe@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1445-6255</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로165번길 38 청구아파트 상가 601동 125호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luminail_bd</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>522</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>29</v>
+      </c>
+      <c r="R50" t="n">
+        <v>551</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1065650334</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1065650334</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>나는 너의 네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>boboboc098@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1391-8690</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 5층(다이소 바로 옆건물)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_Jxahxkxj/friend</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>40</v>
+      </c>
+      <c r="R51" t="n">
+        <v>49</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1174632490</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1174632490</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>포세타네일</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>achellnet@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailfossetta</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>86</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1702940792</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1702940792</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>조이네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>aa6364844@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1352-5816</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 2층 207호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aa6364844</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>2329</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>603</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2932</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>37049599</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37049599</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>네일발라봄</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>theboni@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1350-1712</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 51 B29호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nailballabom</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>14</v>
+      </c>
+      <c r="R54" t="n">
+        <v>41</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1585268852</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1585268852</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>하르네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cxd1000@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1305-3099</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/harr__nail/</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>36</v>
+      </c>
+      <c r="R55" t="n">
+        <v>310</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2066713618</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2066713618</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>비온빛 네일브라운 분당미금점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>nailb1212@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1407-1279</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 52 2층 203호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailbrown_</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>882</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>784</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1666</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1647015847</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1647015847</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>비벨리</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>traveltrip11@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1371-1908</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>532</v>
+      </c>
+      <c r="R57" t="n">
+        <v>789</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1626230048</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1626230048</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>다다네일</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>tykd2048@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1466-3338</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dada.nail/</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>70</v>
+      </c>
+      <c r="R58" t="n">
+        <v>511</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>240537974</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/240537974</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>안녕,예쁜손</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>bbolm@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1429-8836</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/hello_jininail</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>885</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>258</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1143</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>13399185</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13399185</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>라모르뷰티 분당수내 본점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>lamour11@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1465-5979</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>http://instagram.com/lamour.nail</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>81</v>
+      </c>
+      <c r="R60" t="n">
+        <v>345</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1397181784</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397181784</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>루나네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>seoyan11@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1338-3307</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 12 3층 317, 318호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sKOPRm0f</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>40</v>
+      </c>
+      <c r="R61" t="n">
+        <v>204</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1892992657</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1892992657</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>네일604</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>esb2967@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1327-5862</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로916번길 20 노블리치오피스텔 A동208호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail604_ss</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1554</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>39</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1593</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1789988736</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1789988736</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>트리나네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>treenanail@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1361-6532</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/tree_na_nail</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1159</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>95</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1254</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1331495059</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1331495059</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>언투네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1346-4298</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 방아로 25 지하1층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/untonail_?igsh=MXI0ejlrc3FkOGNvcA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>8</v>
+      </c>
+      <c r="R64" t="n">
+        <v>98</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1449565892</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1449565892</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>띠어리네일</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1314-1851</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 68 1층 107호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/theorynail</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>984</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>222</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1206</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1230407614</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1230407614</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>뮤요네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1389-6160</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>316</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>18</v>
+      </c>
+      <c r="R66" t="n">
+        <v>334</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1549676698</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1549676698</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>쏘굿네일 분당미금점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sohyun1304@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1427-2394</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 73 우방코아 2층 211호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/sso_good_nail</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1410</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>390</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1800</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1235289874</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1235289874</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>네일아르떼</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__nail.arte/</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>474</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>37</v>
+      </c>
+      <c r="R68" t="n">
+        <v>511</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1010349043</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1010349043</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>네일인90</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>nailin90@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1331-0990</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로925번길 16 성남분당여객자동차터미널 2층 네일인90</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_in90</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1155</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>53</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1208</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1354180497</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1354180497</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>마틸다네일M 분당점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 3-13 3층 301호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/matilda_nailshop</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1308</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1457</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1714191610</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1714191610</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>보니타네일 더푸스프로</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1327-4406</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>http://instagram.com/bonita_sohe_e</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>635</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>52</v>
+      </c>
+      <c r="R71" t="n">
+        <v>687</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1005133986</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1005133986</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>뮤네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1474-1789</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로925번길 19 5층 501-2호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_fxizxcxj</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>26</v>
+      </c>
+      <c r="R72" t="n">
+        <v>259</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1325100624</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1325100624</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>온들네일 분당정자점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1443-7794</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 67 1층 104호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xkxaKin</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>26</v>
+      </c>
+      <c r="R73" t="n">
+        <v>80</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2085728870</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2085728870</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>네일바이라라</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1356-4115</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailbylala.official</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>29</v>
+      </c>
+      <c r="R74" t="n">
+        <v>389</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1737395332</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1737395332</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>포쉬네일 판교아브뉴프랑점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>031-603-3011</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>133</v>
+      </c>
+      <c r="R75" t="n">
+        <v>334</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>38258395</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38258395</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>헤몬네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>barbie7085055@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/barbie7085055</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>1299</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>719</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2018</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1117775011</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1117775011</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver-place-crawler/results_nail/분당_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/분당_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>후와네일</t>
+          <t>레푸스 분당정자점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kimnk980409@naver.com</t>
+          <t>refuss_bundang@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1342-1792</t>
+          <t>031-709-8870</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 3층 304호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/refuss_bundang</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>447</v>
+        <v>1039</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="R2" t="n">
-        <v>465</v>
+        <v>1171</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1782262137</t>
+          <t>1293054958</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782262137</t>
+          <t>https://m.place.naver.com/place/1293054958</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>포쉬네일 AK분당점</t>
+          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>woosy0225@naver.com</t>
+          <t>uijn_dd@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1416-2324</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_footcare</t>
+          <t>https://www.instagram.com/cherryshbeauty_official</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>682</v>
+        <v>1079</v>
       </c>
       <c r="Q3" t="n">
-        <v>59</v>
+        <v>524</v>
       </c>
       <c r="R3" t="n">
-        <v>741</v>
+        <v>1603</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1692272902</t>
+          <t>36524000</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692272902</t>
+          <t>https://m.place.naver.com/place/36524000</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>레푸스 분당정자점</t>
+          <t>비온빛 네일브라운 분당미금점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>refuss_bundang@naver.com</t>
+          <t>nailb1212@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>031-709-8870</t>
+          <t>0507-1407-1279</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 3층 304호</t>
+          <t>경기도 성남시 분당구 돌마로 52 2층 203호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refuss_bundang</t>
+          <t>https://www.instagram.com/nailbrown_</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,7 +796,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1038</v>
+        <v>882</v>
       </c>
       <c r="Q4" t="n">
-        <v>131</v>
+        <v>784</v>
       </c>
       <c r="R4" t="n">
-        <v>1169</v>
+        <v>1666</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1293054958</t>
+          <t>1647015847</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293054958</t>
+          <t>https://m.place.naver.com/place/1647015847</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +842,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>베베네일</t>
+          <t>라이티티아네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kub1207@naver.com</t>
+          <t>laetitia5980@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1309-9064</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 3층 308호</t>
+          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/bebe.nailstudio</t>
+          <t>https://www.instagram.com/laetitia_nail_j</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>342</v>
+        <v>156</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="R5" t="n">
-        <v>368</v>
+        <v>257</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1290736362</t>
+          <t>1418162766</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290736362</t>
+          <t>https://m.place.naver.com/place/1418162766</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +932,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>서영언니네일 앤 뷰티크 판교점</t>
+          <t>알로이네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>seo0unnienail@naver.com</t>
+          <t>aloinail@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1429-9122</t>
+          <t>0507-1448-7808</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+          <t>경기도 성남시 분당구 정자일로 1 코오롱트리플리스1 상가 201호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+          <t>https://blog.naver.com/aloinail</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +969,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +980,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2434</v>
+        <v>360</v>
       </c>
       <c r="Q6" t="n">
-        <v>2342</v>
+        <v>58</v>
       </c>
       <c r="R6" t="n">
-        <v>4776</v>
+        <v>418</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1335668367</t>
+          <t>1956208028</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335668367</t>
+          <t>https://m.place.naver.com/place/1956208028</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1026,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>어도어네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>gywjd2303@naver.com</t>
-        </is>
-      </c>
+          <t>백프로네일</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1391-6431</t>
+          <t>0507-1416-7323</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 8 킨스타워 3층 311호</t>
+          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/adorenail__?igsh=MThpanMxYXA3a2M1aA==</t>
+          <t>https://pf.kakao.com/_MgAwxl</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1070,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1079,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>158</v>
+        <v>66</v>
       </c>
       <c r="Q7" t="n">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="R7" t="n">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1094,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1011483246</t>
+          <t>512636239</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1011483246</t>
+          <t>https://m.place.naver.com/place/512636239</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1116,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>예쁘게살자</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>sukjin1125@naver.com</t>
-        </is>
-      </c>
+          <t>네일포엠</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-702-9340</t>
+          <t>0507-1381-1685</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 2층 예쁘게살자</t>
+          <t>경기도 성남시 분당구 성남대로 295 대림아크로텔 c동 129호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sukjin1125</t>
+          <t>http://instagram.com/nail_poem</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1149,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>753</v>
+        <v>77</v>
       </c>
       <c r="Q8" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="R8" t="n">
-        <v>794</v>
+        <v>98</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1221851423</t>
+          <t>1373998196</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1221851423</t>
+          <t>https://m.place.naver.com/place/1373998196</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1222,34 +1206,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일드와</t>
+          <t>다나네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hellomj18@naver.com</t>
+          <t>spring7503@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1445-1545</t>
+          <t>0507-1464-0476</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
+          <t>경기도 성남시 분당구 성남대로 165 2층 218호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_wa</t>
+          <t>http://pf.kakao.com/_FZMiG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1270,7 +1254,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>721</v>
+        <v>231</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>737</v>
+        <v>242</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1349678048</t>
+          <t>1679531126</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349678048</t>
+          <t>https://m.place.naver.com/place/1679531126</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1300,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>언니네네일</t>
+          <t>반디인하우스 큐릭스 분당서현점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fuddl3318@naver.com</t>
+          <t>sdfw3t4@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1378-0725</t>
+          <t>0507-1359-2111</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 170 한국프라자 1층</t>
+          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sdfw3t4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,12 +1332,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,17 +1353,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>406</v>
+        <v>1105</v>
       </c>
       <c r="Q10" t="n">
-        <v>187</v>
+        <v>34</v>
       </c>
       <c r="R10" t="n">
-        <v>593</v>
+        <v>1139</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1372,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37554011</t>
+          <t>1557758291</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37554011</t>
+          <t>https://m.place.naver.com/place/1557758291</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1410,44 +1394,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일팜</t>
+          <t>네일 조안</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nailpalm@naver.com</t>
+          <t>yoj1116kr@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1371-5111</t>
+          <t>0507-1369-6361</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 67 금산젬월드 4층 405호</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailpalm</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1451,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>862</v>
+        <v>328</v>
       </c>
       <c r="Q11" t="n">
-        <v>323</v>
+        <v>31</v>
       </c>
       <c r="R11" t="n">
-        <v>1185</v>
+        <v>359</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1466,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37398310</t>
+          <t>1520161470</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37398310</t>
+          <t>https://m.place.naver.com/place/1520161470</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1488,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일보담</t>
+          <t>네일발라봄</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>theboni@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1344-9616</t>
+          <t>0507-1350-1712</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로926번길 12 금탑프라자 103호</t>
+          <t>경기도 성남시 분당구 성남대로 51 B29호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_bodam/?r=nametag</t>
+          <t>http://instagram.com/nailballabom</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1552,7 +1536,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1561,13 +1545,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>297</v>
+        <v>27</v>
       </c>
       <c r="Q12" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="R12" t="n">
-        <v>336</v>
+        <v>41</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1560,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1229535513</t>
+          <t>1585268852</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229535513</t>
+          <t>https://m.place.naver.com/place/1585268852</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1598,34 +1582,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>르에 판교점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>leehhnail@naver.com</t>
-        </is>
-      </c>
+          <t>포쉬네일 AK분당점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1466-0874</t>
+          <t>0507-1416-2324</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/le.ehh</t>
+          <t>https://www.instagram.com/forsynail_footcare</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1635,7 +1615,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1655,13 +1635,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>107</v>
+        <v>682</v>
       </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="R13" t="n">
-        <v>162</v>
+        <v>741</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1650,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1963747515</t>
+          <t>1692272902</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963747515</t>
+          <t>https://m.place.naver.com/place/1692272902</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1692,25 +1672,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
+          <t>네일오브윤 분당점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>uijn_dd@naver.com</t>
+          <t>o___o373@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1366-7390</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
+          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cherryshbeauty_official</t>
+          <t>https://blog.naver.com/o___o373</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1725,7 +1709,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1745,13 +1729,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1079</v>
+        <v>1172</v>
       </c>
       <c r="Q14" t="n">
-        <v>524</v>
+        <v>921</v>
       </c>
       <c r="R14" t="n">
-        <v>1603</v>
+        <v>2093</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1744,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>36524000</t>
+          <t>1300308336</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36524000</t>
+          <t>https://m.place.naver.com/place/1300308336</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1782,30 +1766,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>러브엘네일</t>
+          <t>벨라뷰티</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>haniii_world@naver.com</t>
+          <t>aqsw0111@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1391-1078</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 513-1호 5층 내려서 바로 왼쪽 입니다 :)</t>
+          <t>경기도 성남시 분당구 정자일로 158 백궁프라자2 3층 301호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhRYWn</t>
+          <t>https://www.instagram.com/bellabeauty_nail</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1835,13 +1823,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>246</v>
+        <v>468</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="R15" t="n">
-        <v>253</v>
+        <v>522</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1838,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2023334466</t>
+          <t>1236154271</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023334466</t>
+          <t>https://m.place.naver.com/place/1236154271</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1929,13 +1917,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4213</v>
+        <v>4217</v>
       </c>
       <c r="Q16" t="n">
         <v>324</v>
       </c>
       <c r="R16" t="n">
-        <v>4537</v>
+        <v>4541</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1954,7 +1942,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1966,34 +1954,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일, 연</t>
+          <t>뮤네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>wlsl9169@naver.com</t>
+          <t>mieux_by_nail@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1400-3992</t>
+          <t>0507-1474-1789</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 1층 107호</t>
+          <t>경기도 성남시 분당구 성남대로925번길 19 5층 501-2호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailyeon_?igsh=MXAxdWN4M2I1ZHRldQ==</t>
+          <t>http://pf.kakao.com/_fxizxcxj</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2014,7 +2002,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2023,13 +2011,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="R17" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2026,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1232273978</t>
+          <t>1325100624</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1232273978</t>
+          <t>https://m.place.naver.com/place/1325100624</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2060,29 +2048,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>827네일 분당미금점</t>
+          <t>라모르뷰티 분당수내 본점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>827nail@naver.com</t>
+          <t>lamour11@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1308-0827</t>
+          <t>0507-1465-5979</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로144번길 16 1층 827네일</t>
+          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/827nail</t>
+          <t>http://instagram.com/lamour.nail</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2117,13 +2105,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2524</v>
+        <v>264</v>
       </c>
       <c r="Q18" t="n">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="R18" t="n">
-        <v>2908</v>
+        <v>345</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2120,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1290037889</t>
+          <t>1397181784</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290037889</t>
+          <t>https://m.place.naver.com/place/1397181784</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2154,34 +2142,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>유리네일</t>
+          <t>오로지푸스 앤 네일 스파</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sfsf0525@naver.com</t>
+          <t>orosy2020@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1310-6342</t>
+          <t>0507-1382-0859</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 51 분당포스빌 1층</t>
+          <t>경기도 성남시 분당구 느티로 16 304호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://toss.place/_lb/dnrtwwsxK</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2207,17 +2195,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>198</v>
+        <v>124</v>
       </c>
       <c r="Q19" t="n">
         <v>116</v>
       </c>
       <c r="R19" t="n">
-        <v>314</v>
+        <v>240</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,17 +2214,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>37638489</t>
+          <t>1948399629</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37638489</t>
+          <t>https://m.place.naver.com/place/1948399629</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2248,29 +2236,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>벨라뷰티</t>
+          <t>에러퍼펙트 분당서현점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>aqsw0111@naver.com</t>
+          <t>jungwonnail@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1391-1078</t>
+          <t>0507-1436-5758</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 158 백궁프라자2 3층 301호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bellabeauty_nail</t>
+          <t>https://blog.naver.com/jungwonnail?tab=1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2285,7 +2273,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2296,7 +2284,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2305,13 +2293,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>467</v>
+        <v>1952</v>
       </c>
       <c r="Q20" t="n">
-        <v>54</v>
+        <v>640</v>
       </c>
       <c r="R20" t="n">
-        <v>521</v>
+        <v>2592</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2308,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1236154271</t>
+          <t>1180875815</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236154271</t>
+          <t>https://m.place.naver.com/place/1180875815</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2342,29 +2330,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>레푸스 판교점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>yedamcp@naver.com</t>
-        </is>
-      </c>
+          <t>솜솜네일</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>031-702-8870</t>
+          <t>0507-1416-2241</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+          <t>경기도 성남시 분당구 성남대로 51 포스빌 지하1층 50호 솜솜네일</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yedamcp</t>
+          <t>https://www.instagram.com/somsomnail_</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,7 +2363,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2399,13 +2383,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1378</v>
+        <v>405</v>
       </c>
       <c r="Q21" t="n">
-        <v>567</v>
+        <v>51</v>
       </c>
       <c r="R21" t="n">
-        <v>1945</v>
+        <v>456</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,17 +2398,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1710320799</t>
+          <t>1165691375</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710320799</t>
+          <t>https://m.place.naver.com/place/1165691375</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2436,25 +2420,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>더블트리</t>
+          <t>하낭네일스튜디오</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>doubletree-lash@naver.com</t>
+          <t>senniverse@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1322-5647</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
+          <t>경기도 성남시 분당구 느티로 73 현대 빌딩 2층 204호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://instagram.com/doubletree_nail</t>
+          <t>https://www.instagram.com/ha.nang_nail_studio?igsh=MTR4anJrZW8yN3M4eA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2489,13 +2477,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>138</v>
+        <v>584</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R22" t="n">
-        <v>152</v>
+        <v>595</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2492,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>32699868</t>
+          <t>1339933062</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32699868</t>
+          <t>https://m.place.naver.com/place/1339933062</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2526,29 +2514,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>알로이네일</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>aloinail@naver.com</t>
-        </is>
-      </c>
+          <t>네일그자체</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0507-1448-7808</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 1 코오롱트리플리스1 상가 201호</t>
+          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aloinail</t>
+          <t>https://www.instagram.com/nail_itself</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2563,7 +2543,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2574,7 +2554,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2583,13 +2563,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>360</v>
+        <v>169</v>
       </c>
       <c r="Q23" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="R23" t="n">
-        <v>418</v>
+        <v>192</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2578,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1956208028</t>
+          <t>2089755300</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956208028</t>
+          <t>https://m.place.naver.com/place/2089755300</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2620,34 +2600,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>솜솜네일</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>mydbfla33@naver.com</t>
-        </is>
-      </c>
+          <t>러브엘네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1416-2241</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 51 포스빌 지하1층 50호 솜솜네일</t>
+          <t>경기도 성남시 분당구 돌마로 47 513-1호 5층 내려서 바로 왼쪽 입니다 :)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/somsomnail_</t>
+          <t>http://pf.kakao.com/_xhRYWn</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2668,7 +2640,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2677,13 +2649,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>405</v>
+        <v>247</v>
       </c>
       <c r="Q24" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>456</v>
+        <v>254</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2664,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1165691375</t>
+          <t>2023334466</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165691375</t>
+          <t>https://m.place.naver.com/place/2023334466</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2714,25 +2686,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>네일인어스</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>gywjd2303@naver.com</t>
-        </is>
-      </c>
+          <t>안녕,예쁜손</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1429-8836</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
+          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailinus</t>
+          <t>http://www.instagram.com/hello_jininail</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2767,13 +2739,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>635</v>
+        <v>887</v>
       </c>
       <c r="Q25" t="n">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="R25" t="n">
-        <v>797</v>
+        <v>1145</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2754,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1591004723</t>
+          <t>13399185</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591004723</t>
+          <t>https://m.place.naver.com/place/13399185</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2804,29 +2776,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>하낭네일스튜디오</t>
+          <t>포쉬네일 판교아브뉴프랑점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>senniverse@naver.com</t>
+          <t>silentforest_studio@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1322-5647</t>
+          <t>031-603-3011</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 73 현대 빌딩 2층 204호</t>
+          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ha.nang_nail_studio?igsh=MTR4anJrZW8yN3M4eA%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2836,7 +2808,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2857,17 +2829,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>584</v>
+        <v>201</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="R26" t="n">
-        <v>595</v>
+        <v>334</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2848,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1339933062</t>
+          <t>38258395</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1339933062</t>
+          <t>https://m.place.naver.com/place/38258395</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2898,25 +2870,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일드잇</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>tudougunniang@naver.com</t>
-        </is>
-      </c>
+          <t>네일바이라라</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1356-4115</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로 172 2층 203호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://instagram.com/nailedit_mj</t>
+          <t>https://www.instagram.com/nailbylala.official</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2951,13 +2923,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>194</v>
+        <v>360</v>
       </c>
       <c r="Q27" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="R27" t="n">
-        <v>228</v>
+        <v>389</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2966,17 +2938,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>37918491</t>
+          <t>1737395332</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37918491</t>
+          <t>https://m.place.naver.com/place/1737395332</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2988,29 +2960,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>모스네일 판교점</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>mossnail@naver.com</t>
-        </is>
-      </c>
+          <t>마틸다네일M 분당점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0507-1317-6311</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-13 3층 301호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss._.nail</t>
+          <t>https://www.instagram.com/matilda_nailshop</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3045,13 +3009,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>396</v>
+        <v>149</v>
       </c>
       <c r="Q28" t="n">
-        <v>69</v>
+        <v>1308</v>
       </c>
       <c r="R28" t="n">
-        <v>465</v>
+        <v>1457</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3060,17 +3024,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1816221132</t>
+          <t>1714191610</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816221132</t>
+          <t>https://m.place.naver.com/place/1714191610</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3082,30 +3046,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>뽐내 네일</t>
+          <t>모스네일 판교점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ppomnae369@naver.com</t>
+          <t>mossnail@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1317-6311</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 926 분당메트로 3층 뽐내</t>
+          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qgWrG</t>
+          <t>https://www.instagram.com/moss._.nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3126,7 +3094,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3135,13 +3103,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>243</v>
+        <v>397</v>
       </c>
       <c r="Q29" t="n">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="R29" t="n">
-        <v>364</v>
+        <v>466</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3150,17 +3118,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1228519183</t>
+          <t>1816221132</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228519183</t>
+          <t>https://m.place.naver.com/place/1816221132</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3172,29 +3140,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>반디인하우스 큐릭스 분당서현점</t>
+          <t>트리나네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sdfw3t4@naver.com</t>
+          <t>treenanail@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1359-2111</t>
+          <t>0507-1361-6532</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sdfw3t4</t>
+          <t>http://www.instagram.com/tree_na_nail</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3209,7 +3177,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3229,13 +3197,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1105</v>
+        <v>1159</v>
       </c>
       <c r="Q30" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="R30" t="n">
-        <v>1139</v>
+        <v>1254</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3244,17 +3212,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1557758291</t>
+          <t>1331495059</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557758291</t>
+          <t>https://m.place.naver.com/place/1331495059</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3266,29 +3234,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일다움 내성발톱 무좀 발각질 네일 문제성발 디톡스족욕</t>
+          <t>예쁘게살자</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>nail_dawoom@naver.com</t>
+          <t>sukjin1125@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1483-9994</t>
+          <t>031-702-9340</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 85 동양프라자 4층</t>
+          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 2층 예쁘게살자</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/foot_naildawoom</t>
+          <t>https://blog.naver.com/sukjin1125</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3303,7 +3271,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3323,13 +3291,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>632</v>
+        <v>753</v>
       </c>
       <c r="Q31" t="n">
-        <v>391</v>
+        <v>41</v>
       </c>
       <c r="R31" t="n">
-        <v>1023</v>
+        <v>794</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,17 +3306,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1587982343</t>
+          <t>1221851423</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1587982343</t>
+          <t>https://m.place.naver.com/place/1221851423</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3360,29 +3328,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>버베인네일 분당수내점</t>
+          <t>위치네일스 판교점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>llltwjhlll@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1375-0335</t>
+          <t>031-622-7290</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/llltwjhlll</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3417,13 +3385,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>54</v>
+        <v>556</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="R32" t="n">
-        <v>85</v>
+        <v>623</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,17 +3400,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2016496556</t>
+          <t>1458353971</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016496556</t>
+          <t>https://m.place.naver.com/place/1458353971</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3454,29 +3422,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>다나네일</t>
+          <t>르에 판교점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>spring7503@naver.com</t>
+          <t>leehhnail@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1464-0476</t>
+          <t>0507-1466-0874</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 165 2층 218호</t>
+          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FZMiG</t>
+          <t>https://link.inpock.co.kr/le.ehh</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3491,7 +3459,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3502,7 +3470,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3511,13 +3479,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>231</v>
+        <v>107</v>
       </c>
       <c r="Q33" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="R33" t="n">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,17 +3494,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1679531126</t>
+          <t>1963747515</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679531126</t>
+          <t>https://m.place.naver.com/place/1963747515</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3548,30 +3516,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>요푸네일</t>
+          <t>하르네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>may_12kr@naver.com</t>
+          <t>cxd1000@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1305-3099</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 158 5층 505호</t>
+          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_YxnRpxj?fbclid=PAAabkExMKD1XfiHVnimpBpaxeFWr-IdBTPk4ssczHjPJqMvRDPWrhZlMlVNY</t>
+          <t>https://www.instagram.com/harr__nail/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3592,7 +3564,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3601,13 +3573,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="R34" t="n">
-        <v>13</v>
+        <v>312</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,17 +3588,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1301522129</t>
+          <t>2066713618</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1301522129</t>
+          <t>https://m.place.naver.com/place/2066713618</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3638,34 +3610,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>백프로네일</t>
+          <t>네일아르떼</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dodream8069@naver.com</t>
+          <t>tpfla1999@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0507-1416-7323</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_MgAwxl</t>
+          <t>https://www.instagram.com/__nail.arte/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3686,7 +3654,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3695,13 +3663,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>66</v>
+        <v>474</v>
       </c>
       <c r="Q35" t="n">
-        <v>118</v>
+        <v>37</v>
       </c>
       <c r="R35" t="n">
-        <v>184</v>
+        <v>511</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,17 +3678,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>512636239</t>
+          <t>1010349043</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/512636239</t>
+          <t>https://m.place.naver.com/place/1010349043</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3732,44 +3700,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일 조안</t>
+          <t>네일팜</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>yoj1116kr@naver.com</t>
+          <t>nailpalm@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1369-6361</t>
+          <t>0507-1371-5111</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
+          <t>경기도 성남시 분당구 돌마로 67 금산젬월드 4층 405호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>https://blog.naver.com/nailpalm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3789,13 +3757,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>328</v>
+        <v>862</v>
       </c>
       <c r="Q36" t="n">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="R36" t="n">
-        <v>359</v>
+        <v>1185</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3804,17 +3772,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1520161470</t>
+          <t>37398310</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520161470</t>
+          <t>https://m.place.naver.com/place/37398310</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3876,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3920,29 +3888,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>네일오브윤 분당점</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>o___o373@naver.com</t>
-        </is>
-      </c>
+          <t>뮤트샵</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1366-7390</t>
+          <t>031-607-0069</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 1층 134호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/o___o373</t>
+          <t>http://instagram.com/_muteshop</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3957,7 +3921,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3977,13 +3941,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1172</v>
+        <v>1018</v>
       </c>
       <c r="Q38" t="n">
-        <v>921</v>
+        <v>71</v>
       </c>
       <c r="R38" t="n">
-        <v>2093</v>
+        <v>1089</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,17 +3956,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1300308336</t>
+          <t>37883447</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300308336</t>
+          <t>https://m.place.naver.com/place/37883447</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4014,12 +3978,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일그자체</t>
+          <t>더블트리</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>wisp1205@naver.com</t>
+          <t>doubletree-lash@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -4027,12 +3991,12 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_itself</t>
+          <t>http://instagram.com/doubletree_nail</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4067,13 +4031,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="Q39" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="R39" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4082,17 +4046,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2089755300</t>
+          <t>32699868</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089755300</t>
+          <t>https://m.place.naver.com/place/32699868</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4104,25 +4068,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>바이뮤즈</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>ynh3377@naver.com</t>
-        </is>
-      </c>
+          <t>다다네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1466-3338</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 1층 C 10-1</t>
+          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://instagram.com/_bymuse_</t>
+          <t>https://www.instagram.com/dada.nail/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4157,13 +4121,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Q40" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="R40" t="n">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4172,17 +4136,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1198012559</t>
+          <t>240537974</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198012559</t>
+          <t>https://m.place.naver.com/place/240537974</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4194,29 +4158,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일포엠</t>
+          <t>네일인어스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sahsar@naver.com</t>
+          <t>kmj8937@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1381-1685</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 295 대림아크로텔 c동 129호</t>
+          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_poem</t>
+          <t>https://www.instagram.com/nailinus</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4251,13 +4211,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>77</v>
+        <v>635</v>
       </c>
       <c r="Q41" t="n">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="R41" t="n">
-        <v>98</v>
+        <v>798</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4266,17 +4226,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1373998196</t>
+          <t>1591004723</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373998196</t>
+          <t>https://m.place.naver.com/place/1591004723</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4288,34 +4248,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>뮤요네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>rabong1219@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1365-1483</t>
+          <t>0507-1389-6160</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
+          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnCjDG</t>
+          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4336,7 +4296,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4345,13 +4305,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>107</v>
+        <v>316</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="R42" t="n">
-        <v>145</v>
+        <v>334</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4360,17 +4320,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1505688975</t>
+          <t>1549676698</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505688975</t>
+          <t>https://m.place.naver.com/place/1549676698</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4382,29 +4342,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>오로지푸스 앤 네일 스파</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>orosy2020@naver.com</t>
-        </is>
-      </c>
+          <t>나는 너의 네일</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1382-0859</t>
+          <t>0507-1391-8690</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 304호</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 5층(다이소 바로 옆건물)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/dnrtwwsxK</t>
+          <t>https://pf.kakao.com/_Jxahxkxj/friend</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4414,7 +4370,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4430,7 +4386,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4439,13 +4395,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="Q43" t="n">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="R43" t="n">
-        <v>241</v>
+        <v>49</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4454,17 +4410,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1948399629</t>
+          <t>1174632490</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948399629</t>
+          <t>https://m.place.naver.com/place/1174632490</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4476,29 +4432,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>메이드마이네일</t>
+          <t>베베네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>joololol_@naver.com</t>
+          <t>kub1207@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1370-1842</t>
+          <t>0507-1309-9064</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 14 2층 208호</t>
+          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 3층 308호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/made_mynail</t>
+          <t>http://www.instagram.com/bebe.nailstudio</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4533,13 +4489,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>252</v>
+        <v>342</v>
       </c>
       <c r="Q44" t="n">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="R44" t="n">
-        <v>410</v>
+        <v>368</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4548,17 +4504,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1528348158</t>
+          <t>1290736362</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1528348158</t>
+          <t>https://m.place.naver.com/place/1290736362</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4570,34 +4526,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>에러퍼펙트 분당서현점</t>
+          <t>뽐내 네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jungwonnail@naver.com</t>
+          <t>ppomnae369@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1436-5758</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+          <t>경기도 성남시 분당구 성남대로 926 분당메트로 3층 뽐내</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+          <t>http://pf.kakao.com/_qgWrG</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4607,7 +4559,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4618,7 +4570,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4627,13 +4579,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1952</v>
+        <v>243</v>
       </c>
       <c r="Q45" t="n">
-        <v>640</v>
+        <v>121</v>
       </c>
       <c r="R45" t="n">
-        <v>2592</v>
+        <v>364</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4642,17 +4594,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1180875815</t>
+          <t>1228519183</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180875815</t>
+          <t>https://m.place.naver.com/place/1228519183</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4664,29 +4616,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>뮤트샵</t>
+          <t>네일, 연</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kimyi95@naver.com</t>
+          <t>wlsl9169@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>031-607-0069</t>
+          <t>0507-1400-3992</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 1층 134호</t>
+          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 1층 107호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://instagram.com/_muteshop</t>
+          <t>https://www.instagram.com/nailyeon_?igsh=MXAxdWN4M2I1ZHRldQ==</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4721,13 +4673,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1018</v>
+        <v>226</v>
       </c>
       <c r="Q46" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="R46" t="n">
-        <v>1089</v>
+        <v>256</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4736,17 +4688,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>37883447</t>
+          <t>1232273978</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37883447</t>
+          <t>https://m.place.naver.com/place/1232273978</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4758,29 +4710,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>코코네일</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>jjuahlee@naver.com</t>
-        </is>
-      </c>
+          <t>띠어리네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1403-3341</t>
+          <t>0507-1314-1851</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
+          <t>경기도 성남시 분당구 돌마로 68 1층 107호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/theorynail</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4790,7 +4738,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4811,17 +4759,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1036</v>
+        <v>984</v>
       </c>
       <c r="Q47" t="n">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="R47" t="n">
-        <v>1157</v>
+        <v>1206</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4830,17 +4778,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>37870150</t>
+          <t>1230407614</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870150</t>
+          <t>https://m.place.naver.com/place/1230407614</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4852,25 +4800,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>라이티티아네일</t>
+          <t>레푸스 판교점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>laetitia5980@naver.com</t>
+          <t>yedamcp@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>031-702-8870</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
+          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/laetitia_nail_j</t>
+          <t>https://blog.naver.com/yedamcp</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4885,7 +4837,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4905,13 +4857,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>156</v>
+        <v>1378</v>
       </c>
       <c r="Q48" t="n">
-        <v>101</v>
+        <v>568</v>
       </c>
       <c r="R48" t="n">
-        <v>257</v>
+        <v>1946</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4920,17 +4872,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1418162766</t>
+          <t>1710320799</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418162766</t>
+          <t>https://m.place.naver.com/place/1710320799</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4942,34 +4894,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>위치네일스 판교점</t>
+          <t>온들네일 분당정자점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>witch_nail@naver.com</t>
+          <t>lovmaria@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>031-622-7290</t>
+          <t>0507-1443-7794</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+          <t>경기도 성남시 분당구 느티로 67 1층 104호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>http://pf.kakao.com/_xkxaKin</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4979,7 +4931,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4990,7 +4942,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4999,13 +4951,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>556</v>
+        <v>54</v>
       </c>
       <c r="Q49" t="n">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="R49" t="n">
-        <v>623</v>
+        <v>80</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5014,17 +4966,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1458353971</t>
+          <t>2085728870</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458353971</t>
+          <t>https://m.place.naver.com/place/2085728870</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5036,29 +4988,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>루미네일 수내점</t>
+          <t>메이드마이네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>halobebe@naver.com</t>
+          <t>joololol_@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1445-6255</t>
+          <t>0507-1370-1842</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로165번길 38 청구아파트 상가 601동 125호</t>
+          <t>경기도 성남시 분당구 분당로53번길 14 2층 208호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luminail_bd</t>
+          <t>https://www.instagram.com/made_mynail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5093,13 +5045,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>522</v>
+        <v>252</v>
       </c>
       <c r="Q50" t="n">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="R50" t="n">
-        <v>551</v>
+        <v>410</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5108,17 +5060,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1065650334</t>
+          <t>1528348158</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065650334</t>
+          <t>https://m.place.naver.com/place/1528348158</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5130,34 +5082,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>나는 너의 네일</t>
+          <t>네일드잇</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>boboboc098@naver.com</t>
+          <t>tudougunniang@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0507-1391-8690</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 미금프라자 5층(다이소 바로 옆건물)</t>
+          <t>경기도 성남시 분당구 내정로 172 2층 203호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_Jxahxkxj/friend</t>
+          <t>https://instagram.com/nailedit_mj</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5178,7 +5126,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5187,13 +5135,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>9</v>
+        <v>195</v>
       </c>
       <c r="Q51" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="R51" t="n">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5202,17 +5150,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1174632490</t>
+          <t>37918491</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174632490</t>
+          <t>https://m.place.naver.com/place/37918491</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5224,30 +5172,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>포세타네일</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>achellnet@naver.com</t>
+          <t>milkycoco95@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1365-1483</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
+          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfossetta</t>
+          <t>https://pf.kakao.com/_xnCjDG</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5268,7 +5220,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5277,13 +5229,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R52" t="n">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5292,17 +5244,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1702940792</t>
+          <t>1505688975</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1702940792</t>
+          <t>https://m.place.naver.com/place/1505688975</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5314,29 +5266,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>조이네일</t>
+          <t>서영언니네일 앤 뷰티크 판교점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>aa6364844@naver.com</t>
+          <t>seo0unnienail@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1352-5816</t>
+          <t>0507-1429-9122</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 2층 207호</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aa6364844</t>
+          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5351,7 +5303,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5371,13 +5323,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2329</v>
+        <v>2434</v>
       </c>
       <c r="Q53" t="n">
-        <v>603</v>
+        <v>2342</v>
       </c>
       <c r="R53" t="n">
-        <v>2932</v>
+        <v>4776</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5386,17 +5338,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>37049599</t>
+          <t>1335668367</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37049599</t>
+          <t>https://m.place.naver.com/place/1335668367</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5408,29 +5360,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일발라봄</t>
+          <t>루나네일스튜디오</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>theboni@naver.com</t>
+          <t>seoyan11@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1350-1712</t>
+          <t>0507-1338-3307</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 51 B29호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 12 3층 317, 318호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailballabom</t>
+          <t>https://open.kakao.com/o/sKOPRm0f</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5456,7 +5408,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5465,13 +5417,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="Q54" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="R54" t="n">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5480,17 +5432,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1585268852</t>
+          <t>1892992657</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1585268852</t>
+          <t>https://m.place.naver.com/place/1892992657</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5502,29 +5454,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>하르네일</t>
+          <t>네일드와</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>cxd1000@naver.com</t>
+          <t>gmldo111@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1305-3099</t>
+          <t>0507-1445-1545</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/harr__nail/</t>
+          <t>https://www.instagram.com/nail_de_wa</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5559,13 +5511,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>274</v>
+        <v>721</v>
       </c>
       <c r="Q55" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="R55" t="n">
-        <v>310</v>
+        <v>737</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5574,17 +5526,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2066713618</t>
+          <t>1349678048</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066713618</t>
+          <t>https://m.place.naver.com/place/1349678048</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5596,29 +5548,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>비온빛 네일브라운 분당미금점</t>
+          <t>비벨리</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>nailb1212@naver.com</t>
+          <t>traveltrip11@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1407-1279</t>
+          <t>0507-1371-1908</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 52 2층 203호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbrown_</t>
+          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5653,13 +5605,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>882</v>
+        <v>257</v>
       </c>
       <c r="Q56" t="n">
-        <v>784</v>
+        <v>532</v>
       </c>
       <c r="R56" t="n">
-        <v>1666</v>
+        <v>789</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5668,17 +5620,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1647015847</t>
+          <t>1626230048</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1647015847</t>
+          <t>https://m.place.naver.com/place/1626230048</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5690,29 +5642,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>비벨리</t>
+          <t>헤몬네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>traveltrip11@naver.com</t>
+          <t>barbie7085055@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0507-1371-1908</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+          <t>https://blog.naver.com/barbie7085055</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5727,7 +5675,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5738,7 +5686,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5747,13 +5695,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>257</v>
+        <v>1299</v>
       </c>
       <c r="Q57" t="n">
-        <v>532</v>
+        <v>719</v>
       </c>
       <c r="R57" t="n">
-        <v>789</v>
+        <v>2018</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5762,17 +5710,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1626230048</t>
+          <t>1117775011</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626230048</t>
+          <t>https://m.place.naver.com/place/1117775011</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5784,29 +5732,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>다다네일</t>
+          <t>유리네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>tykd2048@naver.com</t>
+          <t>sfsf0525@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1466-3338</t>
+          <t>0507-1310-6342</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
+          <t>경기도 성남시 분당구 성남대로 51 분당포스빌 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada.nail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5816,7 +5764,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5837,17 +5785,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>441</v>
+        <v>198</v>
       </c>
       <c r="Q58" t="n">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="R58" t="n">
-        <v>511</v>
+        <v>314</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5856,17 +5804,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>240537974</t>
+          <t>37638489</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/240537974</t>
+          <t>https://m.place.naver.com/place/37638489</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5878,29 +5826,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>안녕,예쁜손</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>bbolm@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1429-8836</t>
+          <t>0507-1403-3341</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
+          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hello_jininail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5910,7 +5858,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5931,17 +5879,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>885</v>
+        <v>1037</v>
       </c>
       <c r="Q59" t="n">
-        <v>258</v>
+        <v>121</v>
       </c>
       <c r="R59" t="n">
-        <v>1143</v>
+        <v>1158</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5950,17 +5898,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>13399185</t>
+          <t>37870150</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13399185</t>
+          <t>https://m.place.naver.com/place/37870150</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5972,29 +5920,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>라모르뷰티 분당수내 본점</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>lamour11@naver.com</t>
-        </is>
-      </c>
+          <t>바이뮤즈</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1465-5979</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
+          <t>경기도 성남시 분당구 정자일로 121 1층 C 10-1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://instagram.com/lamour.nail</t>
+          <t>http://instagram.com/_bymuse_</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6029,13 +5969,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>264</v>
+        <v>443</v>
       </c>
       <c r="Q60" t="n">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="R60" t="n">
-        <v>345</v>
+        <v>499</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6044,17 +5984,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1397181784</t>
+          <t>1198012559</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397181784</t>
+          <t>https://m.place.naver.com/place/1198012559</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6066,34 +6006,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>루나네일스튜디오</t>
+          <t>포세타네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>seoyan11@naver.com</t>
+          <t>achellnet@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0507-1338-3307</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 3층 317, 318호</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sKOPRm0f</t>
+          <t>https://www.instagram.com/nailfossetta</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6114,7 +6050,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6123,13 +6059,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="Q61" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>204</v>
+        <v>86</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,17 +6074,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1892992657</t>
+          <t>1702940792</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892992657</t>
+          <t>https://m.place.naver.com/place/1702940792</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6160,29 +6096,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일604</t>
+          <t>827네일 분당미금점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>esb2967@naver.com</t>
+          <t>827nail@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1327-5862</t>
+          <t>0507-1308-0827</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 20 노블리치오피스텔 A동208호</t>
+          <t>경기도 성남시 분당구 성남대로144번길 16 1층 827네일</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail604_ss</t>
+          <t>http://www.instagram.com/827nail</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6217,13 +6153,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1554</v>
+        <v>2524</v>
       </c>
       <c r="Q62" t="n">
-        <v>39</v>
+        <v>384</v>
       </c>
       <c r="R62" t="n">
-        <v>1593</v>
+        <v>2908</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6232,17 +6168,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1789988736</t>
+          <t>1290037889</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1789988736</t>
+          <t>https://m.place.naver.com/place/1290037889</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6254,29 +6190,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>트리나네일</t>
+          <t>조이네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>treenanail@naver.com</t>
+          <t>aa6364844@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1361-6532</t>
+          <t>0507-1352-5816</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 2층 207호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/tree_na_nail</t>
+          <t>https://blog.naver.com/aa6364844</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6291,7 +6227,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6311,13 +6247,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1159</v>
+        <v>2330</v>
       </c>
       <c r="Q63" t="n">
-        <v>95</v>
+        <v>603</v>
       </c>
       <c r="R63" t="n">
-        <v>1254</v>
+        <v>2933</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,17 +6262,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1331495059</t>
+          <t>37049599</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331495059</t>
+          <t>https://m.place.naver.com/place/37049599</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6348,25 +6284,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>언투네일</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>언니네네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>fuddl3318@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1346-4298</t>
+          <t>0507-1378-0725</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 방아로 25 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로 170 한국프라자 1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/untonail_?igsh=MXI0ejlrc3FkOGNvcA%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6376,7 +6316,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6397,17 +6337,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>90</v>
+        <v>406</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>187</v>
       </c>
       <c r="R64" t="n">
-        <v>98</v>
+        <v>593</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6416,17 +6356,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1449565892</t>
+          <t>37554011</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1449565892</t>
+          <t>https://m.place.naver.com/place/37554011</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6438,25 +6378,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>띠어리네일</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>네일인90</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>nailin90@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1314-1851</t>
+          <t>0507-1331-0990</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 68 1층 107호</t>
+          <t>경기도 성남시 분당구 성남대로925번길 16 성남분당여객자동차터미널 2층 네일인90</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/theorynail</t>
+          <t>https://www.instagram.com/nail_in90</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6491,13 +6435,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>984</v>
+        <v>1155</v>
       </c>
       <c r="Q65" t="n">
-        <v>222</v>
+        <v>53</v>
       </c>
       <c r="R65" t="n">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6506,17 +6450,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1230407614</t>
+          <t>1354180497</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230407614</t>
+          <t>https://m.place.naver.com/place/1354180497</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6528,25 +6472,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>뮤요네일</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>네일다움 내성발톱 무좀 발각질 네일 문제성발 디톡스족욕</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>nail_dawoom@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1389-6160</t>
+          <t>0507-1483-9994</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
+          <t>경기도 성남시 분당구 돌마로 85 동양프라자 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/foot_naildawoom</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6581,13 +6529,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>316</v>
+        <v>632</v>
       </c>
       <c r="Q66" t="n">
-        <v>18</v>
+        <v>391</v>
       </c>
       <c r="R66" t="n">
-        <v>334</v>
+        <v>1023</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6596,17 +6544,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1549676698</t>
+          <t>1587982343</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549676698</t>
+          <t>https://m.place.naver.com/place/1587982343</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6618,34 +6566,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>쏘굿네일 분당미금점</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>sohyun1304@naver.com</t>
-        </is>
-      </c>
+          <t>어도어네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1427-2394</t>
+          <t>0507-1391-6431</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 73 우방코아 2층 211호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 8 킨스타워 3층 311호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/sso_good_nail</t>
+          <t>https://www.instagram.com/adorenail__?igsh=MThpanMxYXA3a2M1aA==</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6655,7 +6599,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6675,13 +6619,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1410</v>
+        <v>158</v>
       </c>
       <c r="Q67" t="n">
-        <v>390</v>
+        <v>39</v>
       </c>
       <c r="R67" t="n">
-        <v>1800</v>
+        <v>197</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6690,17 +6634,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1235289874</t>
+          <t>1011483246</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1235289874</t>
+          <t>https://m.place.naver.com/place/1011483246</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6712,21 +6656,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일아르떼</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>버베인네일 분당수내점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>llltwjhlll@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1375-0335</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nail.arte/</t>
+          <t>https://blog.naver.com/llltwjhlll</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6741,7 +6693,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6761,13 +6713,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>474</v>
+        <v>54</v>
       </c>
       <c r="Q68" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="R68" t="n">
-        <v>511</v>
+        <v>85</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6776,17 +6728,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1010349043</t>
+          <t>2016496556</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010349043</t>
+          <t>https://m.place.naver.com/place/2016496556</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6798,29 +6750,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일인90</t>
+          <t>보니타네일 더푸스프로</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>nailin90@naver.com</t>
+          <t>klsh012@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1331-0990</t>
+          <t>0507-1327-4406</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로925번길 16 성남분당여객자동차터미널 2층 네일인90</t>
+          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 지하1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_in90</t>
+          <t>http://instagram.com/bonita_sohe_e</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6855,13 +6807,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1155</v>
+        <v>636</v>
       </c>
       <c r="Q69" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R69" t="n">
-        <v>1208</v>
+        <v>688</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6870,17 +6822,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1354180497</t>
+          <t>1005133986</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354180497</t>
+          <t>https://m.place.naver.com/place/1005133986</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6892,21 +6844,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>마틸다네일M 분당점</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>후와네일</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>kimnk980409@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1342-1792</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-13 3층 301호</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/matilda_nailshop</t>
+          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6941,13 +6901,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>149</v>
+        <v>447</v>
       </c>
       <c r="Q70" t="n">
-        <v>1308</v>
+        <v>18</v>
       </c>
       <c r="R70" t="n">
-        <v>1457</v>
+        <v>465</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6956,17 +6916,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1714191610</t>
+          <t>1782262137</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1714191610</t>
+          <t>https://m.place.naver.com/place/1782262137</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6978,25 +6938,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>보니타네일 더푸스프로</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>네일보담</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1327-4406</t>
+          <t>0507-1344-9616</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로926번길 12 금탑프라자 103호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://instagram.com/bonita_sohe_e</t>
+          <t>https://www.instagram.com/nail_bodam/?r=nametag</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7022,7 +6986,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7031,13 +6995,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>635</v>
+        <v>297</v>
       </c>
       <c r="Q71" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="R71" t="n">
-        <v>687</v>
+        <v>336</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7046,17 +7010,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1005133986</t>
+          <t>1229535513</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005133986</t>
+          <t>https://m.place.naver.com/place/1229535513</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7068,30 +7032,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>뮤네일</t>
+          <t>언투네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1474-1789</t>
+          <t>0507-1346-4298</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로925번길 19 5층 501-2호</t>
+          <t>경기도 성남시 분당구 방아로 25 지하1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fxizxcxj</t>
+          <t>https://www.instagram.com/untonail_?igsh=MXI0ejlrc3FkOGNvcA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7112,7 +7076,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7121,13 +7085,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>233</v>
+        <v>90</v>
       </c>
       <c r="Q72" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="R72" t="n">
-        <v>259</v>
+        <v>98</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7136,17 +7100,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1325100624</t>
+          <t>1449565892</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325100624</t>
+          <t>https://m.place.naver.com/place/1449565892</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7158,30 +7122,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>온들네일 분당정자점</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>쏘굿네일 분당미금점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sohyun1304@naver.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1443-7794</t>
+          <t>0507-1427-2394</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 67 1층 104호</t>
+          <t>경기도 성남시 분당구 돌마로 73 우방코아 2층 211호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkxaKin</t>
+          <t>http://www.instagram.com/sso_good_nail</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7202,7 +7170,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7211,13 +7179,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>54</v>
+        <v>1411</v>
       </c>
       <c r="Q73" t="n">
-        <v>26</v>
+        <v>390</v>
       </c>
       <c r="R73" t="n">
-        <v>80</v>
+        <v>1801</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7226,17 +7194,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2085728870</t>
+          <t>1235289874</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2085728870</t>
+          <t>https://m.place.naver.com/place/1235289874</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7248,25 +7216,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일바이라라</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>루미네일 수내점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>halobebe@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1356-4115</t>
+          <t>0507-1445-6255</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+          <t>경기도 성남시 분당구 내정로165번길 38 청구아파트 상가 601동 125호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbylala.official</t>
+          <t>https://www.instagram.com/luminail_bd</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7301,13 +7273,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>360</v>
+        <v>522</v>
       </c>
       <c r="Q74" t="n">
         <v>29</v>
       </c>
       <c r="R74" t="n">
-        <v>389</v>
+        <v>551</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7316,17 +7288,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1737395332</t>
+          <t>1065650334</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737395332</t>
+          <t>https://m.place.naver.com/place/1065650334</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7338,35 +7310,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>포쉬네일 판교아브뉴프랑점</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>요푸네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>may_12kr@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>031-603-3011</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+          <t>경기도 성남시 분당구 정자일로 158 5층 505호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_YxnRpxj?fbclid=PAAabkExMKD1XfiHVnimpBpaxeFWr-IdBTPk4ssczHjPJqMvRDPWrhZlMlVNY</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7382,22 +7354,22 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>201</v>
+        <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>133</v>
+        <v>11</v>
       </c>
       <c r="R75" t="n">
-        <v>334</v>
+        <v>13</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7406,17 +7378,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>38258395</t>
+          <t>1301522129</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38258395</t>
+          <t>https://m.place.naver.com/place/1301522129</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7428,25 +7400,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>헤몬네일</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>barbie7085055@naver.com</t>
-        </is>
-      </c>
+          <t>네일604</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1327-5862</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
+          <t>경기도 성남시 분당구 성남대로916번길 20 노블리치오피스텔 A동208호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbie7085055</t>
+          <t>https://www.instagram.com/nail604_ss</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7461,7 +7433,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7472,7 +7444,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7481,13 +7453,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1299</v>
+        <v>1556</v>
       </c>
       <c r="Q76" t="n">
-        <v>719</v>
+        <v>39</v>
       </c>
       <c r="R76" t="n">
-        <v>2018</v>
+        <v>1595</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7496,17 +7468,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1117775011</t>
+          <t>1789988736</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117775011</t>
+          <t>https://m.place.naver.com/place/1789988736</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/분당_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/분당_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>레푸스 분당정자점</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>refuss_bundang@naver.com</t>
-        </is>
-      </c>
+          <t>네일포엠</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-709-8870</t>
+          <t>0507-1381-1685</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 3층 304호</t>
+          <t>경기도 성남시 분당구 성남대로 295 대림아크로텔 c동 129호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refuss_bundang</t>
+          <t>http://instagram.com/nail_poem</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +608,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1039</v>
+        <v>77</v>
       </c>
       <c r="Q2" t="n">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="R2" t="n">
-        <v>1171</v>
+        <v>98</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1293054958</t>
+          <t>1373998196</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293054958</t>
+          <t>https://m.place.naver.com/place/1373998196</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,30 +654,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>uijn_dd@naver.com</t>
-        </is>
-      </c>
+          <t>비비네일</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1365-1483</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
+          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cherryshbeauty_official</t>
+          <t>https://pf.kakao.com/_xnCjDG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -702,7 +698,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -711,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1079</v>
+        <v>107</v>
       </c>
       <c r="Q3" t="n">
-        <v>524</v>
+        <v>38</v>
       </c>
       <c r="R3" t="n">
-        <v>1603</v>
+        <v>145</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +722,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>36524000</t>
+          <t>1505688975</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36524000</t>
+          <t>https://m.place.naver.com/place/1505688975</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,29 +744,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비온빛 네일브라운 분당미금점</t>
+          <t>포쉬네일 AK분당점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nailb1212@naver.com</t>
+          <t>woosy0225@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1407-1279</t>
+          <t>0507-1416-2324</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 52 2층 203호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbrown_</t>
+          <t>https://www.instagram.com/forsynail_footcare</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>882</v>
+        <v>681</v>
       </c>
       <c r="Q4" t="n">
-        <v>784</v>
+        <v>58</v>
       </c>
       <c r="R4" t="n">
-        <v>1666</v>
+        <v>739</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1647015847</t>
+          <t>1692272902</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1647015847</t>
+          <t>https://m.place.naver.com/place/1692272902</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -842,12 +838,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>라이티티아네일</t>
+          <t>더블트리</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>laetitia5980@naver.com</t>
+          <t>doubletree-lash@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -855,12 +851,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/laetitia_nail_j</t>
+          <t>http://instagram.com/doubletree_nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,13 +891,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="Q5" t="n">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>257</v>
+        <v>152</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +906,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1418162766</t>
+          <t>32699868</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418162766</t>
+          <t>https://m.place.naver.com/place/32699868</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -932,29 +928,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>알로이네일</t>
+          <t>헤몬네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>aloinail@naver.com</t>
+          <t>barbie7085055@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1448-7808</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 1 코오롱트리플리스1 상가 201호</t>
+          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aloinail</t>
+          <t>https://blog.naver.com/barbie7085055</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,13 +981,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>360</v>
+        <v>1300</v>
       </c>
       <c r="Q6" t="n">
-        <v>58</v>
+        <v>720</v>
       </c>
       <c r="R6" t="n">
-        <v>418</v>
+        <v>2020</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +996,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1956208028</t>
+          <t>1117775011</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956208028</t>
+          <t>https://m.place.naver.com/place/1117775011</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1026,25 +1018,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>백프로네일</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>온들네일 분당정자점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>hyewon3681@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1416-7323</t>
+          <t>0507-1443-7794</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
+          <t>경기도 성남시 분당구 느티로 67 1층 104호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_MgAwxl</t>
+          <t>http://pf.kakao.com/_xkxaKin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1079,13 +1075,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="Q7" t="n">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="R7" t="n">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,17 +1090,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>512636239</t>
+          <t>2085728870</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/512636239</t>
+          <t>https://m.place.naver.com/place/2085728870</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1116,30 +1112,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일포엠</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>다나네일</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>spring7503@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1381-1685</t>
+          <t>0507-1464-0476</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 295 대림아크로텔 c동 129호</t>
+          <t>경기도 성남시 분당구 성남대로 165 2층 218호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_poem</t>
+          <t>http://pf.kakao.com/_FZMiG</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1160,7 +1160,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R8" t="n">
-        <v>98</v>
+        <v>243</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1373998196</t>
+          <t>1679531126</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373998196</t>
+          <t>https://m.place.naver.com/place/1679531126</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1206,39 +1206,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>다나네일</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>spring7503@naver.com</t>
-        </is>
-      </c>
+          <t>언니네네일</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1464-0476</t>
+          <t>0507-1378-0725</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 165 2층 218호</t>
+          <t>경기도 성남시 분당구 성남대로 170 한국프라자 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FZMiG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1254,22 +1250,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>231</v>
+        <v>406</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>187</v>
       </c>
       <c r="R9" t="n">
-        <v>242</v>
+        <v>593</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1278,17 +1274,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1679531126</t>
+          <t>37554011</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679531126</t>
+          <t>https://m.place.naver.com/place/37554011</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1300,29 +1296,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>반디인하우스 큐릭스 분당서현점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>sdfw3t4@naver.com</t>
-        </is>
-      </c>
+          <t>하르네일</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-2111</t>
+          <t>0507-1305-3099</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
+          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sdfw3t4</t>
+          <t>https://www.instagram.com/harr__nail/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1337,7 +1329,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1357,13 +1349,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1105</v>
+        <v>277</v>
       </c>
       <c r="Q10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R10" t="n">
-        <v>1139</v>
+        <v>313</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1372,17 +1364,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1557758291</t>
+          <t>2066713618</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557758291</t>
+          <t>https://m.place.naver.com/place/2066713618</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1394,39 +1386,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일 조안</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>yoj1116kr@naver.com</t>
-        </is>
-      </c>
+          <t>라모르뷰티 분당수내 본점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1369-6361</t>
+          <t>0507-1465-5979</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
+          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>http://instagram.com/lamour.nail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1451,13 +1439,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>328</v>
+        <v>264</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="R11" t="n">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1466,17 +1454,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1520161470</t>
+          <t>1397181784</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520161470</t>
+          <t>https://m.place.naver.com/place/1397181784</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1476,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일발라봄</t>
+          <t>분당 체리쉬뷰티 네일아뜰리에 수내본점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>theboni@naver.com</t>
+          <t>uijn_dd@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1350-1712</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 51 B29호</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 궁전프라자-3 125호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailballabom</t>
+          <t>https://www.instagram.com/cherryshbeauty_official</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1545,13 +1529,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>27</v>
+        <v>1079</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>524</v>
       </c>
       <c r="R12" t="n">
-        <v>41</v>
+        <v>1603</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1560,17 +1544,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1585268852</t>
+          <t>36524000</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1585268852</t>
+          <t>https://m.place.naver.com/place/36524000</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1582,35 +1566,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>포쉬네일 AK분당점</t>
+          <t>네일 조안</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1416-2324</t>
+          <t>0507-1369-6361</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 42 AK플라자 3층 301호</t>
+          <t>경기도 성남시 분당구 판교공원로2길 40 1층 네일조안</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_footcare</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1635,13 +1619,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>682</v>
+        <v>328</v>
       </c>
       <c r="Q13" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="R13" t="n">
-        <v>741</v>
+        <v>359</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1650,17 +1634,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1692272902</t>
+          <t>1520161470</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692272902</t>
+          <t>https://m.place.naver.com/place/1520161470</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1672,34 +1656,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일오브윤 분당점</t>
+          <t>요푸네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>o___o373@naver.com</t>
+          <t>may_12kr@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1366-7390</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
+          <t>경기도 성남시 분당구 정자일로 158 5층 505호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/o___o373</t>
+          <t>https://pf.kakao.com/_YxnRpxj?fbclid=PAAabkExMKD1XfiHVnimpBpaxeFWr-IdBTPk4ssczHjPJqMvRDPWrhZlMlVNY</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1709,7 +1689,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1720,7 +1700,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1729,13 +1709,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1172</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>921</v>
+        <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>2093</v>
+        <v>13</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1744,17 +1724,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1300308336</t>
+          <t>1301522129</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300308336</t>
+          <t>https://m.place.naver.com/place/1301522129</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1766,34 +1746,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>벨라뷰티</t>
+          <t>르에 판교점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>aqsw0111@naver.com</t>
+          <t>leehhnail@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1391-1078</t>
+          <t>0507-1466-0874</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 158 백궁프라자2 3층 301호</t>
+          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bellabeauty_nail</t>
+          <t>https://link.inpock.co.kr/le.ehh</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1803,7 +1783,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1814,7 +1794,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1823,13 +1803,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>468</v>
+        <v>108</v>
       </c>
       <c r="Q15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R15" t="n">
-        <v>522</v>
+        <v>163</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1838,17 +1818,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1236154271</t>
+          <t>1963747515</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236154271</t>
+          <t>https://m.place.naver.com/place/1963747515</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1860,29 +1840,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>프리미엘네일 분당미금역점</t>
+          <t>알로이네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>premiel__nail@naver.com</t>
+          <t>aloinail@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1362-6250</t>
+          <t>0507-1448-7808</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층 203-1호 프리미엘네일</t>
+          <t>경기도 성남시 분당구 정자일로 1 코오롱트리플리스1 상가 201호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/premiel_nail</t>
+          <t>https://blog.naver.com/aloinail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1897,7 +1877,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1908,7 +1888,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1917,13 +1897,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4217</v>
+        <v>360</v>
       </c>
       <c r="Q16" t="n">
-        <v>324</v>
+        <v>58</v>
       </c>
       <c r="R16" t="n">
-        <v>4541</v>
+        <v>418</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1932,17 +1912,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1105478632</t>
+          <t>1956208028</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105478632</t>
+          <t>https://m.place.naver.com/place/1956208028</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1954,34 +1934,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>뮤네일</t>
+          <t>트리나네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mieux_by_nail@naver.com</t>
+          <t>treenanail@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1474-1789</t>
+          <t>0507-1361-6532</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로925번길 19 5층 501-2호</t>
+          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fxizxcxj</t>
+          <t>http://www.instagram.com/tree_na_nail</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2002,7 +1982,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2011,13 +1991,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>233</v>
+        <v>1159</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="R17" t="n">
-        <v>259</v>
+        <v>1254</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2026,17 +2006,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1325100624</t>
+          <t>1331495059</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325100624</t>
+          <t>https://m.place.naver.com/place/1331495059</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2048,29 +2028,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>라모르뷰티 분당수내 본점</t>
+          <t>솜솜네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>lamour11@naver.com</t>
+          <t>mydbfla33@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1465-5979</t>
+          <t>0507-1416-2241</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로 42 두산위브센티움 2동 2층 라모르뷰티</t>
+          <t>경기도 성남시 분당구 성남대로 51 포스빌 지하1층 50호 솜솜네일</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://instagram.com/lamour.nail</t>
+          <t>https://www.instagram.com/somsomnail_</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2105,13 +2085,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>264</v>
+        <v>405</v>
       </c>
       <c r="Q18" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="R18" t="n">
-        <v>345</v>
+        <v>456</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2120,17 +2100,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1397181784</t>
+          <t>1165691375</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397181784</t>
+          <t>https://m.place.naver.com/place/1165691375</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2142,39 +2122,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>오로지푸스 앤 네일 스파</t>
+          <t>프리미엘네일 분당미금역점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>orosy2020@naver.com</t>
+          <t>premiel__nail@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1382-0859</t>
+          <t>0507-1362-6250</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 304호</t>
+          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 2층 203-1호 프리미엘네일</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/dnrtwwsxK</t>
+          <t>https://www.instagram.com/premiel_nail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2199,13 +2179,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>124</v>
+        <v>4221</v>
       </c>
       <c r="Q19" t="n">
-        <v>116</v>
+        <v>324</v>
       </c>
       <c r="R19" t="n">
-        <v>240</v>
+        <v>4545</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2214,17 +2194,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1948399629</t>
+          <t>1105478632</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948399629</t>
+          <t>https://m.place.naver.com/place/1105478632</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2236,34 +2216,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에러퍼펙트 분당서현점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>jungwonnail@naver.com</t>
-        </is>
-      </c>
+          <t>네일발라봄</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1436-5758</t>
+          <t>0507-1350-1712</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
+          <t>경기도 성남시 분당구 성남대로 51 B29호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jungwonnail?tab=1</t>
+          <t>http://instagram.com/nailballabom</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2293,13 +2269,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1952</v>
+        <v>27</v>
       </c>
       <c r="Q20" t="n">
-        <v>640</v>
+        <v>14</v>
       </c>
       <c r="R20" t="n">
-        <v>2592</v>
+        <v>41</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2308,17 +2284,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1180875815</t>
+          <t>1585268852</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180875815</t>
+          <t>https://m.place.naver.com/place/1585268852</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2330,35 +2306,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>솜솜네일</t>
+          <t>오로지푸스 앤 네일 스파</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1416-2241</t>
+          <t>0507-1382-0859</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 51 포스빌 지하1층 50호 솜솜네일</t>
+          <t>경기도 성남시 분당구 느티로 16 304호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/somsomnail_</t>
+          <t>https://toss.place/_lb/dnrtwwsxK</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2383,13 +2359,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>405</v>
+        <v>124</v>
       </c>
       <c r="Q21" t="n">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="R21" t="n">
-        <v>456</v>
+        <v>240</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2398,17 +2374,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1165691375</t>
+          <t>1948399629</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165691375</t>
+          <t>https://m.place.naver.com/place/1948399629</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2420,29 +2396,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>하낭네일스튜디오</t>
+          <t>라이티티아네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>senniverse@naver.com</t>
+          <t>laetitia5980@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0507-1322-5647</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 73 현대 빌딩 2층 204호</t>
+          <t>경기도 성남시 분당구 정자일로 220 동양정자파라곤 2단지상가 104호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ha.nang_nail_studio?igsh=MTR4anJrZW8yN3M4eA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/laetitia_nail_j</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2477,13 +2449,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>584</v>
+        <v>156</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="R22" t="n">
-        <v>595</v>
+        <v>257</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2464,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1339933062</t>
+          <t>1418162766</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1339933062</t>
+          <t>https://m.place.naver.com/place/1418162766</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2514,21 +2486,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일그자체</t>
+          <t>루미네일 수내점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1445-6255</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
+          <t>경기도 성남시 분당구 내정로165번길 38 청구아파트 상가 601동 125호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_itself</t>
+          <t>https://www.instagram.com/luminail_bd</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2563,13 +2539,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>169</v>
+        <v>522</v>
       </c>
       <c r="Q23" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R23" t="n">
-        <v>192</v>
+        <v>551</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2578,17 +2554,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2089755300</t>
+          <t>1065650334</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089755300</t>
+          <t>https://m.place.naver.com/place/1065650334</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2600,26 +2576,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>러브엘네일</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>반디인하우스 큐릭스 분당서현점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sdfw3t4@naver.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1359-2111</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 513-1호 5층 내려서 바로 왼쪽 입니다 :)</t>
+          <t>경기도 성남시 분당구 분당로53번길 21 2층 210호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhRYWn</t>
+          <t>https://blog.naver.com/sdfw3t4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2629,7 +2613,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2640,7 +2624,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2649,13 +2633,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>247</v>
+        <v>1105</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="R24" t="n">
-        <v>254</v>
+        <v>1139</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2664,17 +2648,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2023334466</t>
+          <t>1557758291</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023334466</t>
+          <t>https://m.place.naver.com/place/1557758291</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2686,25 +2670,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>안녕,예쁜손</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>네일오브윤 분당점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>o___o373@naver.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1429-8836</t>
+          <t>0507-1366-7390</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
+          <t>경기도 성남시 분당구 야탑로69번길 24-8 3층 308호 네일오브윤 분당점</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hello_jininail</t>
+          <t>https://blog.naver.com/o___o373</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2719,7 +2707,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2739,13 +2727,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>887</v>
+        <v>1180</v>
       </c>
       <c r="Q25" t="n">
-        <v>258</v>
+        <v>928</v>
       </c>
       <c r="R25" t="n">
-        <v>1145</v>
+        <v>2108</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2754,17 +2742,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>13399185</t>
+          <t>1300308336</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13399185</t>
+          <t>https://m.place.naver.com/place/1300308336</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2776,29 +2764,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>포쉬네일 판교아브뉴프랑점</t>
+          <t>모스네일 판교점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>silentforest_studio@naver.com</t>
+          <t>mossnail@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>031-603-3011</t>
+          <t>0507-1317-6311</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
+          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/moss._.nail</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2808,7 +2796,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2829,17 +2817,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>201</v>
+        <v>399</v>
       </c>
       <c r="Q26" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="R26" t="n">
-        <v>334</v>
+        <v>468</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2848,17 +2836,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>38258395</t>
+          <t>1816221132</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38258395</t>
+          <t>https://m.place.naver.com/place/1816221132</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2870,25 +2858,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일바이라라</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>비온빛 네일브라운 분당미금점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>nailb1212@naver.com</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1356-4115</t>
+          <t>0507-1407-1279</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
+          <t>경기도 성남시 분당구 돌마로 52 2층 203호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbylala.official</t>
+          <t>https://www.instagram.com/nailbrown_</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2923,13 +2915,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>360</v>
+        <v>882</v>
       </c>
       <c r="Q27" t="n">
-        <v>29</v>
+        <v>785</v>
       </c>
       <c r="R27" t="n">
-        <v>389</v>
+        <v>1667</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2938,17 +2930,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1737395332</t>
+          <t>1647015847</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737395332</t>
+          <t>https://m.place.naver.com/place/1647015847</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2960,21 +2952,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>마틸다네일M 분당점</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>안녕,예쁜손</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bbolm@naver.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1429-8836</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-13 3층 301호</t>
+          <t>경기도 성남시 분당구 서현로210번길 14 유성트윈프라자2차 4층 안녕,예쁜손</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/matilda_nailshop</t>
+          <t>http://www.instagram.com/hello_jininail</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>149</v>
+        <v>888</v>
       </c>
       <c r="Q28" t="n">
-        <v>1308</v>
+        <v>258</v>
       </c>
       <c r="R28" t="n">
-        <v>1457</v>
+        <v>1146</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1714191610</t>
+          <t>13399185</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1714191610</t>
+          <t>https://m.place.naver.com/place/13399185</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3046,29 +3046,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>모스네일 판교점</t>
+          <t>벨라뷰티</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mossnail@naver.com</t>
+          <t>aqsw0111@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1317-6311</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 1층 1061호 MOSS</t>
+          <t>경기도 성남시 분당구 정자일로 158 백궁프라자2 3층 301호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moss._.nail</t>
+          <t>https://www.instagram.com/bellabeauty_nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3094,7 +3090,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3103,13 +3099,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>397</v>
+        <v>468</v>
       </c>
       <c r="Q29" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="R29" t="n">
-        <v>466</v>
+        <v>523</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3118,17 +3114,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1816221132</t>
+          <t>1236154271</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816221132</t>
+          <t>https://m.place.naver.com/place/1236154271</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3140,29 +3136,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>트리나네일</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>treenanail@naver.com</t>
-        </is>
-      </c>
+          <t>네일바이라라</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1361-6532</t>
+          <t>0507-1356-4115</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 145 알파리움 2동 212호 트리나네일</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층 306호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/tree_na_nail</t>
+          <t>https://www.instagram.com/nailbylala.official</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3197,13 +3189,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1159</v>
+        <v>360</v>
       </c>
       <c r="Q30" t="n">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="R30" t="n">
-        <v>1254</v>
+        <v>389</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3212,17 +3204,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1331495059</t>
+          <t>1737395332</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331495059</t>
+          <t>https://m.place.naver.com/place/1737395332</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3234,34 +3226,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>예쁘게살자</t>
+          <t>뮤네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sukjin1125@naver.com</t>
+          <t>mieux_by_nail@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>031-702-9340</t>
+          <t>0507-1474-1789</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 2층 예쁘게살자</t>
+          <t>경기도 성남시 분당구 성남대로925번길 19 5층 501-2호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sukjin1125</t>
+          <t>http://pf.kakao.com/_fxizxcxj</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3271,7 +3263,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3282,7 +3274,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3291,13 +3283,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>753</v>
+        <v>233</v>
       </c>
       <c r="Q31" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="R31" t="n">
-        <v>794</v>
+        <v>259</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3306,17 +3298,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1221851423</t>
+          <t>1325100624</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1221851423</t>
+          <t>https://m.place.naver.com/place/1325100624</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3328,29 +3320,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>위치네일스 판교점</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>witch_nail@naver.com</t>
-        </is>
-      </c>
+          <t>띠어리네일</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>031-622-7290</t>
+          <t>0507-1314-1851</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
+          <t>경기도 성남시 분당구 돌마로 68 1층 107호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/witch_nail</t>
+          <t>https://www.instagram.com/theorynail</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3365,7 +3353,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3385,13 +3373,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>556</v>
+        <v>985</v>
       </c>
       <c r="Q32" t="n">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="R32" t="n">
-        <v>623</v>
+        <v>1207</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3400,17 +3388,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1458353971</t>
+          <t>1230407614</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458353971</t>
+          <t>https://m.place.naver.com/place/1230407614</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3422,34 +3410,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>르에 판교점</t>
+          <t>비벨리</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>leehhnail@naver.com</t>
+          <t>traveltrip11@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1466-0874</t>
+          <t>0507-1371-1908</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 109 SK HUB 오피스텔 지2층 A동 b206호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/le.ehh</t>
+          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3459,7 +3447,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3479,13 +3467,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="Q33" t="n">
-        <v>55</v>
+        <v>532</v>
       </c>
       <c r="R33" t="n">
-        <v>162</v>
+        <v>789</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3494,17 +3482,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1963747515</t>
+          <t>1626230048</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1963747515</t>
+          <t>https://m.place.naver.com/place/1626230048</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3516,34 +3504,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>하르네일</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>cxd1000@naver.com</t>
-        </is>
-      </c>
+          <t>러브엘네일</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1305-3099</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 판매시설동 1층 1049호(백현동, 힐스테이트판교역 (7-1블럭))</t>
+          <t>경기도 성남시 분당구 돌마로 47 513-1호 5층 내려서 바로 왼쪽 입니다 :)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/harr__nail/</t>
+          <t>http://pf.kakao.com/_xhRYWn</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3564,7 +3544,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3573,13 +3553,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="Q34" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>312</v>
+        <v>253</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3588,17 +3568,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2066713618</t>
+          <t>2023334466</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066713618</t>
+          <t>https://m.place.naver.com/place/2023334466</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3610,25 +3590,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일아르떼</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>tpfla1999@naver.com</t>
-        </is>
-      </c>
+          <t>유리네일</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1310-6342</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
+          <t>경기도 성남시 분당구 성남대로 51 분당포스빌 1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nail.arte/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3638,7 +3618,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3659,17 +3639,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>474</v>
+        <v>199</v>
       </c>
       <c r="Q35" t="n">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="R35" t="n">
-        <v>511</v>
+        <v>315</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3678,17 +3658,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1010349043</t>
+          <t>37638489</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010349043</t>
+          <t>https://m.place.naver.com/place/37638489</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3700,29 +3680,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일팜</t>
+          <t>뮤요네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nailpalm@naver.com</t>
+          <t>rabong1219@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1371-5111</t>
+          <t>0507-1389-6160</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 67 금산젬월드 4층 405호</t>
+          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailpalm</t>
+          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3737,7 +3717,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3757,13 +3737,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>862</v>
+        <v>317</v>
       </c>
       <c r="Q36" t="n">
-        <v>323</v>
+        <v>18</v>
       </c>
       <c r="R36" t="n">
-        <v>1185</v>
+        <v>335</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3772,17 +3752,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>37398310</t>
+          <t>1549676698</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37398310</t>
+          <t>https://m.place.naver.com/place/1549676698</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3794,29 +3774,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일스튜디오미니</t>
+          <t>조이네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>milk924@naver.com</t>
+          <t>aa6364844@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>031-789-3555</t>
+          <t>0507-1352-5816</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
+          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 2층 207호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_mini</t>
+          <t>https://blog.naver.com/aa6364844</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3831,7 +3811,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3851,13 +3831,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>321</v>
+        <v>2330</v>
       </c>
       <c r="Q37" t="n">
-        <v>33</v>
+        <v>603</v>
       </c>
       <c r="R37" t="n">
-        <v>354</v>
+        <v>2933</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3866,17 +3846,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>495440903</t>
+          <t>37049599</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/495440903</t>
+          <t>https://m.place.naver.com/place/37049599</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3888,25 +3868,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>뮤트샵</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>쏘굿네일 분당미금점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sohyun1304@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>031-607-0069</t>
+          <t>0507-1427-2394</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 1층 134호</t>
+          <t>경기도 성남시 분당구 돌마로 73 우방코아 2층 211호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://instagram.com/_muteshop</t>
+          <t>http://www.instagram.com/sso_good_nail</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3941,13 +3925,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1018</v>
+        <v>1412</v>
       </c>
       <c r="Q38" t="n">
-        <v>71</v>
+        <v>390</v>
       </c>
       <c r="R38" t="n">
-        <v>1089</v>
+        <v>1802</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3956,17 +3940,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>37883447</t>
+          <t>1235289874</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37883447</t>
+          <t>https://m.place.naver.com/place/1235289874</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3978,12 +3962,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>더블트리</t>
+          <t>바이뮤즈</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>doubletree-lash@naver.com</t>
+          <t>ynh3377@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3991,12 +3975,12 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 3-7 101호</t>
+          <t>경기도 성남시 분당구 정자일로 121 1층 C 10-1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://instagram.com/doubletree_nail</t>
+          <t>http://instagram.com/_bymuse_</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4031,13 +4015,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>138</v>
+        <v>443</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="R39" t="n">
-        <v>152</v>
+        <v>499</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4046,17 +4030,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>32699868</t>
+          <t>1198012559</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32699868</t>
+          <t>https://m.place.naver.com/place/1198012559</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4068,25 +4052,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>다다네일</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>네일팜</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nailpalm@naver.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1466-3338</t>
+          <t>0507-1371-5111</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
+          <t>경기도 성남시 분당구 돌마로 67 금산젬월드 4층 405호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada.nail/</t>
+          <t>https://blog.naver.com/nailpalm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4101,7 +4089,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4121,13 +4109,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>441</v>
+        <v>862</v>
       </c>
       <c r="Q40" t="n">
-        <v>70</v>
+        <v>323</v>
       </c>
       <c r="R40" t="n">
-        <v>511</v>
+        <v>1185</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4136,17 +4124,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>240537974</t>
+          <t>37398310</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/240537974</t>
+          <t>https://m.place.naver.com/place/37398310</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4158,25 +4146,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일인어스</t>
+          <t>네일보담</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kmj8937@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1344-9616</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
+          <t>경기도 성남시 분당구 성남대로926번길 12 금탑프라자 103호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailinus</t>
+          <t>https://www.instagram.com/nail_bodam/?r=nametag</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4202,7 +4194,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4211,13 +4203,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>635</v>
+        <v>297</v>
       </c>
       <c r="Q41" t="n">
-        <v>163</v>
+        <v>39</v>
       </c>
       <c r="R41" t="n">
-        <v>798</v>
+        <v>336</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4226,17 +4218,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1591004723</t>
+          <t>1229535513</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591004723</t>
+          <t>https://m.place.naver.com/place/1229535513</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4248,29 +4240,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>뮤요네일</t>
+          <t>보니타네일 더푸스프로</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rabong1219@naver.com</t>
+          <t>klsh012@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1389-6160</t>
+          <t>0507-1327-4406</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 332 5층 뮤요네일</t>
+          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 지하1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muyo_nail?igsh=bjFmd2s2cXV5dnE2&amp;utm_source=qr</t>
+          <t>http://instagram.com/bonita_sohe_e</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4305,13 +4297,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>316</v>
+        <v>638</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="R42" t="n">
-        <v>334</v>
+        <v>690</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4320,17 +4312,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1549676698</t>
+          <t>1005133986</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549676698</t>
+          <t>https://m.place.naver.com/place/1005133986</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4342,30 +4334,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>나는 너의 네일</t>
+          <t>루나네일스튜디오</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1391-8690</t>
+          <t>0507-1338-3307</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 미금프라자 5층(다이소 바로 옆건물)</t>
+          <t>경기도 성남시 분당구 황새울로360번길 12 3층 317, 318호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_Jxahxkxj/friend</t>
+          <t>https://open.kakao.com/o/sKOPRm0f</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4395,13 +4387,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>9</v>
+        <v>164</v>
       </c>
       <c r="Q43" t="n">
         <v>40</v>
       </c>
       <c r="R43" t="n">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4410,17 +4402,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1174632490</t>
+          <t>1892992657</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174632490</t>
+          <t>https://m.place.naver.com/place/1892992657</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4432,29 +4424,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>베베네일</t>
+          <t>포세타네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kub1207@naver.com</t>
+          <t>achellnet@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0507-1309-9064</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 3층 308호</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/bebe.nailstudio</t>
+          <t>https://www.instagram.com/nailfossetta</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4489,13 +4477,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>342</v>
+        <v>86</v>
       </c>
       <c r="Q44" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>368</v>
+        <v>86</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4504,17 +4492,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1290736362</t>
+          <t>1702940792</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290736362</t>
+          <t>https://m.place.naver.com/place/1702940792</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4526,30 +4514,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>뽐내 네일</t>
+          <t>위치네일스 판교점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ppomnae369@naver.com</t>
+          <t>witch_nail@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>031-622-7290</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 926 분당메트로 3층 뽐내</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔 타워 3층 7unit호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qgWrG</t>
+          <t>https://blog.naver.com/witch_nail</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4559,7 +4551,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4570,7 +4562,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4579,13 +4571,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>243</v>
+        <v>556</v>
       </c>
       <c r="Q45" t="n">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="R45" t="n">
-        <v>364</v>
+        <v>623</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4594,17 +4586,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1228519183</t>
+          <t>1458353971</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228519183</t>
+          <t>https://m.place.naver.com/place/1458353971</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4616,29 +4608,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일, 연</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>wlsl9169@naver.com</t>
-        </is>
-      </c>
+          <t>뮤트샵</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1400-3992</t>
+          <t>031-607-0069</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 1층 107호</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 1층 134호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailyeon_?igsh=MXAxdWN4M2I1ZHRldQ==</t>
+          <t>http://instagram.com/_muteshop</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4673,13 +4661,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>226</v>
+        <v>1019</v>
       </c>
       <c r="Q46" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="R46" t="n">
-        <v>256</v>
+        <v>1090</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4688,17 +4676,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1232273978</t>
+          <t>37883447</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1232273978</t>
+          <t>https://m.place.naver.com/place/37883447</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4710,25 +4698,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>띠어리네일</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>서영언니네일 앤 뷰티크 판교점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>seo0unnienail@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1314-1851</t>
+          <t>0507-1429-9122</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 68 1층 107호</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/theorynail</t>
+          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4763,13 +4755,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>984</v>
+        <v>2435</v>
       </c>
       <c r="Q47" t="n">
-        <v>222</v>
+        <v>2343</v>
       </c>
       <c r="R47" t="n">
-        <v>1206</v>
+        <v>4778</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4778,17 +4770,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1230407614</t>
+          <t>1335668367</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230407614</t>
+          <t>https://m.place.naver.com/place/1335668367</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4800,29 +4792,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>레푸스 판교점</t>
+          <t>메이드마이네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>yedamcp@naver.com</t>
+          <t>joololol_@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>031-702-8870</t>
+          <t>0507-1370-1842</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
+          <t>경기도 성남시 분당구 분당로53번길 14 2층 208호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yedamcp</t>
+          <t>https://www.instagram.com/made_mynail</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4837,7 +4829,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4857,13 +4849,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1378</v>
+        <v>252</v>
       </c>
       <c r="Q48" t="n">
-        <v>568</v>
+        <v>158</v>
       </c>
       <c r="R48" t="n">
-        <v>1946</v>
+        <v>410</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4872,17 +4864,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1710320799</t>
+          <t>1528348158</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710320799</t>
+          <t>https://m.place.naver.com/place/1528348158</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4894,29 +4886,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>온들네일 분당정자점</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>lovmaria@naver.com</t>
-        </is>
-      </c>
+          <t>스너그네일하우스</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1443-7794</t>
+          <t>0507-1487-2471</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 67 1층 104호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 22 (서현동247-1) 영건프라자 3층 스너그네일하우스</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkxaKin</t>
+          <t>http://pf.kakao.com/_xbuTbn</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4951,13 +4939,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>54</v>
+        <v>411</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="R49" t="n">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4966,17 +4954,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2085728870</t>
+          <t>1529600110</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2085728870</t>
+          <t>https://m.place.naver.com/place/1529600110</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4988,34 +4976,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>메이드마이네일</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>joololol_@naver.com</t>
-        </is>
-      </c>
+          <t>나는 너의 네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1370-1842</t>
+          <t>0507-1391-8690</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 14 2층 208호</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 5층(다이소 바로 옆건물)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/made_mynail</t>
+          <t>https://pf.kakao.com/_Jxahxkxj/friend</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5036,7 +5020,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5045,13 +5029,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>252</v>
+        <v>9</v>
       </c>
       <c r="Q50" t="n">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="R50" t="n">
-        <v>410</v>
+        <v>49</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5060,17 +5044,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1528348158</t>
+          <t>1174632490</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1528348158</t>
+          <t>https://m.place.naver.com/place/1174632490</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5082,25 +5066,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일드잇</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>tudougunniang@naver.com</t>
-        </is>
-      </c>
+          <t>손을그리다</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>031-704-1009</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로 172 2층 203호</t>
+          <t>경기도 성남시 분당구 산운로160번길 20 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://instagram.com/nailedit_mj</t>
+          <t>https://www.instagram.com/drawhand_nail/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5135,13 +5119,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>195</v>
+        <v>71</v>
       </c>
       <c r="Q51" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="R51" t="n">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5150,17 +5134,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>37918491</t>
+          <t>36398915</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37918491</t>
+          <t>https://m.place.naver.com/place/36398915</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5172,34 +5156,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>레푸스 분당정자점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>refuss_bundang@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1365-1483</t>
+          <t>031-709-8870</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 블루존 지하1층 B1012</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 3층 304호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnCjDG</t>
+          <t>https://blog.naver.com/refuss_bundang</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5209,7 +5193,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5229,13 +5213,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>107</v>
+        <v>1041</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="R52" t="n">
-        <v>145</v>
+        <v>1174</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5244,17 +5228,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1505688975</t>
+          <t>1293054958</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505688975</t>
+          <t>https://m.place.naver.com/place/1293054958</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5266,29 +5250,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>서영언니네일 앤 뷰티크 판교점</t>
+          <t>네일스튜디오미니</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>seo0unnienail@naver.com</t>
+          <t>milk924@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1429-9122</t>
+          <t>031-789-3555</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2, 604호</t>
+          <t>경기도 성남시 분당구 판교역로 231 201호 네일스튜디오미니</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/seo0unnienail_pangyo/</t>
+          <t>http://www.instagram.com/nail_mini</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5323,13 +5307,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2434</v>
+        <v>323</v>
       </c>
       <c r="Q53" t="n">
-        <v>2342</v>
+        <v>33</v>
       </c>
       <c r="R53" t="n">
-        <v>4776</v>
+        <v>356</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5338,17 +5322,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1335668367</t>
+          <t>495440903</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335668367</t>
+          <t>https://m.place.naver.com/place/495440903</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5360,29 +5344,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>루나네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>seoyan11@naver.com</t>
-        </is>
-      </c>
+          <t>후와네일</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1338-3307</t>
+          <t>0507-1342-1792</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 12 3층 317, 318호</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sKOPRm0f</t>
+          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5408,7 +5388,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5417,13 +5397,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>164</v>
+        <v>447</v>
       </c>
       <c r="Q54" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="R54" t="n">
-        <v>204</v>
+        <v>465</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5432,17 +5412,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1892992657</t>
+          <t>1782262137</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892992657</t>
+          <t>https://m.place.naver.com/place/1782262137</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5454,29 +5434,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일드와</t>
+          <t>다다네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>gmldo111@naver.com</t>
+          <t>tykd2048@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1445-1545</t>
+          <t>0507-1466-3338</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스 705호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_wa</t>
+          <t>https://www.instagram.com/dada.nail/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5511,13 +5491,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>721</v>
+        <v>443</v>
       </c>
       <c r="Q55" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="R55" t="n">
-        <v>737</v>
+        <v>513</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5526,17 +5506,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1349678048</t>
+          <t>240537974</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349678048</t>
+          <t>https://m.place.naver.com/place/240537974</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5548,29 +5528,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>비벨리</t>
+          <t>827네일 분당미금점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>traveltrip11@naver.com</t>
+          <t>827nail@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1371-1908</t>
+          <t>0507-1308-0827</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 43 4층 비벨리</t>
+          <t>경기도 성남시 분당구 성남대로144번길 16 1층 827네일</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://instagram.com/bbely_official?igshid=sbg5oe7juva8</t>
+          <t>http://www.instagram.com/827nail</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5605,13 +5585,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>257</v>
+        <v>2525</v>
       </c>
       <c r="Q56" t="n">
-        <v>532</v>
+        <v>385</v>
       </c>
       <c r="R56" t="n">
-        <v>789</v>
+        <v>2910</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5620,17 +5600,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1626230048</t>
+          <t>1290037889</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626230048</t>
+          <t>https://m.place.naver.com/place/1290037889</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5642,30 +5622,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>헤몬네일</t>
+          <t>네일비</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>barbie7085055@naver.com</t>
+          <t>panic9861@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1412-7076</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 10 2층</t>
+          <t>경기도 성남시 분당구 발이봉남로 16 1층 102호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbie7085055</t>
+          <t>http://pf.kakao.com/_TxkQxon</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5675,7 +5659,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5695,13 +5679,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1299</v>
+        <v>39</v>
       </c>
       <c r="Q57" t="n">
-        <v>719</v>
+        <v>9</v>
       </c>
       <c r="R57" t="n">
-        <v>2018</v>
+        <v>48</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5710,17 +5694,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1117775011</t>
+          <t>2039025978</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117775011</t>
+          <t>https://m.place.naver.com/place/2039025978</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5732,29 +5716,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>유리네일</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>sfsf0525@naver.com</t>
-        </is>
-      </c>
+          <t>언투네일</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1310-6342</t>
+          <t>0507-1346-4298</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 51 분당포스빌 1층</t>
+          <t>경기도 성남시 분당구 방아로 25 지하1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/untonail_?igsh=MXI0ejlrc3FkOGNvcA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5764,7 +5744,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5785,17 +5765,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>198</v>
+        <v>90</v>
       </c>
       <c r="Q58" t="n">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="R58" t="n">
-        <v>314</v>
+        <v>98</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5804,17 +5784,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>37638489</t>
+          <t>1449565892</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37638489</t>
+          <t>https://m.place.naver.com/place/1449565892</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5826,29 +5806,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>코코네일</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>jjuahlee@naver.com</t>
-        </is>
-      </c>
+          <t>네일드잇</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0507-1403-3341</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
+          <t>경기도 성남시 분당구 내정로 172 2층 203호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/nailedit_mj</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5858,7 +5830,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5879,17 +5851,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1037</v>
+        <v>195</v>
       </c>
       <c r="Q59" t="n">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="R59" t="n">
-        <v>1158</v>
+        <v>229</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5898,17 +5870,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>37870150</t>
+          <t>37918491</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870150</t>
+          <t>https://m.place.naver.com/place/37918491</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5920,21 +5892,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>바이뮤즈</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>네일인90</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>nailin90@naver.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1331-0990</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 1층 C 10-1</t>
+          <t>경기도 성남시 분당구 성남대로925번길 16 성남분당여객자동차터미널 2층 네일인90</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://instagram.com/_bymuse_</t>
+          <t>https://www.instagram.com/nail_in90</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5969,13 +5949,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>443</v>
+        <v>1156</v>
       </c>
       <c r="Q60" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R60" t="n">
-        <v>499</v>
+        <v>1209</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5984,17 +5964,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1198012559</t>
+          <t>1354180497</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198012559</t>
+          <t>https://m.place.naver.com/place/1354180497</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6006,25 +5986,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>포세타네일</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>achellnet@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1403-3341</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 2층</t>
+          <t>경기도 성남시 분당구 느티로 16 정자동 젤존타워1차 408호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfossetta</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6034,7 +6018,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6055,17 +6039,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>86</v>
+        <v>1037</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="R61" t="n">
-        <v>86</v>
+        <v>1159</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6074,17 +6058,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1702940792</t>
+          <t>37870150</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1702940792</t>
+          <t>https://m.place.naver.com/place/37870150</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6096,29 +6080,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>827네일 분당미금점</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>827nail@naver.com</t>
-        </is>
-      </c>
+          <t>포쉬네일 판교아브뉴프랑점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1308-0827</t>
+          <t>031-603-3011</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로144번길 16 1층 827네일</t>
+          <t>경기도 성남시 분당구 동판교로177번길 25 아브뉴프랑 146호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/827nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6128,7 +6108,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6149,17 +6129,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2524</v>
+        <v>201</v>
       </c>
       <c r="Q62" t="n">
-        <v>384</v>
+        <v>133</v>
       </c>
       <c r="R62" t="n">
-        <v>2908</v>
+        <v>334</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6168,17 +6148,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1290037889</t>
+          <t>38258395</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290037889</t>
+          <t>https://m.place.naver.com/place/38258395</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6190,34 +6170,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>조이네일</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>aa6364844@naver.com</t>
-        </is>
-      </c>
+          <t>백프로네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1352-5816</t>
+          <t>0507-1416-7323</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 2층 207호</t>
+          <t>경기도 성남시 분당구 분당내곡로 159 kcc 웰츠타워 A동 124호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aa6364844</t>
+          <t>https://pf.kakao.com/_MgAwxl</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6227,7 +6203,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6238,7 +6214,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6247,13 +6223,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2330</v>
+        <v>66</v>
       </c>
       <c r="Q63" t="n">
-        <v>603</v>
+        <v>118</v>
       </c>
       <c r="R63" t="n">
-        <v>2933</v>
+        <v>184</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6262,17 +6238,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>37049599</t>
+          <t>512636239</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37049599</t>
+          <t>https://m.place.naver.com/place/512636239</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6284,29 +6260,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>언니네네일</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>fuddl3318@naver.com</t>
-        </is>
-      </c>
+          <t>네일신 판교점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1378-0725</t>
+          <t>031-708-4142</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 170 한국프라자 1층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 1층 48호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailshin_/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6316,7 +6288,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6337,17 +6309,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>406</v>
+        <v>234</v>
       </c>
       <c r="Q64" t="n">
-        <v>187</v>
+        <v>39</v>
       </c>
       <c r="R64" t="n">
-        <v>593</v>
+        <v>273</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6356,17 +6328,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>37554011</t>
+          <t>1768463815</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37554011</t>
+          <t>https://m.place.naver.com/place/1768463815</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6378,29 +6350,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일인90</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>nailin90@naver.com</t>
-        </is>
-      </c>
+          <t>네일, 연</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1331-0990</t>
+          <t>0507-1400-3992</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로925번길 16 성남분당여객자동차터미널 2층 네일인90</t>
+          <t>경기도 성남시 분당구 야탑로 95 세신빌딩 1층 107호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_in90</t>
+          <t>https://www.instagram.com/nailyeon_?igsh=MXAxdWN4M2I1ZHRldQ==</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6435,13 +6403,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1155</v>
+        <v>226</v>
       </c>
       <c r="Q65" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="R65" t="n">
-        <v>1208</v>
+        <v>256</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6450,17 +6418,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1354180497</t>
+          <t>1232273978</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354180497</t>
+          <t>https://m.place.naver.com/place/1232273978</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6472,29 +6440,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일다움 내성발톱 무좀 발각질 네일 문제성발 디톡스족욕</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>nail_dawoom@naver.com</t>
-        </is>
-      </c>
+          <t>네일인어스</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0507-1483-9994</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 85 동양프라자 4층</t>
+          <t>경기도 성남시 분당구 서현로210번길 16 3층 306호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/foot_naildawoom</t>
+          <t>https://www.instagram.com/nailinus</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6529,13 +6489,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="Q66" t="n">
-        <v>391</v>
+        <v>163</v>
       </c>
       <c r="R66" t="n">
-        <v>1023</v>
+        <v>799</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6544,17 +6504,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1587982343</t>
+          <t>1591004723</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1587982343</t>
+          <t>https://m.place.naver.com/place/1591004723</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6566,25 +6526,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>어도어네일스튜디오</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>네일604</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>esb2967@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1391-6431</t>
+          <t>0507-1327-5862</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 8 킨스타워 3층 311호</t>
+          <t>경기도 성남시 분당구 성남대로916번길 20 노블리치오피스텔 A동208호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/adorenail__?igsh=MThpanMxYXA3a2M1aA==</t>
+          <t>https://www.instagram.com/nail604_ss</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6619,13 +6583,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>158</v>
+        <v>1562</v>
       </c>
       <c r="Q67" t="n">
         <v>39</v>
       </c>
       <c r="R67" t="n">
-        <v>197</v>
+        <v>1601</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6634,17 +6598,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1011483246</t>
+          <t>1789988736</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1011483246</t>
+          <t>https://m.place.naver.com/place/1789988736</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6656,29 +6620,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>버베인네일 분당수내점</t>
+          <t>레푸스 판교점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>llltwjhlll@naver.com</t>
+          <t>yedamcp@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1375-0335</t>
+          <t>031-702-8870</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 3층 301-1호</t>
+          <t>경기도 성남시 분당구 분당내곡로 151 삼도타워 3층 304호 레푸스 판교점</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/llltwjhlll</t>
+          <t>https://blog.naver.com/yedamcp</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6713,13 +6677,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>54</v>
+        <v>1382</v>
       </c>
       <c r="Q68" t="n">
-        <v>31</v>
+        <v>568</v>
       </c>
       <c r="R68" t="n">
-        <v>85</v>
+        <v>1950</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6728,17 +6692,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2016496556</t>
+          <t>1710320799</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016496556</t>
+          <t>https://m.place.naver.com/place/1710320799</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6750,29 +6714,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>보니타네일 더푸스프로</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>klsh012@naver.com</t>
-        </is>
-      </c>
+          <t>네일아르떼</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0507-1327-4406</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 11-15 봉우빌딩 지하1층</t>
+          <t>경기도 성남시 분당구 황새울로360번길 12 4층 네일아르떼</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://instagram.com/bonita_sohe_e</t>
+          <t>https://www.instagram.com/__nail.arte/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6807,13 +6763,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>636</v>
+        <v>475</v>
       </c>
       <c r="Q69" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="R69" t="n">
-        <v>688</v>
+        <v>512</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6822,17 +6778,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1005133986</t>
+          <t>1010349043</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005133986</t>
+          <t>https://m.place.naver.com/place/1010349043</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6844,29 +6800,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>후와네일</t>
+          <t>에러퍼펙트 분당서현점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>kimnk980409@naver.com</t>
+          <t>jungwonnail@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1342-1792</t>
+          <t>0507-1436-5758</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 1층 119호</t>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 302호 에러퍼펙트 서현점</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com//whowa_nail?igsh=MXd2NXdlamZxM28xMA%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/jungwonnail?tab=1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6881,7 +6837,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6901,13 +6857,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>447</v>
+        <v>1953</v>
       </c>
       <c r="Q70" t="n">
-        <v>18</v>
+        <v>640</v>
       </c>
       <c r="R70" t="n">
-        <v>465</v>
+        <v>2593</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6916,17 +6872,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1782262137</t>
+          <t>1180875815</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782262137</t>
+          <t>https://m.place.naver.com/place/1180875815</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6938,29 +6894,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일보담</t>
+          <t>네일드와</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>gmldo111@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1344-9616</t>
+          <t>0507-1445-1545</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로926번길 12 금탑프라자 103호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 305호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_bodam/?r=nametag</t>
+          <t>https://www.instagram.com/nail_de_wa</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6986,7 +6942,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6995,13 +6951,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>297</v>
+        <v>722</v>
       </c>
       <c r="Q71" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="R71" t="n">
-        <v>336</v>
+        <v>738</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7010,17 +6966,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1229535513</t>
+          <t>1349678048</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229535513</t>
+          <t>https://m.place.naver.com/place/1349678048</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7032,25 +6988,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>언투네일</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>베베네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>redsea2905@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1346-4298</t>
+          <t>0507-1309-9064</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 방아로 25 지하1층</t>
+          <t>경기도 성남시 분당구 장미로 78 시그마3오피스텔 3층 308호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/untonail_?igsh=MXI0ejlrc3FkOGNvcA%3D%3D&amp;utm_source=qr</t>
+          <t>http://www.instagram.com/bebe.nailstudio</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7085,13 +7045,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>90</v>
+        <v>342</v>
       </c>
       <c r="Q72" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="R72" t="n">
-        <v>98</v>
+        <v>368</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7100,17 +7060,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1449565892</t>
+          <t>1290736362</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1449565892</t>
+          <t>https://m.place.naver.com/place/1290736362</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7122,29 +7082,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>쏘굿네일 분당미금점</t>
+          <t>네일다움 내성발톱 무좀 발각질 네일 문제성발 디톡스족욕</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>sohyun1304@naver.com</t>
+          <t>nail_dawoom@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1427-2394</t>
+          <t>0507-1483-9994</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 73 우방코아 2층 211호</t>
+          <t>경기도 성남시 분당구 돌마로 85 동양프라자 4층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/sso_good_nail</t>
+          <t>https://www.instagram.com/foot_naildawoom</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7179,13 +7139,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1411</v>
+        <v>632</v>
       </c>
       <c r="Q73" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R73" t="n">
-        <v>1801</v>
+        <v>1021</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7194,17 +7154,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1235289874</t>
+          <t>1587982343</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1235289874</t>
+          <t>https://m.place.naver.com/place/1587982343</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7216,29 +7176,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>루미네일 수내점</t>
+          <t>어도어네일스튜디오</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>halobebe@naver.com</t>
+          <t>gywjd2303@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1445-6255</t>
+          <t>0507-1391-6431</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로165번길 38 청구아파트 상가 601동 125호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 8 킨스타워 3층 311호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luminail_bd</t>
+          <t>https://www.instagram.com/adorenail__?igsh=MThpanMxYXA3a2M1aA==</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7273,13 +7233,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>522</v>
+        <v>158</v>
       </c>
       <c r="Q74" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="R74" t="n">
-        <v>551</v>
+        <v>197</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7288,17 +7248,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1065650334</t>
+          <t>1011483246</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065650334</t>
+          <t>https://m.place.naver.com/place/1011483246</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7310,12 +7270,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>요푸네일</t>
+          <t>네일그자체</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>may_12kr@naver.com</t>
+          <t>wisp1205@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -7323,17 +7283,17 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 158 5층 505호</t>
+          <t>경기도 성남시 분당구 동판교로52번길 21-5 1층 103호 일부</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_YxnRpxj?fbclid=PAAabkExMKD1XfiHVnimpBpaxeFWr-IdBTPk4ssczHjPJqMvRDPWrhZlMlVNY</t>
+          <t>https://www.instagram.com/nail_itself</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7354,7 +7314,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7363,13 +7323,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="Q75" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="R75" t="n">
-        <v>13</v>
+        <v>193</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7378,17 +7338,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1301522129</t>
+          <t>2089755300</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1301522129</t>
+          <t>https://m.place.naver.com/place/2089755300</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7400,25 +7360,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일604</t>
+          <t>마틸다네일M 분당점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0507-1327-5862</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 20 노블리치오피스텔 A동208호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-13 3층 301호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail604_ss</t>
+          <t>https://www.instagram.com/matilda_nailshop</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7453,13 +7409,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1556</v>
+        <v>149</v>
       </c>
       <c r="Q76" t="n">
-        <v>39</v>
+        <v>1306</v>
       </c>
       <c r="R76" t="n">
-        <v>1595</v>
+        <v>1455</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7468,17 +7424,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1789988736</t>
+          <t>1714191610</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1789988736</t>
+          <t>https://m.place.naver.com/place/1714191610</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
